--- a/A549_TGFB1/GO_Enrichment_Results.xlsx
+++ b/A549_TGFB1/GO_Enrichment_Results.xlsx
@@ -569,12 +569,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'ITM2B', 'PTGR1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'PYGB', 'ZNHIT6', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'PLOD2', 'PSMB3', 'IGFBP7', 'B4GALT1', 'CTSB', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'TKT', 'ATP6AP2', 'B2M', 'PGK1', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'KRT18', 'PCMT1', 'YWHAE', 'ANXA4', 'ALDH1A1', 'G6PD', 'MYOF', 'ALDH2', 'NUCB2', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'CDC42', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'PYGL', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'SIRPA', 'AKR1C1', 'PDGFC', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'C1GALT1C1', 'TUBB4B', 'CCT3', 'CTNNB1', 'DDX5', 'LMAN1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'ST3GAL1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'GSTP1', 'MYOF', 'HSP90AB1', 'RPL26', 'PYGB', 'TXN', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'ATP1B1', 'AKR1C3', 'PPP1CB', 'APLP2', 'ALDH7A1', 'CNTN1', 'WNT7A', 'PYGL', 'PSMC6', 'SERPINB1', 'UBB', 'ANXA2', 'TAGLN2', 'GAPDH', 'MYL12B', 'IGFBP7', 'HSP90AA1', 'HSPB1', 'KRT18', 'FABP5', 'SLC3A2', 'CAPG', 'ITGB4', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'SERINC2', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'AKR1C1', 'HPGD', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'TM7SF3', 'CDK1', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FUCA2', 'CCT3', 'TUBA1A', 'DNAJA1', 'ANXA3', 'NPC2', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'CTSB', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'SFRP1']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -586,42 +586,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GO:0031982</t>
+          <t>GO:1903561</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vesicle</t>
+          <t>extracellular vesicle</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.508963198729586e-12</v>
+        <v>1.019378360749449e-11</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>"Any small, fluid-filled, spherical organelle enclosed by membrane." [GOC:mah, GOC:pz, GOC:vesicles]</t>
+          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>732</v>
+        <v>472</v>
       </c>
       <c r="H3" t="n">
         <v>409</v>
       </c>
       <c r="I3" t="n">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="J3" t="n">
         <v>2717</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4425427872860636</v>
+        <v>0.3251833740831296</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2472677595628415</v>
+        <v>0.2817796610169492</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -630,17 +630,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>['GO:0043227']</t>
+          <t>['GO:0031982', 'GO:0065010']</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'ITM2B', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'UBB', 'SDC4', 'CLU', 'CAV1', 'HSPA1A', 'NAP1L1', 'PYGB', 'ZNHIT6', 'DERL1', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'TSPAN4', 'SLC3A2', 'CSRP1', 'AKR1B1', 'UBR4', 'MYL12A', 'RPL28', 'HSP90AB1', 'BMP1', 'PLOD2', 'PSMB3', 'CTTN', 'TIMP2', 'IGFBP7', 'B4GALT1', 'CTSB', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'BCL2L1', 'KRT7', 'PRCP', 'PSMC2', 'WIPI1', 'TKT', 'ATP6AP2', 'B2M', 'PGK1', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'DNER', 'S100A10', 'KRT8', 'LAPTM4A', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'GAL', 'KRT18', 'HILPDA', 'F2RL1', 'PCMT1', 'YWHAE', 'PMEPA1', 'PHLDA1', 'SERPINE2', 'ANXA4', 'PSMD11', 'ALDH1A1', 'G6PD', 'MYOF', 'ALDH2', 'NUCB2', 'FABP5', 'AREG', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'FGFR1', 'CDC42', 'MT3', 'ILF2', 'MYL6', 'CALM2', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'ULK1', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'PTP4A1', 'BDNF', 'PYGL', 'NPTX1', 'ADH5', 'ANXA2', 'ANTXR1', 'S100A6', 'TUBA4A', 'MGST1', 'CDK1', 'SERPINE1', 'SERPINB1', 'SPHK1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'SKIL', 'ECE1', 'PSMA4', 'CBR1', 'F2R', 'TAGLN2', 'AP1M2', 'TUBA1C', 'KRT19', 'CAPG', 'PSMC6', 'TSPAN15', 'SIRPA', 'AKR1C1', 'PDGFC', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'ADA', 'C1GALT1C1', 'TUBB4B', 'TMSB4X', 'CCT3', 'PSMD1', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'PYCARD', 'DDX5', 'LMAN1', 'VIM', 'HSP90AA1', 'VPS29', 'PPP1CB', 'SPP1', 'ST3GAL1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'GSTP1', 'MYOF', 'HSP90AB1', 'RPL26', 'PYGB', 'TXN', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'ATP1B1', 'AKR1C3', 'PPP1CB', 'APLP2', 'ALDH7A1', 'CNTN1', 'WNT7A', 'PYGL', 'PSMC6', 'SERPINB1', 'UBB', 'ANXA2', 'TAGLN2', 'GAPDH', 'MYL12B', 'IGFBP7', 'HSP90AA1', 'HSPB1', 'KRT18', 'SERPINE2', 'FABP5', 'SLC3A2', 'CAPG', 'ITGB4', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'SERINC2', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'AKR1C1', 'HPGD', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'TM7SF3', 'CDK1', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FUCA2', 'CCT3', 'TUBA1A', 'DNAJA1', 'ANXA3', 'NPC2', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'CTSB', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'SFRP1']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IBA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IDA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['TAS'], ['IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['TAS'], ['HDA'], ['IEA'], ['IEA'], ['TAS'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'IBA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IEA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -652,27 +652,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GO:1903561</t>
+          <t>GO:0043230</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>extracellular vesicle</t>
+          <t>extracellular organelle</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.019378360749449e-11</v>
+        <v>1.246104393049747e-11</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
+          <t>"Organized structure of distinctive morphology and function, occurring outside the cell. Includes, for example, extracellular membrane vesicles (EMVs) and the cellulosomes of anaerobic bacteria and fungi." [GOC:jl, PMID:9914479]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H4" t="n">
         <v>409</v>
@@ -687,7 +687,7 @@
         <v>0.3251833740831296</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2817796610169492</v>
+        <v>0.2811839323467231</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -696,17 +696,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>['GO:0031982', 'GO:0065010']</t>
+          <t>['GO:0005576', 'GO:0043226']</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'ITM2B', 'PTGR1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'PYGB', 'ZNHIT6', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'PLOD2', 'PSMB3', 'IGFBP7', 'B4GALT1', 'CTSB', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'TKT', 'ATP6AP2', 'B2M', 'PGK1', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'KRT18', 'PCMT1', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'G6PD', 'MYOF', 'ALDH2', 'NUCB2', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'CDC42', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'PYGL', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'SIRPA', 'AKR1C1', 'PDGFC', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'C1GALT1C1', 'TUBB4B', 'CCT3', 'CTNNB1', 'DDX5', 'LMAN1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'ST3GAL1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'GSTP1', 'MYOF', 'HSP90AB1', 'RPL26', 'PYGB', 'TXN', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'ATP1B1', 'AKR1C3', 'PPP1CB', 'APLP2', 'ALDH7A1', 'CNTN1', 'WNT7A', 'PYGL', 'PSMC6', 'SERPINB1', 'UBB', 'ANXA2', 'TAGLN2', 'GAPDH', 'MYL12B', 'IGFBP7', 'HSP90AA1', 'HSPB1', 'KRT18', 'SERPINE2', 'FABP5', 'SLC3A2', 'CAPG', 'ITGB4', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'SERINC2', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'AKR1C1', 'HPGD', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'TM7SF3', 'CDK1', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FUCA2', 'CCT3', 'TUBA1A', 'DNAJA1', 'ANXA3', 'NPC2', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'CTSB', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'SFRP1']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GO:0043230</t>
+          <t>GO:0065010</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>extracellular organelle</t>
+          <t>extracellular membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, occurring outside the cell. Includes, for example, extracellular membrane vesicles (EMVs) and the cellulosomes of anaerobic bacteria and fungi." [GOC:jl, PMID:9914479]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -762,17 +762,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>['GO:0005576', 'GO:0043226']</t>
+          <t>['GO:0043227', 'GO:0043230']</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'ITM2B', 'PTGR1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'PYGB', 'ZNHIT6', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'PLOD2', 'PSMB3', 'IGFBP7', 'B4GALT1', 'CTSB', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'TKT', 'ATP6AP2', 'B2M', 'PGK1', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'KRT18', 'PCMT1', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'G6PD', 'MYOF', 'ALDH2', 'NUCB2', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'CDC42', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'PYGL', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'SIRPA', 'AKR1C1', 'PDGFC', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'C1GALT1C1', 'TUBB4B', 'CCT3', 'CTNNB1', 'DDX5', 'LMAN1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'ST3GAL1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'GSTP1', 'MYOF', 'HSP90AB1', 'RPL26', 'PYGB', 'TXN', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'ATP1B1', 'AKR1C3', 'PPP1CB', 'APLP2', 'ALDH7A1', 'CNTN1', 'WNT7A', 'PYGL', 'PSMC6', 'SERPINB1', 'UBB', 'ANXA2', 'TAGLN2', 'GAPDH', 'MYL12B', 'IGFBP7', 'HSP90AA1', 'HSPB1', 'KRT18', 'SERPINE2', 'FABP5', 'SLC3A2', 'CAPG', 'ITGB4', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'SERINC2', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'AKR1C1', 'HPGD', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'TM7SF3', 'CDK1', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FUCA2', 'CCT3', 'TUBA1A', 'DNAJA1', 'ANXA3', 'NPC2', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'CTSB', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'SFRP1']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -784,42 +784,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GO:0065010</t>
+          <t>GO:0031982</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>extracellular membrane-bounded organelle</t>
+          <t>vesicle</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.246104393049747e-11</v>
+        <v>3.079056241617608e-11</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a lipid bilayer membrane and occurring outside the cell." [GOC:isa_complete]</t>
+          <t>"Any small, fluid-filled, spherical organelle enclosed by membrane." [GOC:mah, GOC:pz, GOC:vesicles]</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>473</v>
+        <v>735</v>
       </c>
       <c r="H6" t="n">
         <v>409</v>
       </c>
       <c r="I6" t="n">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="J6" t="n">
         <v>2717</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251833740831296</v>
+        <v>0.4400977995110024</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2811839323467231</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>['GO:0043227', 'GO:0043230']</t>
+          <t>['GO:0043227']</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'ITM2B', 'PTGR1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'PYGB', 'ZNHIT6', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'PLOD2', 'PSMB3', 'IGFBP7', 'B4GALT1', 'CTSB', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'TKT', 'ATP6AP2', 'B2M', 'PGK1', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'KRT18', 'PCMT1', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'G6PD', 'MYOF', 'ALDH2', 'NUCB2', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'CDC42', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'PYGL', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'SIRPA', 'AKR1C1', 'PDGFC', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'C1GALT1C1', 'TUBB4B', 'CCT3', 'CTNNB1', 'DDX5', 'LMAN1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'ST3GAL1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'RPL28', 'GSTP1', 'UBR4', 'MYOF', 'HSP90AB1', 'RPL26', 'PYGB', 'TXN', 'YWHAE', 'MGST1', 'S100A6', 'SIRPA', 'OCIAD2', 'NAP1L1', 'SKIL', 'BCL2L1', 'SLC2A3', 'TSPAN4', 'GLA', 'RDX', 'CD9', 'LDHA', 'DYNLL1', 'ADH5', 'LMAN1', 'PTP4A1', 'CSRP1', 'PRCP', 'ATP1B1', 'AKR1C3', 'HILPDA', 'PPP1CB', 'APLP2', 'ALDH7A1', 'COL1A1', 'EDN1', 'CNTN1', 'WNT7A', 'PYGL', 'PSMC6', 'SERPINB1', 'ANTXR1', 'UBB', 'F2RL1', 'ULK1', 'ANXA2', 'TAGLN2', 'PMEPA1', 'GAPDH', 'MYL12B', 'DERL1', 'SPHK1', 'IGFBP7', 'AREG', 'HSP90AA1', 'LAPTM4A', 'PHLDA1', 'HSPB1', 'KRT18', 'CALM2', 'SERPINE2', 'FABP5', 'ADA', 'SLC3A2', 'CAPG', 'ITGB4', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'NTS', 'SERINC2', 'F2R', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'AKR1C1', 'BDNF', 'HPGD', 'ACTB', 'TUBA1C', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'AP1M2', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'PSMC2', 'TM7SF3', 'CDK1', 'CTTN', 'WIPI1', 'MUC5AC', 'TSPAN15', 'NUCB2', 'S100A10', 'CDC42', 'TMSB4X', 'CAV1', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'DNER', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'PSMD11', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FGFR1', 'VPS29', 'ILF2', 'FUCA2', 'CCT3', 'TUBA1A', 'NPTX1', 'PSMD1', 'CXCL1', 'DNAJA1', 'ANXA3', 'BMP1', 'NPC2', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'MT3', 'TIMP2', 'LDHB', 'CTSB', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'SFRP1']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['HDA', 'TAS'], ['IDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['IBA'], ['IDA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'TAS'], ['HDA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['IEA'], ['TAS'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.491437337766517e-10</v>
+        <v>1.634836644646662e-10</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H7" t="n">
         <v>409</v>
       </c>
       <c r="I7" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" t="n">
         <v>2717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4156479217603912</v>
+        <v>0.4180929095354523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2442528735632184</v>
+        <v>0.2463976945244957</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'LAMC2', 'ITM2B', 'PTGR1', 'EDN1', 'UBB', 'SDC4', 'CLU', 'CCL2', 'HSPA1A', 'IL32', 'PYGB', 'ZNHIT6', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'CXCL5', 'DMKN', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'BMP1', 'PLOD2', 'PSMB3', 'IGFBP3', 'TIMP2', 'IGFBP7', 'B4GALT1', 'CTSB', 'CLCF1', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'IGFL3', 'COL4A1', 'LTBP4', 'TKT', 'IGFBP4', 'ATP6AP2', 'B2M', 'PGK1', 'CXCL1', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'GAL', 'KRT18', 'HILPDA', 'PCMT1', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'TIMP4', 'G6PD', 'MYOF', 'ALDH2', 'ALDH3A1', 'NUCB2', 'FABP5', 'ANGPTL4', 'AREG', 'AIMP1', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'CDC42', 'MT3', 'NMI', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'BDNF', 'PYGL', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'HMGB2', 'PSMA4', 'IL18', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'TNFRSF1A', 'SIRPA', 'AKR1C1', 'PDGFC', 'VCAN', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'ATXN10', 'IGFBP6', 'C1GALT1C1', 'TUBB4B', 'IL11', 'CCT3', 'CTNNB1', 'COL1A1', 'DDX5', 'AGR2', 'LMAN1', 'VIM', 'KRT81', 'HSP90AA1', 'CXCL8', 'PPP1CB', 'SPP1', 'ST3GAL1', 'STC1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'ANGPTL4', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'LTBP4', 'GSTP1', 'MYOF', 'ATXN10', 'HSP90AB1', 'RPL26', 'NMI', 'PYGB', 'TXN', 'TIMP4', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'IL11', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'DMKN', 'ATP1B1', 'AKR1C3', 'HILPDA', 'PPP1CB', 'APLP2', 'ALDH7A1', 'COL1A1', 'EDN1', 'CNTN1', 'RSPO3', 'WNT7A', 'PYGL', 'PSMC6', 'LAMC2', 'SERPINB1', 'UBB', 'CCL2', 'AIMP1', 'ANXA2', 'TAGLN2', 'TNFRSF1A', 'GAPDH', 'MYL12B', 'IGFBP6', 'IGFBP7', 'AREG', 'HSP90AA1', 'HSPB1', 'KRT18', 'SERPINE2', 'FABP5', 'SLC3A2', 'CAPG', 'ITGB4', 'CXCL5', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'SERINC2', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'AGR2', 'B2M', 'AKR1C1', 'BDNF', 'IGFBP3', 'HPGD', 'KRT81', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'PSMB3', 'TM7SF3', 'CDK1', 'IL18', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FUCA2', 'IGFL3', 'HMGB2', 'CCT3', 'VCAN', 'TUBA1A', 'CLCF1', 'CXCL1', 'DNAJA1', 'ANXA3', 'BMP1', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'MT3', 'TIMP2', 'LDHB', 'IGFBP4', 'CTSB', 'ALDH3A1', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'COL4A1', 'SFRP1']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IBA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['IBA'], ['HDA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IMP', 'HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IBA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IBA'], ['IBA', 'TAS'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['HDA'], ['HDA'], ['IBA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IBA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IBA'], ['IDA', 'HDA', 'IBA']]</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.321646745729956e-08</v>
+        <v>8.728883221472592e-09</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="H8" t="n">
         <v>409</v>
@@ -951,7 +951,7 @@
         <v>0.4547677261613692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2293464858199753</v>
+        <v>0.2301980198019802</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -965,12 +965,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'LAMC2', 'ITM2B', 'PTGR1', 'EDN1', 'UBB', 'LYPD1', 'SDC4', 'CLU', 'CCL2', 'HSPA1A', 'IL32', 'CCDC80', 'PYGB', 'ZNHIT6', 'RSPO3', 'MUC5AC', 'ACTB', 'FUCA2', 'HSPA5', 'CNTN1', 'SLC3A2', 'CSRP1', 'CXCL5', 'DMKN', 'AKR1B1', 'MYL12A', 'RPL28', 'HSP90AB1', 'BMP1', 'PLOD2', 'PSMB3', 'IGFBP3', 'TIMP2', 'AKR1B10', 'IGFBP7', 'B4GALT1', 'CTSB', 'CLCF1', 'HPGD', 'ATIC', 'RPL26', 'GPX3', 'KRT7', 'PRCP', 'PSMC2', 'IGFL3', 'COL4A1', 'LTBP4', 'TKT', 'IGFBP4', 'ATP6AP2', 'B2M', 'PGK1', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'S100A10', 'KRT8', 'HSPB1', 'LGALS3', 'GLA', 'ITGB4', 'SDC1', 'AKR1C3', 'C1orf56', 'GAL', 'KRT18', 'HILPDA', 'PCMT1', 'YWHAE', 'SERPINE2', 'ANXA4', 'PSMD11', 'ALDH1A1', 'TIMP4', 'G6PD', 'PGRMC2', 'MYOF', 'ALDH2', 'ALDH3A1', 'NUCB2', 'FABP5', 'ANGPTL4', 'AREG', 'AIMP1', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'ALDH7A1', 'SLC26A2', 'APP', 'TUBA1A', 'APLP2', 'FGFR1', 'CDC42', 'MT3', 'NMI', 'ILF2', 'MYL6', 'S100A4', 'LGALS1', 'SVIP', 'CTSL', 'GAPDH', 'CD9', 'MYL12B', 'SULT2B1', 'SERINC2', 'JUP', 'ACP2', 'TGFBI', 'COTL1', 'BDNF', 'PYGL', 'NPTX1', 'ADH5', 'ANXA2', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'SERPINB1', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'ECE1', 'HMGB2', 'PSMA4', 'IL18', 'CBR1', 'F2R', 'TAGLN2', 'KRT19', 'CAPG', 'PSMC6', 'TNFRSF1A', 'SIRPA', 'AKR1C1', 'PDGFC', 'VCAN', 'NPC2', 'FN1', 'DNAJA1', 'RDX', 'ATXN10', 'IGFBP6', 'C1GALT1C1', 'TUBB4B', 'IL11', 'TMSB4X', 'CCT3', 'PSMD1', 'CTNNB1', 'COL1A1', 'PYCARD', 'DDX5', 'AGR2', 'LMAN1', 'VIM', 'KRT81', 'HSP90AA1', 'CXCL8', 'PPP1CB', 'SPP1', 'ST3GAL1', 'STC1', 'RAB3B', 'COL4A2', 'WNT7A', 'GSTP1', 'PACSIN3', 'RRAS', 'SLC2A3', 'SQSTM1', 'ATP1B1', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'RRAS', 'ITM2B', 'MYL6', 'ANGPTL4', 'CCT4', 'ZNHIT6', 'TUBA4A', 'PSMD7', 'MFGE8', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'RPL28', 'LTBP4', 'GSTP1', 'MYOF', 'ATXN10', 'HSP90AB1', 'RPL26', 'C1orf56', 'NMI', 'PYGB', 'TXN', 'TIMP4', 'YWHAE', 'S100A6', 'SIRPA', 'SLC2A3', 'GLA', 'RDX', 'IL11', 'CD9', 'LDHA', 'ADH5', 'LMAN1', 'CSRP1', 'PRCP', 'DMKN', 'ATP1B1', 'AKR1C3', 'HILPDA', 'PPP1CB', 'APLP2', 'ALDH7A1', 'COL1A1', 'EDN1', 'CNTN1', 'RSPO3', 'WNT7A', 'PYGL', 'PSMC6', 'LAMC2', 'SERPINB1', 'UBB', 'CCL2', 'AIMP1', 'ANXA2', 'TAGLN2', 'TNFRSF1A', 'GAPDH', 'MYL12B', 'IGFBP6', 'IGFBP7', 'AREG', 'HSP90AA1', 'HSPB1', 'KRT18', 'SERPINE2', 'FABP5', 'SLC3A2', 'PGRMC2', 'CAPG', 'ITGB4', 'CXCL5', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'DDX5', 'SPP1', 'CD44', 'COL4A2', 'LGALS3', 'NTS', 'SERINC2', 'F2R', 'APP', 'PRDX1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'FN1', 'HSPA1A', 'AGR2', 'B2M', 'AKR1C1', 'BDNF', 'IGFBP3', 'HPGD', 'KRT81', 'ACTB', 'ST3GAL1', 'RAB3B', 'ANXA4', 'PDGFC', 'PACSIN3', 'CLU', 'FTL', 'SDC4', 'ATIC', 'AKR1B10', 'PSMB3', 'PSMC2', 'TM7SF3', 'CDK1', 'IL18', 'MUC5AC', 'NUCB2', 'S100A10', 'CDC42', 'TMSB4X', 'PCMT1', 'MYL12A', 'KRT19', 'SERPINE1', 'VIM', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'PSMD11', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'GPX3', 'SLC26A2', 'FGFR1', 'LYPD1', 'ILF2', 'FUCA2', 'IGFL3', 'HMGB2', 'CCT3', 'VCAN', 'TUBA1A', 'CLCF1', 'NPTX1', 'PSMD1', 'CXCL1', 'DNAJA1', 'ANXA3', 'BMP1', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'ALDH2', 'CD63', 'COTL1', 'PTGR1', 'UBC', 'MT3', 'CCDC80', 'TIMP2', 'LDHB', 'IGFBP4', 'CTSB', 'ALDH3A1', 'ECH1', 'ECE1', 'JUP', 'PLOD2', 'COL4A1', 'SFRP1']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['NAS'], ['HDA'], ['IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['HDA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'TAS'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['NAS'], ['TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0004635528207766379</v>
+        <v>0.0003659126865987956</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1924</v>
+        <v>1937</v>
       </c>
       <c r="H9" t="n">
         <v>409</v>
       </c>
       <c r="I9" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J9" t="n">
         <v>2717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8215158924205379</v>
+        <v>0.8264058679706602</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1746361746361746</v>
+        <v>0.174496644295302</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1031,59 +1031,59 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['CD44', 'MRPL13', 'LDHB', 'CD63', 'ANXA3', 'CCT4', 'LDHA', 'LAMC2', 'ITM2B', 'NQO1', 'PTGR1', 'DYNLL1', 'PDHA1', 'EDN1', 'OCIAD2', 'UBB', 'HNRNPH1', 'NNMT', 'ETHE1', 'KLF6', 'KIF23', 'SDC4', 'CLU', 'CAV1', 'HSPA1A', 'PDLIM5', 'REEP5', 'TMSB10', 'IL32', 'NAP1L1', 'PYGB', 'ATP5G1', 'TOP2A', 'RASSF1', 'TUBA1B', 'NFKBIZ', 'DERL1', 'MAP1B', 'CDK2AP2', 'MUC5AC', 'AATF', 'ACTB', 'FUCA2', 'HSPA5', 'RND1', 'CHCHD10', 'GALNT14', 'SLC3A2', 'CSRP1', 'UPF3B', 'AKR1B1', 'UBR4', 'MYL12A', 'RPL28', 'TPD52', 'TMBIM6', 'ID3', 'POLR2L', 'HSP90AB1', 'BMP1', 'DRAM1', 'PLOD2', 'PSMB3', 'CTTN', 'IGFBP3', 'TIMP2', 'AKR1B10', 'IGFBP7', 'B4GALT1', 'CTSB', 'CALB2', 'HPGD', 'ATIC', 'RPL26', 'CDC42SE1', 'BCL2L1', 'CCNB1', 'KRT7', 'PRCP', 'NUP37', 'FRMD6', 'SPDL1', 'MT2A', 'PSMC2', 'FILIP1', 'COL4A1', 'SCD', 'WIPI1', 'TKT', 'CCND1', 'IGFBP4', 'ATP6AP2', 'B2M', 'PTTG1', 'RBP1', 'PGK1', 'OSBPL8', 'UBE2S', 'HMGA1', 'CKAP2L', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'CPLX2', 'FBXO22', 'DNER', 'S100A10', 'KRT8', 'PLK2', 'LAPTM4A', 'HSPB1', 'LGALS3', 'GLA', 'LCE3D', 'SDC1', 'C15orf48', 'AKR1C3', 'EPHX1', 'HACD3', 'GAL', 'NUDT19', 'KRT18', 'NUAK1', 'HILPDA', 'CYP24A1', 'F2RL1', 'BAMBI', 'PCMT1', 'RND3', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'PHLDA1', 'SERPINE2', 'ANXA4', 'PSMD11', 'NIFK', 'ALDH1A1', 'G6PD', 'MYO10', 'PGRMC2', 'ETFB', 'MYOF', 'PERP', 'ALDH2', 'ALDH3A1', 'PGM2L1', 'NUCB2', 'ARHGAP29', 'FABP5', 'AREG', 'AIMP1', 'TXN', 'HSPA2', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TSFM', 'TGM2', 'ALDH7A1', 'ODC1', 'APP', 'PHLDA2', 'PDLIM2', 'TUBA1A', 'APLP2', 'EIF1', 'NEK6', 'FGFR1', 'MICAL2', 'LMNA', 'CDC42', 'FDXR', 'AIMP2', 'CREM', 'MT3', 'CDKN1A', 'AHNAK2', 'DHRS3', 'NMI', 'CXXC5', 'ILF2', 'CALD1', 'MYL6', 'CALM2', 'S100A4', 'LGALS1', 'CYB5A', 'SVIP', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'DHRS7', 'TK1', 'NPM1', 'CD9', 'LRRC75A', 'MYL12B', 'ZFAS1', 'SULT2B1', 'LBH', 'FHL1', 'JUP', 'TIGAR', 'LAS1L', 'ACP2', 'TGFBI', 'RNF182', 'TXNRD2', 'TSC22D1', 'COTL1', 'PTP4A1', 'NFKB2', 'BDNF', 'SFPQ', 'PYGL', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'ADH5', 'SAT1', 'BLOC1S2', 'HSD17B11', 'TRIB3', 'ANXA2', 'ELF3', 'ANTXR1', 'S100A6', 'CNN3', 'TUBA4A', 'MGST1', 'CDK1', 'MT-ND6', 'SERPINE1', 'PRMT5', 'SERPINB1', 'TROAP', 'SPHK1', 'HNRNPH2', 'SRP54', 'ECH1', 'SFRP1', 'PSMD7', 'MOB3B', 'UBC', 'SKIL', 'ECE1', 'SPATS2', 'HMGB2', 'PSMA4', 'CCDC85B', 'BIRC3', 'IL18', 'LACTB2', 'CBR1', 'F2R', 'TAGLN2', 'MT1X', 'AP1M2', 'TUBA1C', 'KRT19', 'CAPG', 'PSMC6', 'RGS3', 'TSPAN15', 'TNFRSF1A', 'SIRPA', 'AKR1C1', 'PDGFC', 'VCAN', 'NPC2', 'DUSP1', 'TMPO', 'FN1', 'DNAJA1', 'RDX', 'EPAS1', 'BCCIP', 'AIFM1', 'ADA', 'ATXN10', 'TP53I3', 'VRK1', 'C1GALT1C1', 'LACTB', 'TUBB4B', 'IL11', 'TMSB4X', 'CCT3', 'PSMD1', 'CDK5RAP1', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'HCFC1R1', 'PYCARD', 'DDX5', 'AGR2', 'FA2H', 'LMAN1', 'GPX2', 'BCL2A1', 'VIM', 'KRT81', 'FEN1', 'HSP90AA1', 'VPS29', 'BZW1', 'PPP1CB', 'SPP1', 'ST3GAL1', 'STC1', 'ZFP36', 'RAB3B', 'COL4A2', 'MLXIP', 'CDKN3', 'TPM1', 'WNT7A', 'SOX4', 'GSTP1', 'KPNA2', 'PACSIN3', 'PHLDA3', 'NEK7', 'SLC2A3', 'PTGES3', 'SQSTM1', 'PLEK2', 'MT1F', 'PRDX1', 'PLK1']</t>
+          <t>['HSPA2', 'CXXC5', 'TXNRD2', 'CTNNB1', 'ITM2B', 'TK1', 'MYL6', 'NNMT', 'RAP1GAP', 'CCT4', 'TUBA4A', 'PSMD7', 'SPATS2', 'CDK5RAP1', 'MFGE8', 'TRIB3', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'ETHE1', 'RPL28', 'GSTP1', 'UBR4', 'NFKBIZ', 'MYOF', 'ATXN10', 'HSP90AB1', 'KYNU', 'RPL26', 'CYP24A1', 'NMI', 'PYGB', 'TXN', 'MRPL13', 'PERP', 'YWHAE', 'SOX4', 'HCFC1R1', 'CNN3', 'MGST1', 'S100A6', 'FA2H', 'SIRPA', 'OCIAD2', 'LRRC75A', 'ID3', 'NAP1L1', 'SKIL', 'SCD', 'BCL2L1', 'SLC2A3', 'GLA', 'SFPQ', 'UBE2C', 'MT1F', 'RDX', 'MGST3', 'IL11', 'FBXO22', 'LACTB', 'CCDC85B', 'RNF182', 'NFKB2', 'PRMT5', 'BCL2A1', 'CD9', 'PHLDA2', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'LMAN1', 'PTP4A1', 'CSRP1', 'PRCP', 'EPAS1', 'LAS1L', 'ATP5G1', 'KLF6', 'AKR1C3', 'HILPDA', 'PPP1CB', 'APLP2', 'ALDH7A1', 'COL1A1', 'EDN1', 'EPHX1', 'C15orf48', 'CPLX2', 'WNT7A', 'PYGL', 'PSMC6', 'HSD17B11', 'LAMC2', 'SERPINB1', 'ANTXR1', 'UBB', 'NPM1', 'F2RL1', 'NUP37', 'GPX2', 'ULK1', 'TROAP', 'PLEK2', 'CHCHD10', 'AIMP1', 'ANXA2', 'TAGLN2', 'PMEPA1', 'TNFRSF1A', 'FILIP1', 'MT1X', 'GAPDH', 'MYL12B', 'DERL1', 'AIFM1', 'SPHK1', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'HSP90AA1', 'LAPTM4A', 'PHLDA1', 'HSPB1', 'PDHA1', 'KRT18', 'MLXIP', 'CDK2AP2', 'TMBIM6', 'ETFB', 'ARL6IP1', 'CALM2', 'SERPINE2', 'UPF3B', 'RGS3', 'FABP5', 'LCE3D', 'ADA', 'LACTB2', 'SLC3A2', 'PGRMC2', 'CAPG', 'BIRC3', 'HNRNPH2', 'PHLDA3', 'G6PD', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'C1GALT1C1', 'UBE2S', 'DDX5', 'MICAL2', 'TUBA1B', 'AIMP2', 'SPP1', 'KIF23', 'RND1', 'CD44', 'GALNT14', 'NEK6', 'PDLIM5', 'COL4A2', 'LGALS3', 'RND3', 'NTS', 'F2R', 'APP', 'PRDX1', 'RASSF1', 'AKR1B1', 'TGFBI', 'ORMDL2', 'OSBPL8', 'SULT2B1', 'SVIP', 'SAT1', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'B2M', 'AKR1C1', 'BDNF', 'IGFBP3', 'FEN1', 'HPGD', 'KRT81', 'ACTB', 'NUDT19', 'TUBA1C', 'ST3GAL1', 'NUAK1', 'CDKN3', 'RAB3B', 'ANXA4', 'NIFK', 'PDGFC', 'PACSIN3', 'MOB3B', 'CLU', 'PDLIM2', 'AP1M2', 'FTL', 'SDC4', 'BLOC1S2', 'ATIC', 'AKR1B10', 'PSMB3', 'PSMC2', 'VRK1', 'PLK2', 'DUSP1', 'CDK1', 'MYO10', 'IL18', 'SRP54', 'AATF', 'TPM1', 'DHRS2', 'CTTN', 'WIPI1', 'THOC2', 'PLK1', 'MUC5AC', 'TSPAN15', 'ODC1', 'HMGA1', 'NUCB2', 'S100A10', 'CDC42', 'ARHGAP29', 'TMSB4X', 'CDKN1A', 'LBH', 'CAV1', 'PCMT1', 'MYL12A', 'NQO1', 'KRT19', 'SERPINE1', 'VIM', 'DNER', 'PGK1', 'NEK7', 'LGALS1', 'GAL', 'CCND1', 'TKT', 'ALDH1A1', 'KRT8', 'EIF1', 'AHNAK2', 'TGM2', 'PSMD11', 'CKAP2L', 'CBR1', 'KRT7', 'S100A4', 'CTSL', 'SDC1', 'TMSB10', 'FGFR1', 'VPS29', 'TOP2A', 'ILF2', 'FUCA2', 'RBP1', 'HMGB2', 'TIGAR', 'PTGES3', 'MT2A', 'PTTG1', 'DRAM1', 'TPD52', 'CCT3', 'VCAN', 'TUBA1A', 'ZFAS1', 'SPDL1', 'BAMBI', 'FHL1', 'INO80C', 'NPTX1', 'PSMD1', 'TSC22D1', 'CXCL1', 'TP53I3', 'DNAJA1', 'CALD1', 'ANXA3', 'BMP1', 'CDC42SE1', 'DHRS3', 'ZFP36', 'IL32', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'DHRS7', 'ALDH2', 'CD63', 'TPM2', 'COTL1', 'LMNA', 'PTGR1', 'UBC', 'CYB5A', 'MT3', 'BCCIP', 'PGM2L1', 'TIMP2', 'LDHB', 'CALB2', 'IGFBP4', 'CTSB', 'ALDH3A1', 'ECH1', 'ECE1', 'CREM', 'PUS1', 'JUP', 'PLOD2', 'MAP1B', 'COL4A1', 'HNRNPH1', 'SFRP1', 'FRMD6', 'HACD3', 'TMPO', 'KPNA2', 'BZW1']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['HTP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'ISS', 'IEA'], ['IBA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA']]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GO:0031410</t>
+          <t>GO:0031398</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cytoplasmic vesicle</t>
+          <t>positive regulation of protein ubiquitination</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.007096572063921885</v>
+        <v>0.009774875821631565</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>"A vesicle found in the cytoplasm of a cell." [GOC:ai, GOC:mah, GOC:vesicles]</t>
+          <t>"Any process that activates or increases the frequency, rate or extent of the addition of ubiquitin groups to a protein." [GOC:mah]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>436</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
         <v>409</v>
       </c>
       <c r="I10" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>2717</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2518337408312958</v>
+        <v>0.03178484107579462</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2362385321100917</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1092,49 +1092,49 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>['GO:0005737', 'GO:0097708']</t>
+          <t>['GO:0016567', 'GO:0031396', 'GO:1903322']</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'CCT4', 'ITM2B', 'DYNLL1', 'EDN1', 'OCIAD2', 'UBB', 'CLU', 'CAV1', 'HSPA1A', 'NAP1L1', 'PYGB', 'DERL1', 'FUCA2', 'HSPA5', 'SLC3A2', 'UBR4', 'HSP90AB1', 'CTTN', 'TIMP2', 'B4GALT1', 'CTSB', 'BCL2L1', 'PRCP', 'PSMC2', 'WIPI1', 'ATP6AP2', 'B2M', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'DNER', 'LAPTM4A', 'LGALS3', 'GLA', 'GAL', 'HILPDA', 'F2RL1', 'YWHAE', 'PMEPA1', 'PHLDA1', 'SERPINE2', 'ANXA4', 'PSMD11', 'MYOF', 'FABP5', 'AREG', 'ANXA1', 'APP', 'TUBA1A', 'APLP2', 'FGFR1', 'CDC42', 'MT3', 'ILF2', 'SVIP', 'CTSL', 'ULK1', 'CD9', 'JUP', 'COTL1', 'PTP4A1', 'BDNF', 'PYGL', 'NPTX1', 'ANXA2', 'ANTXR1', 'MGST1', 'SERPINE1', 'SERPINB1', 'SPHK1', 'PSMD7', 'UBC', 'SKIL', 'ECE1', 'F2R', 'AP1M2', 'CAPG', 'TSPAN15', 'SIRPA', 'NPC2', 'FN1', 'ADA', 'TUBB4B', 'TMSB4X', 'PSMD1', 'COL1A1', 'RAP1GAP', 'PYCARD', 'LMAN1', 'VIM', 'HSP90AA1', 'VPS29', 'RAB3B', 'WNT7A', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'PRDX1']</t>
+          <t>['TRIB3', 'HSPA5', 'NMI', 'UBE2C', 'UBB', 'DERL1', 'SPHK1', 'BIRC3', 'UBE2S', 'AIMP2', 'RASSF1', 'PLK1', 'CAV1']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['TAS'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['IEA']]</t>
+          <t>[['ISS'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IMP'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'IMP'], ['IMP']]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GO:0097708</t>
+          <t>GO:0012501</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>intracellular vesicle</t>
+          <t>programmed cell death</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.008065799490254733</v>
+        <v>0.01178889683826372</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>"Any vesicle that is part of the intracellular region." [GOC:vesicles]</t>
+          <t>"A process which begins when a cell receives an internal or external signal and activates a series of biochemical events (signaling pathway). The process ends with the death of the cell." [GOC:lr, GOC:mtg_apoptosis]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H11" t="n">
         <v>409</v>
@@ -1149,7 +1149,7 @@
         <v>0.2518337408312958</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2356979405034325</v>
+        <v>0.2340909090909091</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1158,64 +1158,64 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>['GO:0031982', 'GO:0043231']</t>
+          <t>['GO:0008219']</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'CCT4', 'ITM2B', 'DYNLL1', 'EDN1', 'OCIAD2', 'UBB', 'CLU', 'CAV1', 'HSPA1A', 'NAP1L1', 'PYGB', 'DERL1', 'FUCA2', 'HSPA5', 'SLC3A2', 'UBR4', 'HSP90AB1', 'CTTN', 'TIMP2', 'B4GALT1', 'CTSB', 'BCL2L1', 'PRCP', 'PSMC2', 'WIPI1', 'ATP6AP2', 'B2M', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'DNER', 'LAPTM4A', 'LGALS3', 'GLA', 'GAL', 'HILPDA', 'F2RL1', 'YWHAE', 'PMEPA1', 'PHLDA1', 'SERPINE2', 'ANXA4', 'PSMD11', 'MYOF', 'FABP5', 'AREG', 'ANXA1', 'APP', 'TUBA1A', 'APLP2', 'FGFR1', 'CDC42', 'MT3', 'ILF2', 'SVIP', 'CTSL', 'ULK1', 'CD9', 'JUP', 'COTL1', 'PTP4A1', 'BDNF', 'PYGL', 'NPTX1', 'ANXA2', 'ANTXR1', 'MGST1', 'SERPINE1', 'SERPINB1', 'SPHK1', 'PSMD7', 'UBC', 'SKIL', 'ECE1', 'F2R', 'AP1M2', 'CAPG', 'TSPAN15', 'SIRPA', 'NPC2', 'FN1', 'ADA', 'TUBB4B', 'TMSB4X', 'PSMD1', 'COL1A1', 'RAP1GAP', 'PYCARD', 'LMAN1', 'VIM', 'HSP90AA1', 'VPS29', 'RAB3B', 'WNT7A', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'PRDX1']</t>
+          <t>['CTNNB1', 'ANGPTL4', 'TRIB3', 'HSPA5', 'PYCARD', 'GSTP1', 'NFKBIZ', 'HSP90AB1', 'RPL26', 'PERP', 'SOX4', 'ID3', 'SKIL', 'BCL2L1', 'SFPQ', 'BCL2A1', 'PHLDA2', 'DYNLL1', 'AKR1C3', 'ITGA6', 'EDN1', 'HMGA2', 'WNT7A', 'PYGL', 'UBB', 'NPM1', 'F2RL1', 'CCL2', 'CHCHD10', 'AIMP1', 'ANXA2', 'TNFRSF1A', 'GAPDH', 'AIFM1', 'SPHK1', 'HSP90AA1', 'PHLDA1', 'HSPB1', 'KRT18', 'TMBIM6', 'ARL6IP1', 'ADA', 'BIRC3', 'PHLDA3', 'G6PD', 'HELLS', 'ANXA1', 'SQSTM1', 'B4GALT1', 'DDX5', 'AIMP2', 'CD44', 'NEK6', 'LGALS3', 'F2R', 'APP', 'AKR1B1', 'HSPA1A', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'ST3GAL1', 'ANXA4', 'CLU', 'BLOC1S2', 'TM7SF3', 'PLK2', 'CDK1', 'AATF', 'AMIGO2', 'DHRS2', 'CTTN', 'PLK1', 'CDKN1A', 'CAV1', 'NQO1', 'SERPINE1', 'LGALS1', 'GAL', 'CCND1', 'KRT8', 'TGM2', 'CTSL', 'FGFR1', 'JUN', 'TOP2A', 'HMGB2', 'TIGAR', 'DRAM1', 'TUBA1A', 'CLCF1', 'NPTX1', 'TSC22D1', 'DNAJA1', 'ZFP36', 'CD24', 'LMNA', 'SLC7A11', 'MT3', 'CTSB', 'SFRP1', 'EMP3']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['TAS'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['IEA']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IMP', 'IGI'], ['IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'NAS'], ['IDA'], ['IDA', 'IMP'], ['IMP'], ['IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IEA'], ['IMP'], ['IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'ISS'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'TAS'], ['ISS', 'IBA'], ['IMP', 'IEA'], ['IEA'], ['NAS'], ['IEA'], ['TAS'], ['IMP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['IMP', 'IBA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['ISS'], ['IMP'], ['IEA'], ['IMP'], ['TAS', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['IMP'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['NAS'], ['IEA'], ['IMP'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA'], ['IEA'], ['IMP', 'ISS', 'IBA'], ['IDA', 'IMP'], ['IMP'], ['NAS'], ['IEA'], ['IDA', 'IEA'], ['ISS'], ['TAS'], ['IDA', 'IMP', 'IEA'], ['IDA']]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GO:0030141</t>
+          <t>GO:0008219</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>secretory granule</t>
+          <t>cell death</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.008100802358152671</v>
+        <v>0.013358679758399</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>"A small subcellular vesicle, surrounded by a membrane, that is formed from the Golgi apparatus and contains a highly concentrated protein destined for secretion. Secretory granules move towards the periphery of the cell and upon stimulation, their membranes fuse with the cell membrane, and their protein load is exteriorized. Processing of the contained protein may take place in secretory granules." [GOC:mah, ISBN:0198506732]</t>
+          <t>"Any biological process that results in permanent cessation of all vital functions of a cell. A cell should be considered dead when any one of the following molecular or morphological criteria is met: (1) the cell has lost the integrity of its plasma membrane; (2) the cell, including its nucleus, has undergone complete fragmentation into discrete bodies (frequently referred to as apoptotic bodies). The cell corpse (or its fragments) may be engulfed by an adjacent cell in vivo, but engulfment of whole cells should not be considered a strict criteria to define cell death as, under some circumstances, live engulfed cells can be released from phagosomes (see PMID:18045538)." [GOC:mah, GOC:mtg_apoptosis, PMID:25236395]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>202</v>
+        <v>441</v>
       </c>
       <c r="H12" t="n">
         <v>409</v>
       </c>
       <c r="I12" t="n">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="J12" t="n">
         <v>2717</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1418092909535452</v>
+        <v>0.2518337408312958</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2871287128712871</v>
+        <v>0.2335600907029478</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>['GO:0012505', 'GO:0099503']</t>
+          <t>['GO:0009987']</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'DYNLL1', 'EDN1', 'CLU', 'CAV1', 'HSPA1A', 'PYGB', 'FUCA2', 'UBR4', 'HSP90AB1', 'TIMP2', 'B4GALT1', 'CTSB', 'PRCP', 'PSMC2', 'ATP6AP2', 'B2M', 'CXCL1', 'MFGE8', 'FTL', 'LGALS3', 'GLA', 'GAL', 'HILPDA', 'SERPINE2', 'ANXA4', 'PSMD11', 'FABP5', 'APP', 'APLP2', 'CDC42', 'ILF2', 'SVIP', 'CTSL', 'CD9', 'JUP', 'COTL1', 'PYGL', 'ANXA2', 'MGST1', 'SERPINE1', 'SERPINB1', 'PSMD7', 'SKIL', 'ECE1', 'SIRPA', 'NPC2', 'FN1', 'TUBB4B', 'TMSB4X', 'PSMD1', 'COL1A1', 'PYCARD', 'HSP90AA1', 'GSTP1', 'SLC2A3']</t>
+          <t>['CTNNB1', 'ANGPTL4', 'TRIB3', 'HSPA5', 'PYCARD', 'GSTP1', 'NFKBIZ', 'HSP90AB1', 'RPL26', 'PERP', 'SOX4', 'ID3', 'SKIL', 'BCL2L1', 'SFPQ', 'BCL2A1', 'PHLDA2', 'DYNLL1', 'AKR1C3', 'ITGA6', 'EDN1', 'HMGA2', 'WNT7A', 'PYGL', 'UBB', 'NPM1', 'F2RL1', 'CCL2', 'CHCHD10', 'AIMP1', 'ANXA2', 'TNFRSF1A', 'GAPDH', 'AIFM1', 'SPHK1', 'HSP90AA1', 'PHLDA1', 'HSPB1', 'KRT18', 'TMBIM6', 'ARL6IP1', 'ADA', 'BIRC3', 'PHLDA3', 'G6PD', 'HELLS', 'ANXA1', 'SQSTM1', 'B4GALT1', 'DDX5', 'AIMP2', 'CD44', 'NEK6', 'LGALS3', 'F2R', 'APP', 'AKR1B1', 'HSPA1A', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'ST3GAL1', 'ANXA4', 'CLU', 'BLOC1S2', 'TM7SF3', 'PLK2', 'CDK1', 'AATF', 'AMIGO2', 'DHRS2', 'CTTN', 'PLK1', 'CDKN1A', 'CAV1', 'NQO1', 'SERPINE1', 'LGALS1', 'GAL', 'CCND1', 'KRT8', 'TGM2', 'CTSL', 'FGFR1', 'JUN', 'TOP2A', 'HMGB2', 'TIGAR', 'DRAM1', 'TUBA1A', 'CLCF1', 'NPTX1', 'TSC22D1', 'DNAJA1', 'ZFP36', 'CD24', 'LMNA', 'SLC7A11', 'MT3', 'CTSB', 'SFRP1', 'EMP3']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IMP'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS']]</t>
+          <t>[['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IMP', 'IGI'], ['IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'NAS'], ['IDA'], ['IDA', 'IMP'], ['IMP'], ['IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IEA'], ['IMP'], ['IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'ISS'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'TAS'], ['ISS', 'IBA'], ['IMP', 'IEA'], ['IEA'], ['NAS'], ['IEA'], ['TAS'], ['IMP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['IMP', 'IBA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['ISS'], ['IMP'], ['IEA'], ['IMP'], ['TAS', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['IMP'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['NAS'], ['IEA'], ['IMP'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA'], ['IEA'], ['IMP', 'ISS', 'IBA'], ['IDA', 'IMP'], ['IMP'], ['NAS'], ['IEA'], ['IDA', 'IEA'], ['ISS'], ['TAS'], ['IDA', 'IMP', 'IEA'], ['IDA']]</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.009123270507802535</v>
+        <v>0.01829814382123985</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1266,22 +1266,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="H13" t="n">
         <v>409</v>
       </c>
       <c r="I13" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J13" t="n">
         <v>2717</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4669926650366748</v>
+        <v>0.4694376528117359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1989583333333333</v>
+        <v>0.1971252566735113</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1295,59 +1295,59 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'CCT4', 'LDHA', 'NQO1', 'DYNLL1', 'UBB', 'HNRNPH1', 'NNMT', 'KLF6', 'KIF23', 'CLU', 'HSPA1A', 'PDLIM5', 'IL32', 'MAP1B', 'ACTB', 'HSPA5', 'RND1', 'UPF3B', 'AKR1B1', 'UBR4', 'MYL12A', 'RPL28', 'POLR2L', 'HSP90AB1', 'PSMB3', 'CTTN', 'AKR1B10', 'CALB2', 'HPGD', 'ATIC', 'RPL26', 'BCL2L1', 'CCNB1', 'KRT7', 'NUP37', 'SPDL1', 'MT2A', 'PSMC2', 'FILIP1', 'WIPI1', 'TKT', 'CCND1', 'B2M', 'PTTG1', 'RBP1', 'PGK1', 'OSBPL8', 'UBE2S', 'HMGA1', 'CKAP2L', 'FTL', 'CPLX2', 'FBXO22', 'KRT8', 'PLK2', 'HSPB1', 'LGALS3', 'LCE3D', 'AKR1C3', 'NUDT19', 'KRT18', 'HILPDA', 'PCMT1', 'RND3', 'KYNU', 'YWHAE', 'PHLDA1', 'SERPINE2', 'PSMD11', 'ALDH1A1', 'G6PD', 'MYO10', 'ALDH3A1', 'PGM2L1', 'NUCB2', 'ARHGAP29', 'FABP5', 'AIMP1', 'TXN', 'HSPA2', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'ALDH7A1', 'ODC1', 'APP', 'TUBA1A', 'NEK6', 'FGFR1', 'LMNA', 'CDC42', 'AIMP2', 'MT3', 'CDKN1A', 'AHNAK2', 'NMI', 'CXXC5', 'ILF2', 'CALD1', 'MYL6', 'CALM2', 'S100A4', 'LGALS1', 'CYB5A', 'GAPDH', 'ULK1', 'TK1', 'NPM1', 'MYL12B', 'SULT2B1', 'FHL1', 'JUP', 'TIGAR', 'LAS1L', 'TXNRD2', 'TSC22D1', 'COTL1', 'NFKB2', 'SFPQ', 'PYGL', 'TPM2', 'ADH5', 'SAT1', 'BLOC1S2', 'HSD17B11', 'TRIB3', 'ANXA2', 'ELF3', 'S100A6', 'CNN3', 'TUBA4A', 'CDK1', 'PRMT5', 'SPHK1', 'HNRNPH2', 'SRP54', 'ECH1', 'SFRP1', 'PSMD7', 'UBC', 'SPATS2', 'PSMA4', 'BIRC3', 'IL18', 'CBR1', 'TAGLN2', 'AP1M2', 'KRT19', 'PSMC6', 'RGS3', 'TSPAN15', 'AKR1C1', 'PDGFC', 'DNAJA1', 'EPAS1', 'BCCIP', 'AIFM1', 'ADA', 'ATXN10', 'TP53I3', 'VRK1', 'LACTB', 'TUBB4B', 'TMSB4X', 'CCT3', 'PSMD1', 'CDK5RAP1', 'CTNNB1', 'RAP1GAP', 'PYCARD', 'DDX5', 'GPX2', 'BCL2A1', 'VIM', 'KRT81', 'HSP90AA1', 'VPS29', 'PPP1CB', 'ZFP36', 'CDKN3', 'TPM1', 'GSTP1', 'KPNA2', 'PACSIN3', 'PTGES3', 'SQSTM1', 'PRDX1', 'PLK1']</t>
+          <t>['HSPA2', 'CXXC5', 'TXNRD2', 'CTNNB1', 'TK1', 'MYL6', 'NNMT', 'RAP1GAP', 'CCT4', 'TUBA4A', 'PSMD7', 'SPATS2', 'CDK5RAP1', 'TRIB3', 'HSPA5', 'TUBB4B', 'PYCARD', 'RPL28', 'GSTP1', 'UBR4', 'ATXN10', 'HSP90AB1', 'KYNU', 'RPL26', 'NMI', 'TXN', 'YWHAE', 'CNN3', 'S100A6', 'BCL2L1', 'SFPQ', 'UBE2C', 'FBXO22', 'LACTB', 'NFKB2', 'PRMT5', 'BCL2A1', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'EPAS1', 'LAS1L', 'KLF6', 'AKR1C3', 'HILPDA', 'PPP1CB', 'ALDH7A1', 'CPLX2', 'PYGL', 'PSMC6', 'HSD17B11', 'UBB', 'NPM1', 'NUP37', 'GPX2', 'ULK1', 'AIMP1', 'ANXA2', 'TAGLN2', 'FILIP1', 'GAPDH', 'MYL12B', 'AIFM1', 'SPHK1', 'ELF3', 'HSP90AA1', 'PHLDA1', 'HSPB1', 'KRT18', 'ARL6IP1', 'CALM2', 'SERPINE2', 'UPF3B', 'RGS3', 'FABP5', 'LCE3D', 'ADA', 'BIRC3', 'HNRNPH2', 'G6PD', 'ANXA1', 'SQSTM1', 'UBE2S', 'DDX5', 'AIMP2', 'KIF23', 'RND1', 'CD44', 'NEK6', 'PDLIM5', 'LGALS3', 'RND3', 'APP', 'PRDX1', 'AKR1B1', 'OSBPL8', 'SULT2B1', 'SAT1', 'HSPA1A', 'POLR2L', 'B2M', 'AKR1C1', 'HPGD', 'KRT81', 'ACTB', 'NUDT19', 'CDKN3', 'PDGFC', 'PACSIN3', 'CLU', 'AP1M2', 'FTL', 'BLOC1S2', 'ATIC', 'AKR1B10', 'PSMB3', 'PSMC2', 'VRK1', 'PLK2', 'CDK1', 'MYO10', 'IL18', 'SRP54', 'TPM1', 'CTTN', 'WIPI1', 'PLK1', 'TSPAN15', 'ODC1', 'HMGA1', 'NUCB2', 'CDC42', 'ARHGAP29', 'TMSB4X', 'CDKN1A', 'PCMT1', 'MYL12A', 'NQO1', 'KRT19', 'VIM', 'PGK1', 'LGALS1', 'CCND1', 'TKT', 'ALDH1A1', 'KRT8', 'AHNAK2', 'TGM2', 'PSMD11', 'CKAP2L', 'CBR1', 'KRT7', 'S100A4', 'FGFR1', 'VPS29', 'ILF2', 'RBP1', 'TIGAR', 'PTGES3', 'MT2A', 'PTTG1', 'CCT3', 'TUBA1A', 'SPDL1', 'FHL1', 'INO80C', 'PSMD1', 'TSC22D1', 'TP53I3', 'DNAJA1', 'CALD1', 'ZFP36', 'IL32', 'PSMA4', 'TPM2', 'COTL1', 'LMNA', 'UBC', 'CYB5A', 'MT3', 'BCCIP', 'PGM2L1', 'LDHB', 'CALB2', 'ALDH3A1', 'ECH1', 'JUP', 'MAP1B', 'HNRNPH1', 'SFRP1', 'KPNA2']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['IDA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA'], ['TAS'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IBA'], ['IBA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['IDA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS']]</t>
+          <t>[['IDA', 'IBA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IEA'], ['IDA'], ['IBA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['IDA', 'ISS', 'TAS'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'NAS']]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GO:0031398</t>
+          <t>GO:0031410</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>positive regulation of protein ubiquitination</t>
+          <t>cytoplasmic vesicle</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.009774875821631565</v>
+        <v>0.020732824508474</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"Any process that activates or increases the frequency, rate or extent of the addition of ubiquitin groups to a protein." [GOC:mah]</t>
+          <t>"A vesicle found in the cytoplasm of a cell." [GOC:ai, GOC:mah, GOC:vesicles]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19</v>
+        <v>439</v>
       </c>
       <c r="H14" t="n">
         <v>409</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="J14" t="n">
         <v>2717</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03178484107579462</v>
+        <v>0.2493887530562347</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.2323462414578588</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1356,64 +1356,64 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['GO:0016567', 'GO:0031396', 'GO:1903322']</t>
+          <t>['GO:0005737', 'GO:0097708']</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['UBB', 'CAV1', 'RASSF1', 'DERL1', 'HSPA5', 'UBE2S', 'UBE2C', 'AIMP2', 'NMI', 'TRIB3', 'SPHK1', 'BIRC3', 'PLK1']</t>
+          <t>['ITM2B', 'CCT4', 'PSMD7', 'MFGE8', 'HSPA5', 'TUBB4B', 'PYCARD', 'GSTP1', 'UBR4', 'MYOF', 'HSP90AB1', 'PYGB', 'YWHAE', 'MGST1', 'SIRPA', 'OCIAD2', 'NAP1L1', 'SKIL', 'BCL2L1', 'SLC2A3', 'GLA', 'CD9', 'DYNLL1', 'LMAN1', 'PTP4A1', 'PRCP', 'HILPDA', 'APLP2', 'COL1A1', 'EDN1', 'WNT7A', 'PYGL', 'SERPINB1', 'ANTXR1', 'UBB', 'F2RL1', 'ULK1', 'ANXA2', 'PMEPA1', 'DERL1', 'SPHK1', 'AREG', 'HSP90AA1', 'LAPTM4A', 'PHLDA1', 'SERPINE2', 'FABP5', 'ADA', 'SLC3A2', 'CAPG', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'CD44', 'LGALS3', 'NTS', 'F2R', 'APP', 'PRDX1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'BDNF', 'RAB3B', 'ANXA4', 'PACSIN3', 'CLU', 'AP1M2', 'FTL', 'PSMC2', 'CTTN', 'WIPI1', 'TSPAN15', 'CDC42', 'TMSB4X', 'CAV1', 'SERPINE1', 'VIM', 'DNER', 'GAL', 'PSMD11', 'CTSL', 'FGFR1', 'VPS29', 'ILF2', 'FUCA2', 'TUBA1A', 'NPTX1', 'PSMD1', 'CXCL1', 'ANXA3', 'NPC2', 'CD63', 'COTL1', 'UBC', 'MT3', 'TIMP2', 'CTSB', 'ECE1', 'JUP']</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP'], ['IMP'], ['IDA'], ['IDA'], ['IEA'], ['IDA'], ['TAS'], ['IEA'], ['IEA'], ['ISS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP']]</t>
+          <t>[['IDA', 'IEA'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP'], ['TAS'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IBA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS']]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GO:0012501</t>
+          <t>GO:0097708</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>programmed cell death</t>
+          <t>intracellular vesicle</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01411710920803737</v>
+        <v>0.02343187960421831</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>"A process which begins when a cell receives an internal or external signal and activates a series of biochemical events (signaling pathway). The process ends with the death of the cell." [GOC:lr, GOC:mtg_apoptosis]</t>
+          <t>"Any vesicle that is part of the intracellular region." [GOC:vesicles]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H15" t="n">
         <v>409</v>
       </c>
       <c r="I15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J15" t="n">
         <v>2717</v>
       </c>
       <c r="K15" t="n">
-        <v>0.254278728606357</v>
+        <v>0.2493887530562347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.232662192393736</v>
+        <v>0.2318181818181818</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1422,64 +1422,64 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>['GO:0008219']</t>
+          <t>['GO:0031982', 'GO:0043231']</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'NQO1', 'DYNLL1', 'EDN1', 'UBB', 'CLU', 'CAV1', 'CCL2', 'HSPA1A', 'JUN', 'TOP2A', 'NFKBIZ', 'AATF', 'ACTB', 'HSPA5', 'CHCHD10', 'AKR1B1', 'TMBIM6', 'EMP3', 'ID3', 'HSP90AB1', 'DRAM1', 'CTTN', 'IGFBP3', 'B4GALT1', 'CTSB', 'CLCF1', 'HPGD', 'ITGA6', 'RPL26', 'BCL2L1', 'CCND1', 'CD24', 'KRT8', 'PLK2', 'HSPB1', 'LGALS3', 'AKR1C3', 'GAL', 'KRT18', 'F2RL1', 'DHRS2', 'PHLDA1', 'ANXA4', 'G6PD', 'PERP', 'SLC7A11', 'ANGPTL4', 'AIMP1', 'ANXA1', 'ARL6IP1', 'TGM2', 'APP', 'PHLDA2', 'TUBA1A', 'NEK6', 'FGFR1', 'LMNA', 'CDC42', 'AIMP2', 'MT3', 'CDKN1A', 'HELLS', 'LGALS1', 'CTSL', 'GAPDH', 'NPM1', 'TIGAR', 'TSC22D1', 'BDNF', 'SFPQ', 'PYGL', 'NPTX1', 'BLOC1S2', 'TRIB3', 'ANXA2', 'HMGA2', 'CDK1', 'SERPINE1', 'SPHK1', 'SFRP1', 'SKIL', 'HMGB2', 'BIRC3', 'F2R', 'TNFRSF1A', 'DNAJA1', 'AMIGO2', 'AIFM1', 'ADA', 'CTNNB1', 'PYCARD', 'DDX5', 'BCL2A1', 'HSP90AA1', 'ST3GAL1', 'ZFP36', 'WNT7A', 'SOX4', 'GSTP1', 'PHLDA3', 'SQSTM1', 'PLK1']</t>
+          <t>['ITM2B', 'CCT4', 'PSMD7', 'MFGE8', 'HSPA5', 'TUBB4B', 'PYCARD', 'GSTP1', 'UBR4', 'MYOF', 'HSP90AB1', 'PYGB', 'YWHAE', 'MGST1', 'SIRPA', 'OCIAD2', 'NAP1L1', 'SKIL', 'BCL2L1', 'SLC2A3', 'GLA', 'CD9', 'DYNLL1', 'LMAN1', 'PTP4A1', 'PRCP', 'HILPDA', 'APLP2', 'COL1A1', 'EDN1', 'WNT7A', 'PYGL', 'SERPINB1', 'ANTXR1', 'UBB', 'F2RL1', 'ULK1', 'ANXA2', 'PMEPA1', 'DERL1', 'SPHK1', 'AREG', 'HSP90AA1', 'LAPTM4A', 'PHLDA1', 'SERPINE2', 'FABP5', 'ADA', 'SLC3A2', 'CAPG', 'ANXA1', 'SQSTM1', 'ATP6AP2', 'B4GALT1', 'CD44', 'LGALS3', 'NTS', 'F2R', 'APP', 'PRDX1', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'BDNF', 'RAB3B', 'ANXA4', 'PACSIN3', 'CLU', 'AP1M2', 'FTL', 'PSMC2', 'CTTN', 'WIPI1', 'TSPAN15', 'CDC42', 'TMSB4X', 'CAV1', 'SERPINE1', 'VIM', 'DNER', 'GAL', 'PSMD11', 'CTSL', 'FGFR1', 'VPS29', 'ILF2', 'FUCA2', 'TUBA1A', 'NPTX1', 'PSMD1', 'CXCL1', 'ANXA3', 'NPC2', 'CD63', 'COTL1', 'UBC', 'MT3', 'TIMP2', 'CTSB', 'ECE1', 'JUP']</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP'], ['IMP', 'IBA'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IDA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'TAS'], ['IMP'], ['IDA', 'IBA'], ['IEA'], ['IEA'], ['NAS'], ['IMP', 'TAS'], ['IMP'], ['IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IMP', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['IMP', 'IGI'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['NAS'], ['IEA'], ['ISS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IMP'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['ISS', 'IEA'], ['IDA', 'NAS'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IBA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP'], ['ISS'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IMP'], ['IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IMP']]</t>
+          <t>[['IDA', 'IEA'], ['IEA'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP'], ['TAS'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IBA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS']]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GO:0008219</t>
+          <t>GO:0030141</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cell death</t>
+          <t>secretory granule</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0159678886959841</v>
+        <v>0.02435239938412499</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>"Any biological process that results in permanent cessation of all vital functions of a cell. A cell should be considered dead when any one of the following molecular or morphological criteria is met: (1) the cell has lost the integrity of its plasma membrane; (2) the cell, including its nucleus, has undergone complete fragmentation into discrete bodies (frequently referred to as apoptotic bodies). The cell corpse (or its fragments) may be engulfed by an adjacent cell in vivo, but engulfment of whole cells should not be considered a strict criteria to define cell death as, under some circumstances, live engulfed cells can be released from phagosomes (see PMID:18045538)." [GOC:mah, GOC:mtg_apoptosis, PMID:25236395]</t>
+          <t>"A small subcellular vesicle, surrounded by a membrane, that is formed from the Golgi apparatus and contains a highly concentrated protein destined for secretion. Secretory granules move towards the periphery of the cell and upon stimulation, their membranes fuse with the cell membrane, and their protein load is exteriorized. Processing of the contained protein may take place in secretory granules." [GOC:mah, ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>448</v>
+        <v>203</v>
       </c>
       <c r="H16" t="n">
         <v>409</v>
       </c>
       <c r="I16" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="J16" t="n">
         <v>2717</v>
       </c>
       <c r="K16" t="n">
-        <v>0.254278728606357</v>
+        <v>0.1393643031784841</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.2807881773399015</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1488,17 +1488,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>['GO:0009987']</t>
+          <t>['GO:0012505', 'GO:0099503']</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'NQO1', 'DYNLL1', 'EDN1', 'UBB', 'CLU', 'CAV1', 'CCL2', 'HSPA1A', 'JUN', 'TOP2A', 'NFKBIZ', 'AATF', 'ACTB', 'HSPA5', 'CHCHD10', 'AKR1B1', 'TMBIM6', 'EMP3', 'ID3', 'HSP90AB1', 'DRAM1', 'CTTN', 'IGFBP3', 'B4GALT1', 'CTSB', 'CLCF1', 'HPGD', 'ITGA6', 'RPL26', 'BCL2L1', 'CCND1', 'CD24', 'KRT8', 'PLK2', 'HSPB1', 'LGALS3', 'AKR1C3', 'GAL', 'KRT18', 'F2RL1', 'DHRS2', 'PHLDA1', 'ANXA4', 'G6PD', 'PERP', 'SLC7A11', 'ANGPTL4', 'AIMP1', 'ANXA1', 'ARL6IP1', 'TGM2', 'APP', 'PHLDA2', 'TUBA1A', 'NEK6', 'FGFR1', 'LMNA', 'CDC42', 'AIMP2', 'MT3', 'CDKN1A', 'HELLS', 'LGALS1', 'CTSL', 'GAPDH', 'NPM1', 'TIGAR', 'TSC22D1', 'BDNF', 'SFPQ', 'PYGL', 'NPTX1', 'BLOC1S2', 'TRIB3', 'ANXA2', 'HMGA2', 'CDK1', 'SERPINE1', 'SPHK1', 'SFRP1', 'SKIL', 'HMGB2', 'BIRC3', 'F2R', 'TNFRSF1A', 'DNAJA1', 'AMIGO2', 'AIFM1', 'ADA', 'CTNNB1', 'PYCARD', 'DDX5', 'BCL2A1', 'HSP90AA1', 'ST3GAL1', 'ZFP36', 'WNT7A', 'SOX4', 'GSTP1', 'PHLDA3', 'SQSTM1', 'PLK1']</t>
+          <t>['PSMD7', 'MFGE8', 'TUBB4B', 'PYCARD', 'GSTP1', 'UBR4', 'HSP90AB1', 'PYGB', 'MGST1', 'SIRPA', 'SKIL', 'SLC2A3', 'GLA', 'CD9', 'DYNLL1', 'PRCP', 'HILPDA', 'APLP2', 'COL1A1', 'EDN1', 'PYGL', 'SERPINB1', 'ANXA2', 'HSP90AA1', 'SERPINE2', 'FABP5', 'ATP6AP2', 'B4GALT1', 'CD44', 'LGALS3', 'APP', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'ANXA4', 'CLU', 'FTL', 'PSMC2', 'TMSB4X', 'CAV1', 'SERPINE1', 'GAL', 'PSMD11', 'CTSL', 'ILF2', 'FUCA2', 'PSMD1', 'CXCL1', 'ANXA3', 'NPC2', 'CD63', 'COTL1', 'TIMP2', 'CTSB', 'ECE1', 'JUP']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP'], ['IMP', 'IBA'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IDA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'TAS'], ['IMP'], ['IDA', 'IBA'], ['IEA'], ['IEA'], ['NAS'], ['IMP', 'TAS'], ['IMP'], ['IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IMP', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['IEA'], ['IMP', 'IGI'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['NAS'], ['IEA'], ['ISS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IMP'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['ISS', 'IEA'], ['IDA', 'NAS'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IBA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP'], ['ISS'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IMP'], ['IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IMP']]</t>
+          <t>[['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IMP'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS']]</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01786641684447991</v>
+        <v>0.04932106970719956</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -1530,22 +1530,22 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H17" t="n">
         <v>409</v>
       </c>
       <c r="I17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J17" t="n">
         <v>2717</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1540342298288508</v>
+        <v>0.1515892420537897</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2672413793103448</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'DYNLL1', 'EDN1', 'CLU', 'CAV1', 'HSPA1A', 'PYGB', 'FUCA2', 'UBR4', 'HSP90AB1', 'TIMP2', 'B4GALT1', 'CTSB', 'BCL2L1', 'PRCP', 'PSMC2', 'ATP6AP2', 'B2M', 'CXCL1', 'MFGE8', 'FTL', 'LGALS3', 'GLA', 'GAL', 'HILPDA', 'SERPINE2', 'ANXA4', 'PSMD11', 'MYOF', 'FABP5', 'APP', 'APLP2', 'CDC42', 'MT3', 'ILF2', 'SVIP', 'CTSL', 'CD9', 'JUP', 'COTL1', 'BDNF', 'PYGL', 'ANXA2', 'MGST1', 'SERPINE1', 'SERPINB1', 'PSMD7', 'SKIL', 'ECE1', 'SIRPA', 'NPC2', 'FN1', 'TUBB4B', 'TMSB4X', 'PSMD1', 'COL1A1', 'PYCARD', 'HSP90AA1', 'RAB3B', 'GSTP1', 'SLC2A3']</t>
+          <t>['PSMD7', 'MFGE8', 'TUBB4B', 'PYCARD', 'GSTP1', 'UBR4', 'MYOF', 'HSP90AB1', 'PYGB', 'MGST1', 'SIRPA', 'SKIL', 'BCL2L1', 'SLC2A3', 'GLA', 'CD9', 'DYNLL1', 'PRCP', 'HILPDA', 'APLP2', 'COL1A1', 'EDN1', 'PYGL', 'SERPINB1', 'ANXA2', 'HSP90AA1', 'SERPINE2', 'FABP5', 'ATP6AP2', 'B4GALT1', 'CD44', 'LGALS3', 'APP', 'SVIP', 'FN1', 'HSPA1A', 'B2M', 'BDNF', 'RAB3B', 'ANXA4', 'CLU', 'FTL', 'PSMC2', 'TMSB4X', 'CAV1', 'SERPINE1', 'GAL', 'PSMD11', 'CTSL', 'ILF2', 'FUCA2', 'PSMD1', 'CXCL1', 'ANXA3', 'NPC2', 'CD63', 'COTL1', 'MT3', 'TIMP2', 'CTSB', 'ECE1', 'JUP']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IMP'], ['IEA'], ['TAS'], ['IBA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA', 'IMP', 'IBA'], ['TAS'], ['TAS']]</t>
+          <t>[['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IMP'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS']]</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.263196102740603e-14</v>
+        <v>2.864244082801096e-14</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1695,7 +1695,7 @@
         <v>465</v>
       </c>
       <c r="H2" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I2" t="n">
         <v>153</v>
@@ -1704,7 +1704,7 @@
         <v>2717</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3194154488517745</v>
+        <v>0.31875</v>
       </c>
       <c r="L2" t="n">
         <v>0.3290322580645161</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'LDHA', 'PTGR1', 'PGD', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'GLRX', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'F12', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'HSP90AB1', 'PLOD2', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'HSPD1', 'RPL26', 'KRT7', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PGK1', 'CCT2', 'ATP1B1', 'FTL', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'KRT18', 'YWHAE', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'STMN1', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'ARPC3', 'ADH5', 'ANXA2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'RSU1', 'UBC', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PDGFC', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'CCT3', 'PTPRJ', 'CTNNB1', 'SFN', 'VIM', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'HSPD1', 'TUBA4A', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'NT5E', 'ATP1B1', 'AKR1C3', 'APLP2', 'PPP1CB', 'FLOT1', 'UBB', 'FLNB', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'GAPDH', 'MYL12B', 'PRSS23', 'F12', 'IGFBP7', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'STMN1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'HPGD', 'ACTB', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'CCT5', 'CCT3', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'HSP90B1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'LDHB', 'ECH1', 'JUP', 'PLOD2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.247259661300412e-14</v>
+        <v>5.375136797758984e-14</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>472</v>
       </c>
       <c r="H3" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I3" t="n">
         <v>154</v>
@@ -1770,7 +1770,7 @@
         <v>2717</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3215031315240083</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="L3" t="n">
         <v>0.326271186440678</v>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'LDHA', 'PTGR1', 'PGD', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'GLRX', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'F12', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'HSP90AB1', 'PLOD2', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'HSPD1', 'RPL26', 'KRT7', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PGK1', 'CCT2', 'ATP1B1', 'FTL', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'KRT18', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'STMN1', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'ARPC3', 'ADH5', 'ANXA2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'RSU1', 'UBC', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PDGFC', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'CCT3', 'PTPRJ', 'CTNNB1', 'SFN', 'VIM', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'HSPD1', 'TUBA4A', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'NT5E', 'ATP1B1', 'AKR1C3', 'APLP2', 'PPP1CB', 'FLOT1', 'UBB', 'FLNB', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'GAPDH', 'MYL12B', 'PRSS23', 'F12', 'IGFBP7', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'STMN1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'HPGD', 'ACTB', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'CCT5', 'CCT3', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'HSP90B1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'LDHB', 'ECH1', 'JUP', 'PLOD2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.396292516247356e-14</v>
+        <v>6.825814636962582e-14</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1827,7 +1827,7 @@
         <v>473</v>
       </c>
       <c r="H4" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I4" t="n">
         <v>154</v>
@@ -1836,7 +1836,7 @@
         <v>2717</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3215031315240083</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="L4" t="n">
         <v>0.3255813953488372</v>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'LDHA', 'PTGR1', 'PGD', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'GLRX', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'F12', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'HSP90AB1', 'PLOD2', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'HSPD1', 'RPL26', 'KRT7', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PGK1', 'CCT2', 'ATP1B1', 'FTL', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'KRT18', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'STMN1', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'ARPC3', 'ADH5', 'ANXA2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'RSU1', 'UBC', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PDGFC', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'CCT3', 'PTPRJ', 'CTNNB1', 'SFN', 'VIM', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'HSPD1', 'TUBA4A', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'NT5E', 'ATP1B1', 'AKR1C3', 'APLP2', 'PPP1CB', 'FLOT1', 'UBB', 'FLNB', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'GAPDH', 'MYL12B', 'PRSS23', 'F12', 'IGFBP7', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'STMN1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'HPGD', 'ACTB', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'CCT5', 'CCT3', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'HSP90B1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'LDHB', 'ECH1', 'JUP', 'PLOD2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.396292516247356e-14</v>
+        <v>6.825814636962582e-14</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1893,7 +1893,7 @@
         <v>473</v>
       </c>
       <c r="H5" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I5" t="n">
         <v>154</v>
@@ -1902,7 +1902,7 @@
         <v>2717</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3215031315240083</v>
+        <v>0.3208333333333334</v>
       </c>
       <c r="L5" t="n">
         <v>0.3255813953488372</v>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'LDHA', 'PTGR1', 'PGD', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'HSPA1A', 'GLRX', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'F12', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'HSP90AB1', 'PLOD2', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'HSPD1', 'RPL26', 'KRT7', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PGK1', 'CCT2', 'ATP1B1', 'FTL', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'KRT18', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'STMN1', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'ARPC3', 'ADH5', 'ANXA2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'RSU1', 'UBC', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'PDGFC', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'CCT3', 'PTPRJ', 'CTNNB1', 'SFN', 'VIM', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'HSPD1', 'TUBA4A', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'NT5E', 'ATP1B1', 'AKR1C3', 'APLP2', 'PPP1CB', 'FLOT1', 'UBB', 'FLNB', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'GAPDH', 'MYL12B', 'PRSS23', 'F12', 'IGFBP7', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'STMN1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'HPGD', 'ACTB', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'CCT5', 'CCT3', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'HSP90B1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'LDHB', 'ECH1', 'JUP', 'PLOD2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.012359712615224e-12</v>
+        <v>3.660694740538852e-13</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H6" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J6" t="n">
         <v>2717</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4154488517745303</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2859195402298851</v>
+        <v>0.2881844380403458</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['OLFM2', 'CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'SPOCK1', 'LDHA', 'LAMC2', 'PTGR1', 'EDN1', 'PGD', 'ACTG1', 'UBB', 'GNL3', 'SDC4', 'CLU', 'HSPA1A', 'CCL2', 'IL32', 'GLRX', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'EREG', 'F12', 'CSRP1', 'SLC3A2', 'GNG4', 'DMKN', 'S100A11', 'CXCL5', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'TFPI2', 'HSP90AB1', 'PLOD2', 'IGFBP3', 'TIMP2', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'FIBCD1', 'HSPD1', 'RPL26', 'KRT7', 'PSME2', 'COL4A1', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'ATP1B1', 'FTL', 'CMTM3', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'NRG1', 'GAL', 'KRT18', 'MTHFD2', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'ALDH3A1', 'STMN1', 'FABP5', 'AREG', 'TXN', 'ANGPTL4', 'HMGB1', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'NMI', 'RAET1G', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'BDNF', 'ARPC3', 'ADH5', 'ANXA2', 'COL5A2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'SERPINE1', 'PVR', 'ECH1', 'RSU1', 'UBC', 'HMGB2', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'TNFRSF1A', 'PRSS3', 'PDGFC', 'VCAN', 'NPC2', 'FN1', 'RDX', 'IGFBP6', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'PSMA5', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'SFN', 'AGR2', 'VIM', 'KRT81', 'HEXA', 'HSP90AA1', 'GSN', 'CXCL8', 'TUBB2A', 'PPP1CB', 'STC1', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'HBEGF', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'FSTL3', 'ANGPTL4', 'HSPD1', 'TUBA4A', 'CMTM3', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'NMI', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'IL11', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'DMKN', 'NT5E', 'ATP1B1', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'PRSS3', 'LAMC2', 'UBB', 'CCL2', 'FLNB', 'COL5A2', 'NRG1', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'TNFRSF1A', 'PCSK1N', 'GAPDH', 'MYL12B', 'IGFBP6', 'PRSS23', 'F12', 'IGFBP7', 'AREG', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'CXCL5', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'TNFAIP6', 'STMN1', 'HMGB1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TFPI2', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'AGR2', 'HBEGF', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'KRT81', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'FIBCD1', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'SPOCK1', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'CCT5', 'PVR', 'HMGB2', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'CXCL1', 'HSP90B1', 'ANXA3', 'MTHFD2', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'RAET1G', 'LDHB', 'TIMP2', 'IGFBP4', 'ALDH3A1', 'ECH1', 'JUP', 'PLOD2', 'COL4A1', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IBA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'IBA'], ['IMP', 'HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'ISS'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['IBA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IBA'], ['HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.133831928302618e-10</v>
+        <v>1.067895844030228e-10</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="H7" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J7" t="n">
         <v>2717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4196242171189979</v>
+        <v>0.4208333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2745901639344263</v>
+        <v>0.2748299319727891</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'LDHA', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'PGD', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'HSPA1A', 'GLRX', 'NAP1L1', 'DERL1', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'HSPA5', 'EREG', 'F12', 'TSPAN4', 'SCG5', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'HSP90AB1', 'PLOD2', 'CTTN', 'TIMP2', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'HSPD1', 'GRAMD1A', 'RPL26', 'KRT7', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'ATP1B1', 'FTL', 'CMTM3', 'DNER', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'EIF2S1', 'RHOU', 'GAL', 'CYBA', 'KRT18', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'G6PD', 'PRNP', 'MYOF', 'STMN1', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'FGFR1', 'AXL', 'CDC42', 'FH', 'KCNN4', 'SH3BGRL3', 'PDCD5', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'LTBP3', 'RIN2', 'COPB1', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'BDNF', 'ARPC3', 'NPTX1', 'ADH5', 'ANXA2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'MGST1', 'SERPINE1', 'CDA', 'ECH1', 'RSU1', 'UBC', 'PSMA4', 'CBR1', 'TAGLN2', 'AP1M2', 'TUBA1C', 'KRT19', 'CAPG', 'TSPAN15', 'PRSS3', 'PDGFC', 'SYT1', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'PSMA5', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'PYCARD', 'SFN', 'VIM', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'HBEGF', 'SQSTM1', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'RHOU', 'MYL6', 'HSPD1', 'CDA', 'TUBA4A', 'CMTM3', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'PYCARD', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'RPL26', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'RIN2', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'NAP1L1', 'SLC2A3', 'PSMD2', 'TSPAN4', 'GLRX', 'RDX', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'DYNLL1', 'ADH5', 'CSRP1', 'IFITM2', 'NT5E', 'ATP1B1', 'AKR1C3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'ANTXR1', 'UBB', 'FLNB', 'ULK1', 'AXL', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'PCSK1N', 'GAPDH', 'MYL12B', 'DERL1', 'PRSS23', 'F12', 'IGFBP7', 'AREG', 'S100A16', 'HSP90AA1', 'COPB1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'CALM2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'PLAUR', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'TNFAIP6', 'CYBA', 'STMN1', 'HMGB1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'SYT1', 'LTBP3', 'FN1', 'HSPA1A', 'HBEGF', 'BDNF', 'DSE', 'HPGD', 'ACTB', 'SH3BGRL3', 'TUBA1C', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'AP1M2', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'TM7SF3', 'CDK1', 'TMEM59', 'CTTN', 'TSPAN15', 'S100A10', 'CDC42', 'TMSB4X', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'DNER', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'FGFR1', 'SCG5', 'CCT5', 'GRAMD1A', 'CCT3', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'MAP1LC3A', 'CXCL1', 'HSP90B1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'COTL1', 'PTGR1', 'NME1', 'UBC', 'RSU1', 'LDHB', 'TIMP2', 'ECH1', 'JUP', 'PLOD2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['TAS'], ['HDA'], ['IDA'], ['ISS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['IBA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IEA'], ['TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['TAS'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA'], ['HDA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['TAS'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IBA'], ['HDA'], ['HDA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'TAS'], ['TAS'], ['IBA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['ISS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['TAS'], ['IEA'], ['TAS'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.107278590104843e-10</v>
+        <v>1.730839271470884e-10</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="H8" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I8" t="n">
         <v>216</v>
@@ -2100,10 +2100,10 @@
         <v>2717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4509394572025052</v>
+        <v>0.45</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2663378545006165</v>
+        <v>0.2673267326732673</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['OLFM2', 'CD44', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'SPOCK1', 'LDHA', 'LAMC2', 'PTGR1', 'EDN1', 'PGD', 'ACTG1', 'UBB', 'GNL3', 'SDC4', 'CLU', 'PLAUR', 'HSPA1A', 'CCL2', 'IL32', 'CCDC80', 'GLRX', 'RSPO3', 'TMEM59', 'ACTB', 'RAN', 'HSPA5', 'EREG', 'F12', 'SCG5', 'CSRP1', 'SLC3A2', 'GNG4', 'DMKN', 'S100A11', 'CXCL5', 'ANPEP', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'RPL28', 'HLA-C', 'SEMA3C', 'MTHFD1', 'ENO1', 'TFPI2', 'HSP90AB1', 'PLOD2', 'IGFBP3', 'TIMP2', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'HSP90B1', 'HPGD', 'FIBCD1', 'HSPD1', 'RPL26', 'KRT7', 'NRP2', 'PSME2', 'COL4A1', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'ATP1B1', 'FTL', 'CMTM3', 'S100A10', 'KRT8', 'PRSS23', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'SDC1', 'AKR1C3', 'C1orf56', 'EIF2S1', 'NRG1', 'GAL', 'KRT18', 'MTHFD2', 'YWHAE', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'G6PD', 'PRNP', 'MYOF', 'ALDH3A1', 'STMN1', 'FABP5', 'AREG', 'TXN', 'ANGPTL4', 'HMGB1', 'HSPA2', 'ANXA1', 'TGM2', 'VTN', 'SLC26A2', 'FSCN1', 'NTN4', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'FGFR1', 'AXL', 'CDC42', 'FH', 'SH3BGRL3', 'PDCD5', 'NMI', 'RAET1G', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'SULT2B1', 'MYL12B', 'JUP', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'PSMB1', 'COTL1', 'PSMD2', 'BDNF', 'ARPC3', 'NPTX1', 'ADH5', 'ANXA2', 'COL5A2', 'S100A6', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'GALNT1', 'SERPINE1', 'CDA', 'PVR', 'ECH1', 'RSU1', 'UBC', 'HMGB2', 'PSMA4', 'CBR1', 'TAGLN2', 'KRT19', 'CAPG', 'TNFRSF1A', 'PRSS3', 'PDGFC', 'VCAN', 'NPC2', 'FN1', 'RDX', 'IGFBP6', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'IL11', 'PSMA5', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'PYCARD', 'SFN', 'AGR2', 'VIM', 'KRT81', 'HEXA', 'HSP90AA1', 'GSN', 'CXCL8', 'TUBB2A', 'PPP1CB', 'STC1', 'RAB3B', 'COL4A2', 'BLVRA', 'GSTP1', 'PACSIN3', 'SLC2A3', 'HBEGF', 'SQSTM1', 'C1QBP', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'MTHFD1', 'CTNNB1', 'MYL6', 'FSTL3', 'ANGPTL4', 'HSPD1', 'CDA', 'TUBA4A', 'CMTM3', 'FSCN1', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'PYCARD', 'RPL28', 'ARPC3', 'GSTP1', 'MYOF', 'GALNT1', 'RPL26', 'NMI', 'C1orf56', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'HLA-C', 'YWHAE', 'FH', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'IL11', 'RBP4', 'RHOF', 'CD9', 'LDHA', 'ADH5', 'CSRP1', 'DMKN', 'NT5E', 'ATP1B1', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'PRSS3', 'LAMC2', 'UBB', 'CCL2', 'FLNB', 'COL5A2', 'NRG1', 'AXL', 'TAGLN2', 'ANXA2', 'EIF2S1', 'TNFRSF1A', 'PCSK1N', 'GAPDH', 'MYL12B', 'IGFBP6', 'PRSS23', 'F12', 'IGFBP7', 'AREG', 'S100A16', 'HSP90AA1', 'TUBB2A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'PLAUR', 'CXCL5', 'G6PD', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'EPHB2', 'TNFAIP6', 'STMN1', 'HMGB1', 'CD44', 'ENO3', 'COL4A2', 'SRSF7', 'TFPI2', 'TXNRD1', 'PRDX1', 'BAX', 'AKR1B1', 'TGFBI', 'SULT2B1', 'SVIP', 'LTBP3', 'FN1', 'HSPA1A', 'AGR2', 'HBEGF', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'KRT81', 'SH3BGRL3', 'RAB3B', 'ITGA3', 'ANXA4', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'FIBCD1', 'PKM', 'HEXA', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'AKR1B10', 'TM7SF3', 'CDK1', 'TMEM59', 'S100A10', 'CDC42', 'TMSB4X', 'SPOCK1', 'PGD', 'VTN', 'MYL12A', 'PSME2', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'KRT8', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'SLC26A2', 'PTPRJ', 'FGFR1', 'SCG5', 'CCT5', 'PVR', 'HMGB2', 'CCT3', 'NRP2', 'VCAN', 'PDCD5', 'TUBA1A', 'TUBB', 'EIF2S3', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'CXCL1', 'HSP90B1', 'ANXA3', 'MTHFD2', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'CD63', 'COTL1', 'C1QBP', 'PTGR1', 'NTN4', 'NME1', 'UBC', 'RSU1', 'RAET1G', 'CCDC80', 'LDHB', 'TIMP2', 'IGFBP4', 'ALDH3A1', 'ECH1', 'JUP', 'PLOD2', 'COL4A1', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IBA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA', 'IBA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['NAS'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['TAS'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['NAS'], ['IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA', 'IBA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.365704372556127e-06</v>
+        <v>2.759234653648711e-06</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -2154,22 +2154,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="H9" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I9" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J9" t="n">
         <v>2717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4864300626304802</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2427083333333333</v>
+        <v>0.2412731006160164</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2183,59 +2183,59 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['TXNDC9', 'CD44', 'LDHB', 'LDHA', 'NQO1', 'DYNLL1', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'NNMT', 'IER3', 'CLU', 'PDLIM5', 'HSPA1A', 'IL32', 'GLRX', 'MAP1B', 'ACTB', 'RAN', 'MAP1LC3A', 'PPP1R14A', 'RND1', 'HSPA5', 'CTPS1', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'PSMD8', 'MTHFD1', 'ENO1', 'NUDC', 'TNS3', 'POLR2L', 'HSP90AB1', 'CTTN', 'AKR1B10', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'HSPD1', 'GRAMD1A', 'S100A3', 'RPL26', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'PKM', 'TKT', 'S100A16', 'PTTG1', 'NUP93', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'FTL', 'CPLX2', 'CMTM3', 'MGLL', 'KRT8', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'LCE3D', 'AKR1C3', 'CES1', 'EIF2S1', 'RHOU', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'KYNU', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'ENO3', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'PGM2L1', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'ARHGAP29', 'FABP5', 'TXN', 'HSPA2', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'AJUBA', 'FSCN1', 'FBXO2', 'TUBA1A', 'FLNB', 'RHOF', 'FGFR1', 'GPX1', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SH3BGRL3', 'PDCD5', 'AHNAK2', 'NMI', 'RASSF10', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'CYB5A', 'GAPDH', 'ULK1', 'PSMC4', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'COPB1', 'SULT2B1', 'MYL12B', 'PPP3CA', 'CDC20', 'ILK', 'JUP', 'ARHGAP11A', 'MAP2K3', 'GSTO1', 'NME1', 'TXNRD1', 'TXNRD2', 'PSMB1', 'COTL1', 'PSMD2', 'ARPC3', 'SFPQ', 'TPM2', 'UBXN4', 'SAT1', 'ADH5', 'TRIB3', 'BLOC1S2', 'ANXA2', 'ATF4', 'ELF3', 'S100A6', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'ECH1', 'RSU1', 'PRC1', 'UBC', 'NEMF', 'PSMA4', 'ETS2', 'CBR1', 'TAGLN2', 'PHKG1', 'AP1M2', 'KRT19', 'RGS3', 'SRGAP1', 'TSPAN15', 'PDGFC', 'SYT1', 'TP53I3', 'EIF2S3', 'TUBB4B', 'TMSB4X', 'PSMA5', 'PSMD1', 'CCT3', 'CTNNB1', 'HNRNPD', 'PYCARD', 'SFN', 'THRA', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'KRT81', 'HEXA', 'HSP90AA1', 'GSN', 'PPP1CB', 'LIMD2', 'ARL4A', 'UPP1', 'BCL3', 'CDKN3', 'BLVRA', 'TPM1', 'GSTP1', 'AURKB', 'PACSIN3', 'KPNA2', 'CENPA', 'CDCA4', 'SQSTM1', 'C1QBP', 'AP2M1', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'TXNRD2', 'MTHFD1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'NNMT', 'HSPD1', 'CDA', 'CDK6', 'TUBA4A', 'CMTM3', 'TRIB3', 'FSCN1', 'TNS3', 'HSPA5', 'GSN', 'TUBB4B', 'PYCARD', 'RPL28', 'CES1', 'DLGAP5', 'ARPC3', 'GSTP1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'HSP90AB1', 'TXN', 'PSMB1', 'ENO1', 'YWHAE', 'RIN2', 'CNN3', 'FH', 'S100A6', 'PSMD2', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'CENPA', 'RHOF', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'ARL4A', 'NT5E', 'CDCA4', 'AKR1C3', 'PPP1CB', 'KCNN4', 'AJUBA', 'HNRNPD', 'CDC20', 'CPLX2', 'SRGAP1', 'UBB', 'NPM1', 'NUP37', 'GPX2', 'FLNB', 'ULK1', 'PSMD8', 'LIMD2', 'TAGLN2', 'ANXA2', 'EIF2S1', 'FBXO2', 'GAPDH', 'MYL12B', 'ELF3', 'S100A16', 'UPP1', 'HSP90AA1', 'COPB1', 'TXNDC9', 'PPP1R14A', 'HSPB1', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'SERPINE2', 'CALM2', 'RGS3', 'FABP5', 'LCE3D', 'BCL3', 'CCT2', 'SFN', 'MGLL', 'G6PD', 'RGS2', 'ANXA1', 'UBE2S', 'SQSTM1', 'EPHB2', 'DDX56', 'STMN1', 'RND1', 'CD44', 'PDLIM5', 'ENO3', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'ARHGAP11A', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'CCNB2', 'SYT1', 'SAT1', 'HSPA1A', 'POLR2L', 'MALSU1', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'ATF4', 'CDKN3', 'GPX1', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'UBXN4', 'AP1M2', 'PSMA5', 'ACTN1', 'FTL', 'BLOC1S2', 'AKR1B10', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'ETS2', 'TPM1', 'CTTN', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'CDC42', 'TMSB4X', 'PSMC4', 'THRA', 'ARHGAP29', 'PGD', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'VIM', 'FTH1', 'PGK1', 'IER3', 'LGALS1', 'TKT', 'ALDH1A1', 'AURKB', 'KRT8', 'AHNAK2', 'TGM2', 'GSTO1', 'CBR1', 'KRT7', 'S100A4', 'CCNE1', 'FGFR1', 'S100A3', 'CCT5', 'RBP1', 'MT2A', 'PTTG1', 'GRAMD1A', 'CCT3', 'PDCD5', 'TUBA1A', 'CDC25B', 'TUBB', 'EIF2S3', 'INO80C', 'PRNP', 'AP2M1', 'PSMD1', 'MAP1LC3A', 'DOCK5', 'HSP90B1', 'TP53I3', 'NUDC', 'IL32', 'SGK1', 'CTPS1', 'PSMA4', 'PRMT1', 'TPM2', 'COTL1', 'C1QBP', 'LMNA', 'NUP93', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'PGM2L1', 'LDHB', 'NEMF', 'ALDH3A1', 'ECH1', 'JUP', 'MAP1B', 'HNRNPH1', 'PRC1', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['IDA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'NAS'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IGI', 'TAS'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'NAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS'], ['IDA', 'TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'NAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IGI', 'TAS'], ['TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IEA'], ['IBA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS']]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GO:0043226</t>
+          <t>GO:0008150</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>organelle</t>
+          <t>biological_process</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.659445229023141e-05</v>
+        <v>5.20924587382478e-06</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton, and prokaryotic structures such as anammoxosomes and pirellulosomes. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2112</v>
+        <v>2453</v>
       </c>
       <c r="H10" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I10" t="n">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="J10" t="n">
         <v>2717</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8768267223382046</v>
+        <v>0.9729166666666667</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1988636363636364</v>
+        <v>0.1903791275988585</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2244,64 +2244,64 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'MRPL13', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'SPOCK1', 'FKBP3', 'LDHA', 'NQO1', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'JUN', 'TMSB10', 'GLRX', 'NAP1L1', 'NOL7', 'TMEM92', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'RND1', 'HSPA5', 'EREG', 'F12', 'TSPAN4', 'SCG5', 'CHCHD10', 'GALNT14', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'TSPAN5', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'SEMA3C', 'MTHFD1', 'ENO1', 'NUDC', 'TNS3', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'MORC4', 'S100A3', 'RPL26', 'CDC42SE1', 'ASPH', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'COL4A1', 'PKM', 'TKT', 'S100A16', 'CD24', 'IGFBP4', 'TCEAL8', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'ATP1B1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'NEAT1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'PERP', 'DDX10', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'SLC26A2', 'FSCN1', 'FBXO2', 'CADM1', 'TUBA1A', 'APLP2', 'RBP4', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'LTBP3', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'CD9', 'SULT2B1', 'MYL12B', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'ECH1', 'RSU1', 'TCEAL1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'CBR1', 'TAGLN2', 'MT1X', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'RPL22L1', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'CCDC59', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'AURKB', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'CDCA4', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'BLVRA', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'NNMT', 'FSTL3', 'ANGPTL4', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'SMTN', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'BICC1', 'CADM1', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GNG11', 'GSTP1', 'ASPH', 'TNFRSF12A', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'C1orf56', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'LRRC75A', 'ID3', 'NSMCE2', 'NAP1L1', 'KCNMA1', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'TM4SF1', 'BTG1', 'GLRX', 'SFPQ', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'IL11', 'RBP4', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'DMKN', 'ARL4A', 'FOXM1', 'NT5E', 'ATP1B1', 'CDCA4', 'ATP5G1', 'CA8', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'SLN', 'HNRNPD', 'HOXB8', 'FXYD5', 'CDC20', 'CPLX2', 'LAMC2', 'SRGAP1', 'ANTXR1', 'KCNG1', 'UBB', 'NPM1', 'CCL2', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'IGFBP6', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'AVPI1', 'COPB1', 'TUBB2A', 'TXNDC9', 'PPP1R14A', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'NCOA7', 'TAGLN', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MEG3', 'MGLL', 'PHLDA3', 'CA12', 'PLAUR', 'CXCL5', 'G6PD', 'RGS2', 'HELLS', 'PMP22', 'ANXA1', 'GNG4', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'PDLIM5', 'ENO3', 'WDR43', 'COL4A2', 'SRSF7', 'TFPI2', 'RPL22L1', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'SAT1', 'LTBP3', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'CKS2', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'PSMA5', 'ITGA11', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'TM7SF3', 'MALAT1', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'SPOCK1', 'LBH', 'THRA', 'ARHGAP29', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'SLAMF9', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'SLC26A2', 'PTPRJ', 'FGFR1', 'JUN', 'ITGA2', 'TOP2A', 'SNAPC1', 'LCE3E', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'PVR', 'HMGB2', 'MT2A', 'HPCAL1', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'NRP2', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'CCPG1', 'TP53I3', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'TRIML2', 'CXCL8', 'IL32', 'SGK1', 'CTPS1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'NTN4', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'CCDC80', 'PGM2L1', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'EMP3', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'OSGIN1', 'FAM89B', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['NAS'], ['IEA'], ['HDA', 'IBA'], ['IEA'], ['HDA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'IBA'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IGI', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['ISA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['ISA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA']]</t>
+          <t>[['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEA'], ['IBA', 'NAS', 'IEA'], ['NAS'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'HEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HEP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['HMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['ISS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'TAS', 'IC', 'IEA'], ['IMP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HMP'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IEA'], ['NAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IBA'], ['IMP', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GO:0005737</t>
+          <t>GO:0009987</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cytoplasm</t>
+          <t>cellular process</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.845621561145374e-05</v>
+        <v>2.700223472341554e-05</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>"The contents of a cell excluding the plasma membrane and nucleus, but including other subcellular structures." [ISBN:0198547684]</t>
+          <t>"Any process that is carried out at the cellular level, but not necessarily restricted to a single cell. For example, cell communication occurs among more than one cell, but occurs at the cellular level." [GOC:go_curators, GOC:isa_complete]</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1924</v>
+        <v>2402</v>
       </c>
       <c r="H11" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I11" t="n">
-        <v>392</v>
+        <v>460</v>
       </c>
       <c r="J11" t="n">
         <v>2717</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8183716075156576</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2037422037422038</v>
+        <v>0.1915070774354704</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>['GO:0005622', 'GO:0110165']</t>
+          <t>['GO:0008150']</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'MRPL13', 'LDHB', 'SRSF7', 'TAGLN', 'CD63', 'ANXA3', 'SPOCK1', 'LDHA', 'LAMC2', 'NQO1', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'NNMT', 'IER3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'TMSB10', 'IL32', 'GLRX', 'NAP1L1', 'NOL7', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'PPP1R14A', 'RND1', 'HSPA5', 'EREG', 'F12', 'SCG5', 'CHCHD10', 'GALNT14', 'CSRP1', 'SLC3A2', 'S100A11', 'ANPEP', 'TSPAN5', 'CTPS1', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'MTHFD1', 'ENO1', 'NUDC', 'TNS3', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRIML2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'S100A3', 'RPL26', 'CDC42SE1', 'ASPH', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'COL4A1', 'CA8', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'LCE3D', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'BICC1', 'PERP', 'PGM2L1', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'ARHGAP29', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'VTN', 'FSCN1', 'FBXO2', 'TUBA1A', 'APLP2', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'MICAL2', 'GPX1', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'LRRC75A', 'CD9', 'SULT2B1', 'MYL12B', 'PPP3CA', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'PSMB1', 'COTL1', 'PBX1', 'PSMD2', 'BDNF', 'ARPC3', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'SAT1', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'ELF3', 'COL5A2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'RSU1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'CBR1', 'TAGLN2', 'MT1X', 'PHKG1', 'AP1M2', 'TUBA1C', 'KRT19', 'RGS3', 'CAPG', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'ITGA2', 'FN1', 'RDX', 'TP53I3', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'IL11', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'THRA', 'AGR2', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'PHLDA3', 'AURKB', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'CDCA4', 'HBEGF', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'BLVRA', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'NNMT', 'FSTL3', 'ANGPTL4', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'BICC1', 'CADM1', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GNG11', 'GSTP1', 'ASPH', 'TNFRSF12A', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'C1orf56', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'LRRC75A', 'ID3', 'NSMCE2', 'NAP1L1', 'KCNMA1', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'BTG1', 'GLRX', 'SFPQ', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'IL11', 'RBP4', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'DMKN', 'ARL4A', 'FOXM1', 'NT5E', 'ATP1B1', 'CDCA4', 'ATP5G1', 'CA8', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'PRSS3', 'AJUBA', 'HMGA2', 'SLN', 'HNRNPD', 'HOXB8', 'FXYD5', 'CDC20', 'CPLX2', 'LAMC2', 'SRGAP1', 'ANTXR1', 'KCNG1', 'UBB', 'NPM1', 'CCL2', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'IGFBP6', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'UPP1', 'HSP90AA1', 'NUPR1', 'AVPI1', 'COPB1', 'TUBB2A', 'TXNDC9', 'PPP1R14A', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'NCOA7', 'TAGLN', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MEG3', 'MGLL', 'PHLDA3', 'PLAUR', 'CXCL5', 'G6PD', 'RGS2', 'HELLS', 'PMP22', 'ANXA1', 'GNG4', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'PDLIM5', 'ENO3', 'WDR43', 'COL4A2', 'SRSF7', 'TFPI2', 'RPL22L1', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'SAT1', 'LTBP3', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'CKS2', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'PSMA5', 'ITGA11', 'ACTN1', 'SDC4', 'BLOC1S2', 'AKR1B10', 'TM7SF3', 'MALAT1', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'SPOCK1', 'LBH', 'THRA', 'ARHGAP29', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'SLAMF9', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'SLC26A2', 'PTPRJ', 'FGFR1', 'JUN', 'ITGA2', 'TOP2A', 'SNAPC1', 'LCE3E', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'PVR', 'HMGB2', 'MT2A', 'HPCAL1', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'NRP2', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'CCPG1', 'TP53I3', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'TRIML2', 'CXCL8', 'IL32', 'SGK1', 'CTPS1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'NTN4', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'CCDC80', 'PGM2L1', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'EMP3', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'OSGIN1', 'FAM89B', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['ISS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['ISS', 'TAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['HTP'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['TAS'], ['ISS'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IGI', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA']]</t>
+          <t>[['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'IEA'], ['IBA', 'NAS', 'IEA'], ['NAS'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['ISS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IGI', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['HMP', 'IBA'], ['IBA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEP', 'IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IEA'], ['IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IMP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'HMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS'], ['NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'ISS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA'], ['IEA'], ['NAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'IBA'], ['IBA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA'], ['IMP', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2332,42 +2332,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GO:0005622</t>
+          <t>GO:0005737</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>intracellular anatomical structure</t>
+          <t>cytoplasm</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.0004206369576825941</v>
+        <v>4.010177080932034e-05</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
+          <t>"The contents of a cell excluding the plasma membrane and nucleus, but including other subcellular structures." [ISBN:0198547684]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2222</v>
+        <v>1937</v>
       </c>
       <c r="H12" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I12" t="n">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="J12" t="n">
         <v>2717</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9039665970772442</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1948694869486949</v>
+        <v>0.2039235931853381</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2376,17 +2376,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0005622', 'GO:0110165']</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'MRPL13', 'LDHB', 'SRSF7', 'TAGLN', 'CD63', 'ANXA3', 'SPOCK1', 'FKBP3', 'LDHA', 'LAMC2', 'NQO1', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'NNMT', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'JUN', 'TMSB10', 'IL32', 'GLRX', 'NAP1L1', 'NOL7', 'TMEM92', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'PPP1R14A', 'RND1', 'HSPA5', 'EREG', 'F12', 'SCG5', 'CHCHD10', 'GALNT14', 'CSRP1', 'SLC3A2', 'S100A11', 'ANPEP', 'TSPAN5', 'CTPS1', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'MTHFD1', 'ENO1', 'NUDC', 'TNS3', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRIML2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'MORC4', 'S100A3', 'RPL26', 'CDC42SE1', 'ASPH', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'COL4A1', 'CA8', 'PKM', 'TKT', 'S100A16', 'CD24', 'IGFBP4', 'TCEAL8', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'LCE3D', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'NEAT1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'BICC1', 'PERP', 'DDX10', 'PGM2L1', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'ARHGAP29', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'FSCN1', 'FBXO2', 'TUBA1A', 'APLP2', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'LRRC75A', 'CD9', 'SULT2B1', 'MYL12B', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'SAT1', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'RSU1', 'TCEAL1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'CBR1', 'TAGLN2', 'MT1X', 'PHKG1', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'ITGA2', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'TP53I3', 'RPL22L1', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'IL11', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'CCDC59', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'PHLDA3', 'AURKB', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'CDCA4', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['HSPA2', 'BLVRA', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'NNMT', 'FSTL3', 'HSPD1', 'CDA', 'CDK6', 'TUBA4A', 'SMTN', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'BICC1', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GSTP1', 'ASPH', 'MYOF', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'LRRC75A', 'ID3', 'NAP1L1', 'SLC2A3', 'PSMD2', 'BTG1', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'RDX', 'MGST3', 'CENPA', 'IL11', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'ARL4A', 'NT5E', 'CDCA4', 'ATP5G1', 'CA8', 'TRIM7', 'RNF26', 'AKR1C3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'AJUBA', 'C15orf48', 'SLN', 'HNRNPD', 'CDC20', 'CPLX2', 'LAMC2', 'SRGAP1', 'ANTXR1', 'UBB', 'NPM1', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'CHCHD10', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'COPB1', 'TUBB2A', 'TXNDC9', 'PPP1R14A', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'TAGLN', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MGLL', 'PHLDA3', 'PLAUR', 'G6PD', 'RGS2', 'ANXA1', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'TUBA1B', 'STMN1', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'CHST11', 'PDLIM5', 'ENO3', 'COL4A2', 'SRSF7', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'SAT1', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'HEXA', 'UBXN4', 'AP1M2', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'DHRS2', 'CTTN', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'SPOCK1', 'LBH', 'THRA', 'ARHGAP29', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'PTPRJ', 'FGFR1', 'ITGA2', 'TOP2A', 'S100A3', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'PVR', 'HMGB2', 'MT2A', 'PTTG1', 'CDH2', 'GRAMD1A', 'ID1', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'TP53I3', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'TRIML2', 'IL32', 'SGK1', 'CTPS1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'PGM2L1', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'FAM89B', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['ISS'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['ISS', 'TAS', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HTP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'IMP', 'IBA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IEA'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2398,42 +2398,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO:0043227</t>
+          <t>GO:0043226</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>membrane-bounded organelle</t>
+          <t>organelle</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0004757412107023383</v>
+        <v>0.0002107839535952991</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"Organized structure of distinctive morphology and function. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton, and prokaryotic structures such as anammoxosomes and pirellulosomes. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1997</v>
+        <v>2119</v>
       </c>
       <c r="H13" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I13" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="J13" t="n">
         <v>2717</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8350730688935282</v>
+        <v>0.875</v>
       </c>
       <c r="L13" t="n">
-        <v>0.200300450676014</v>
+        <v>0.1982067012741859</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>['GO:0043226']</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'MRPL13', 'TM7SF3', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'FKBP3', 'LDHA', 'NQO1', 'PTGR1', 'DYNLL1', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'HSPA1A', 'REEP5', 'JUN', 'GLRX', 'NAP1L1', 'NOL7', 'TMEM92', 'ATP5G1', 'TOP2A', 'DERL1', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'RND1', 'HSPA5', 'EREG', 'F12', 'TSPAN4', 'SCG5', 'CHCHD10', 'GALNT14', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'ANPEP', 'TSPAN5', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'SEMA3C', 'MTHFD1', 'ENO1', 'NUDC', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'MORC4', 'S100A3', 'RPL26', 'ASPH', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'COL4A1', 'PKM', 'TKT', 'S100A16', 'CD24', 'IGFBP4', 'TCEAL8', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'ATP1B1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'NUAK1', 'NEAT1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'PERP', 'DDX10', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'SLC26A2', 'FSCN1', 'FBXO2', 'TUBA1A', 'APLP2', 'RBP4', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'LTBP3', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'CD9', 'SULT2B1', 'MYL12B', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'SFPQ', 'PUS1', 'MGST3', 'NPTX1', 'UBXN4', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'CCNB2', 'ECH1', 'RSU1', 'TCEAL1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'CBR1', 'TAGLN2', 'MT1X', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'BCL2A1', 'VIM', 'PRMT1', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'CCDC59', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'NUPR1', 'GSTP1', 'AURKB', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'CDCA4', 'HBEGF', 'INO80C', 'SQSTM1', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'BLVRA', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'FSTL3', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'SMTN', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GSTP1', 'ASPH', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'ID3', 'NSMCE2', 'NAP1L1', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'BTG1', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'RBP4', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'ARL4A', 'FOXM1', 'NT5E', 'ATP1B1', 'CDCA4', 'ATP5G1', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'SLN', 'HNRNPD', 'HOXB8', 'CDC20', 'CPLX2', 'ANTXR1', 'UBB', 'NPM1', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'TCEAL1', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'COPB1', 'TUBB2A', 'TXNDC9', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'NCOA7', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MGLL', 'PLAUR', 'G6PD', 'RGS2', 'HELLS', 'ANXA1', 'GNG4', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'PDLIM5', 'ENO3', 'WDR43', 'COL4A2', 'SRSF7', 'RPL22L1', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'LTBP3', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'TCEAL8', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'TM7SF3', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'TMEM92', 'BIRC5', 'TSPAN15', 'HMGA1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'SPOCK1', 'LBH', 'THRA', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'CCDC59', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'SLC26A2', 'PTPRJ', 'FGFR1', 'JUN', 'TOP2A', 'S100A3', 'SNAPC1', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'HMGB2', 'MT2A', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'MORC4', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'SGK1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['IDA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IEA'], ['HDA', 'IBA'], ['IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'IBA'], ['IDA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IGI', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['EXP', 'HDA', 'NAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['EXP', 'IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['HDA', 'ISS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IBA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['NAS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA'], ['HDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -2464,42 +2464,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GO:0043229</t>
+          <t>GO:0043227</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>intracellular organelle</t>
+          <t>membrane-bounded organelle</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.001335520388303981</v>
+        <v>0.0007658401426158301</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"Organized structure of distinctive morphology and function, occurring within the cell. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton. Excludes the plasma membrane." [GOC:go_curators]</t>
+          <t>"Organized structure of distinctive morphology and function, bounded by a single or double lipid bilayer membrane. Includes the nucleus, mitochondria, plastids, vacuoles, and vesicles. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="H14" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I14" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="J14" t="n">
         <v>2717</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8329853862212944</v>
+        <v>0.8395833333333333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1995</v>
+        <v>0.1999007936507937</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2508,17 +2508,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['GO:0005622', 'GO:0043226']</t>
+          <t>['GO:0043226']</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'MRPL13', 'LDHB', 'SRSF7', 'CD63', 'ANXA3', 'FKBP3', 'LDHA', 'NQO1', 'DYNLL1', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'JUN', 'TMSB10', 'GLRX', 'NAP1L1', 'NOL7', 'TMEM92', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'RND1', 'HSPA5', 'EREG', 'F12', 'SCG5', 'CHCHD10', 'GALNT14', 'CSRP1', 'SLC3A2', 'S100A11', 'ANPEP', 'TSPAN5', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'MTHFD1', 'ENO1', 'NUDC', 'TNS3', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'MORC4', 'S100A3', 'RPL26', 'CDC42SE1', 'ASPH', 'CCNB1', 'KRT7', 'NUP37', 'MT2A', 'PSME2', 'COL4A1', 'PKM', 'TKT', 'S100A16', 'CD24', 'IGFBP4', 'TCEAL8', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'RBP1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'NEAT1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'DSE', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'PERP', 'DDX10', 'ALDH3A1', 'STMN1', 'DLGAP5', 'CEP170', 'FABP5', 'AREG', 'TXN', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'FSCN1', 'FBXO2', 'TUBA1A', 'APLP2', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'CD9', 'SULT2B1', 'MYL12B', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'ECH1', 'TCEAL1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'TAGLN2', 'MT1X', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'RPL22L1', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'CCDC59', 'BCL3', 'CDKN3', 'MLXIP', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'AURKB', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'CDCA4', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'BLVRA', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'FSTL3', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GSTP1', 'ASPH', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'ID3', 'NSMCE2', 'NAP1L1', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'BTG1', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'RBP4', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'PRMT5', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'ARL4A', 'FOXM1', 'NT5E', 'ATP1B1', 'CDCA4', 'ATP5G1', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'SLN', 'HNRNPD', 'HOXB8', 'CDC20', 'CPLX2', 'ANTXR1', 'UBB', 'NPM1', 'ISG20', 'NUP37', 'FLNB', 'COL5A2', 'ULK1', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'TCEAL1', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'COPB1', 'TUBB2A', 'TXNDC9', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'NCOA7', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MGLL', 'PLAUR', 'G6PD', 'RGS2', 'HELLS', 'ANXA1', 'GNG4', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'ENO3', 'WDR43', 'COL4A2', 'SRSF7', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'LTBP3', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'HPGD', 'ACTB', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'TCEAL8', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'TM7SF3', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'AMIGO2', 'DHRS2', 'CTTN', 'TMEM92', 'BIRC5', 'TSPAN15', 'HMGA1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'LBH', 'THRA', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'CCDC59', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'SLC26A2', 'PTPRJ', 'FGFR1', 'JUN', 'TOP2A', 'S100A3', 'SNAPC1', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'HMGB2', 'MT2A', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'MORC4', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'HSP90B1', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'NUDC', 'SGK1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['HDA', 'IBA'], ['IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['EXP', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA'], ['IDA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['IDA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['HDA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IGI', 'HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['HDA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['HDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['HDA'], ['IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IC', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'TAS', 'NAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IPI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'HDA', 'NAS', 'IEA'], ['IMP', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['HDA'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IDA', 'IPI', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['HTP', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -2530,42 +2530,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GO:0009987</t>
+          <t>GO:0050896</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cellular process</t>
+          <t>response to stimulus</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.002909759087712923</v>
+        <v>0.0009190463472260473</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>"Any process that is carried out at the cellular level, but not necessarily restricted to a single cell. For example, cell communication occurs among more than one cell, but occurs at the cellular level." [GOC:go_curators, GOC:isa_complete]</t>
+          <t>"Any process that results in a change in state or activity of a cell or an organism (in terms of movement, secretion, enzyme production, gene expression, etc.) as a result of a stimulus. The process begins with detection of the stimulus and ends with a change in state or activity or the cell or organism." [GOC:ai, GOC:bf]</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2402</v>
+        <v>1445</v>
       </c>
       <c r="H15" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I15" t="n">
-        <v>455</v>
+        <v>310</v>
       </c>
       <c r="J15" t="n">
         <v>2717</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9498956158663883</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1894254787676936</v>
+        <v>0.2145328719723184</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2579,59 +2579,59 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'MRPL13', 'TM7SF3', 'LDHB', 'SRSF7', 'TAGLN', 'CD63', 'ANXA3', 'SPOCK1', 'LDHA', 'LAMC2', 'NQO1', 'PTGR1', 'DYNLL1', 'ITGA11', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'NNMT', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'CCL2', 'JUN', 'TMSB10', 'IL32', 'CCDC80', 'GLRX', 'NAP1L1', 'NOL7', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'RSPO3', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'PPP1R14A', 'RND1', 'HSPA5', 'EREG', 'F12', 'TSPAN4', 'SCG5', 'CHCHD10', 'GALNT14', 'KCNMA1', 'GNG11', 'CSRP1', 'SLC3A2', 'GNG4', 'DMKN', 'S100A11', 'CXCL5', 'ANPEP', 'TSPAN5', 'CTPS1', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'SEMA3C', 'MTHFD1', 'ENO1', 'NUDC', 'EMP3', 'TNS3', 'TFPI2', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'CKS2', 'TIMP2', 'TRIML2', 'TRAM1', 'CCPG1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'RPL26', 'CDC42SE1', 'ASPH', 'LCE3E', 'CCNB1', 'KRT7', 'NUP37', 'NRP2', 'MT2A', 'PSME2', 'COL4A1', 'CA8', 'PKM', 'TKT', 'AVPI1', 'CD24', 'IGFBP4', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'OSGIN1', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'ATP1B1', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'LCE3D', 'SDC1', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'C1orf56', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'MEG3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'BICC1', 'PERP', 'DDX10', 'KCNG1', 'PGM2L1', 'ALDH3A1', 'STMN1', 'DLGAP5', 'ARHGAP29', 'FABP5', 'AREG', 'TXN', 'ANGPTL4', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'SLC26A2', 'FSCN1', 'NTN4', 'FBXO2', 'CADM1', 'TUBA1A', 'APLP2', 'RBP4', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'LTBP3', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'CD9', 'SULT2B1', 'SLAMF9', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'PMP22', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'SAT1', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'MALAT1', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'RSU1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'CBR1', 'TAGLN2', 'MT1X', 'PHKG1', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'ITGA2', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'TP53I3', 'IGFBP6', 'RPL22L1', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'IL11', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'TNFRSF12A', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'FXYD5', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'CXCL8', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'PHLDA3', 'AURKB', 'CA12', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'TXNRD2', 'CTNNB1', 'RHOU', 'FSTL3', 'ANGPTL4', 'HSPD1', 'CDA', 'CDK6', 'CMTM3', 'SLC22A18', 'TRIB3', 'TNS3', 'HSPA5', 'GSN', 'TUBB4B', 'PYCARD', 'BICC1', 'CADM1', 'CES1', 'HMGB3', 'ARPC3', 'GNG11', 'GSTP1', 'ASPH', 'TNFRSF12A', 'MYOF', 'NEAT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'ID3', 'NSMCE2', 'KCNMA1', 'SFPQ', 'RDX', 'MGST3', 'IL11', 'RBP4', 'RHOF', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'FOXM1', 'NT5E', 'ATP1B1', 'CA8', 'TRIM7', 'RNF26', 'AKR1C3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'HNRNPD', 'CDC20', 'CPLX2', 'SRGAP1', 'UBB', 'NPM1', 'CCL2', 'ISG20', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'NRG1', 'CHCHD10', 'AXL', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'IGFBP6', 'DERL1', 'F12', 'ELF3', 'IGFBP7', 'AREG', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'AVPI1', 'HSPB1', 'KRT18', 'ACTG1', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'NCOA7', 'BCL3', 'SLC3A2', 'SFN', 'MGLL', 'PHLDA3', 'PLAUR', 'CXCL5', 'G6PD', 'RGS2', 'HELLS', 'ANXA1', 'GNG4', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'TUBA1B', 'STMN1', 'HMGB1', 'RND1', 'CD44', 'FOXD1', 'CHST11', 'COL4A2', 'SRSF7', 'TFPI2', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'ARHGAP11A', 'DUSP4', 'OSBPL8', 'EIF4A3', 'SVIP', 'SYT1', 'JUNB', 'LTBP3', 'FN1', 'HSPA1A', 'AGR2', 'HBEGF', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'GCLC', 'SMAD3', 'ATF4', 'NUAK1', 'TOB1', 'ITGA3', 'ANXA4', 'GPX1', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'UBXN4', 'ITGA11', 'SDC4', 'BLOC1S2', 'AKR1B10', 'TM7SF3', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'TPM1', 'DHRS2', 'CTTN', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'LBH', 'THRA', 'ARHGAP29', 'CAV1', 'VTN', 'MYL12A', 'NQO1', 'KRT19', 'SERPINE1', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'ALDH1A1', 'AURKB', 'SLAMF9', 'KRT8', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'PTPRJ', 'FGFR1', 'JUN', 'ITGA2', 'TOP2A', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'PVR', 'HMGB2', 'MT2A', 'HPCAL1', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'ID1', 'NRP2', 'PDCD5', 'TUBA1A', 'TRAM1', 'TUBB', 'INO80C', 'PRNP', 'NPTX1', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'MAF', 'ANXA3', 'DHRS3', 'CDC42SE1', 'NUDC', 'TRIML2', 'CXCL8', 'IL32', 'SGK1', 'CTPS1', 'NPC2', 'STC1', 'CD24', 'PRMT1', 'CD63', 'COTL1', 'C1QBP', 'LMNA', 'NUP93', 'RSU1', 'RAET1G', 'CCDC80', 'TIMP2', 'IGFBP4', 'ALDH3A1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'COL4A1', 'HACD3', 'OSGIN1', 'FAM89B', 'ILK', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'ISS', 'IBA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HMP', 'IBA', 'IEA'], ['IGI', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IBA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEP', 'IBA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['NAS'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS'], ['TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IGI', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'ISS'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'IMP', 'ISS'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP'], ['IEA'], ['IMP', 'IBA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IBA'], ['ISS', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEP', 'IBA', 'IEA'], ['NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA']]</t>
+          <t>[['IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['NAS'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA'], ['IMP', 'TAS'], ['IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IDA', 'IMP', 'IBA'], ['ISS'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI'], ['IDA', 'IGI', 'IEP'], ['IMP', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IMP', 'ISS', 'IEA'], ['NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IEA'], ['ISS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IEA'], ['IBA'], ['IEA'], ['IGI', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['HMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IEP'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IMP', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEP', 'ISS'], ['IEA'], ['IEA'], ['NAS'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'IMP', 'NAS'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IEP', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEP', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IMP', 'HMP', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IEA'], ['IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS'], ['IDA', 'IBA'], ['IMP', 'TAS', 'NAS'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IMP', 'IEP', 'TAS', 'NAS'], ['IDA', 'IMP', 'IEP', 'ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IEA'], ['NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IMP', 'IBA'], ['ISS', 'IEA'], ['IEA'], ['IMP', 'IBA'], ['ISS', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IMP', 'HMP', 'NAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['IMP', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IC', 'IEA'], ['IBA'], ['IEP'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IMP'], ['IDA', 'IBA', 'IEA'], ['HMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA'], ['IEP', 'ISS'], ['IDA'], ['IBA', 'IEA'], ['NAS', 'IEA'], ['IDA'], ['IDA'], ['IBA'], ['NAS'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP'], ['IMP', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IC', 'IEA'], ['HMP'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IEP', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC'], ['IMP', 'IEA'], ['ISS'], ['IEA'], ['IDA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'HMP', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'IEA'], ['IMP'], ['IDA', 'ISS', 'TAS', 'NAS'], ['IBA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA'], ['IDA', 'IC', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEP'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IEA'], ['IEP'], ['IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['IEP', 'IBA'], ['IBA'], ['IEA'], ['IMP'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['IDA'], ['IEA'], ['IMP', 'IEA'], ['NAS'], ['ISO', 'IEA'], ['IDA', 'IGI', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['NAS'], ['IDA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IEP'], ['IEA'], ['IDA', 'IEP', 'ISS', 'NAS', 'IC'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA'], ['IEA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IC'], ['IEP'], ['IEA'], ['IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GO:0008150</t>
+          <t>GO:0005622</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>biological_process</t>
+          <t>intracellular anatomical structure</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.009520306203969212</v>
+        <v>0.0009731999572367624</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
+          <t>"A component of a cell contained within (but not including) the plasma membrane. In eukaryotes it includes the nucleus and cytoplasm." [ISBN:0198506732]</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2459</v>
+        <v>2230</v>
       </c>
       <c r="H16" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I16" t="n">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="J16" t="n">
         <v>2717</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9624217118997912</v>
+        <v>0.9041666666666667</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1874745831638878</v>
+        <v>0.1946188340807175</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2640,64 +2640,64 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['OLFM2', 'TXNDC9', 'CD44', 'EZH2', 'TMEM205', 'MRPL13', 'TM7SF3', 'LDHB', 'SRSF7', 'TAGLN', 'CD63', 'ANXA3', 'SPOCK1', 'LDHA', 'LAMC2', 'NQO1', 'PTGR1', 'DYNLL1', 'ITGA11', 'EDN1', 'OCIAD2', 'ISG20', 'PGD', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'HNRNPH1', 'BOP1', 'NNMT', 'IER3', 'GNL3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'PDLIM5', 'HSPA1A', 'REEP5', 'CCL2', 'JUN', 'TMSB10', 'IL32', 'CCDC80', 'GLRX', 'NAP1L1', 'NOL7', 'ATP5G1', 'TOP2A', 'TUBA1B', 'DERL1', 'RSPO3', 'MAP1B', 'AATF', 'TMEM59', 'ACTB', 'RAN', 'MAP1LC3A', 'PPP1R14A', 'RND1', 'HSPA5', 'EREG', 'F12', 'TSPAN4', 'SCG5', 'CHCHD10', 'GALNT14', 'KCNMA1', 'GNG11', 'CSRP1', 'SLC3A2', 'GNG4', 'DMKN', 'S100A11', 'CXCL5', 'ANPEP', 'TSPAN5', 'CTPS1', 'CSTF3', 'AKR1B1', 'TM4SF20', 'NAMPT', 'NT5E', 'MYL12A', 'CDC25B', 'RPL28', 'HLA-C', 'PSMD8', 'SEMA3C', 'MTHFD1', 'ENO1', 'NUDC', 'EMP3', 'TNS3', 'TFPI2', 'ID3', 'POLR2L', 'HSP90AB1', 'PLOD2', 'TM4SF1', 'CTTN', 'IGFBP3', 'CKS2', 'TIMP2', 'TRIML2', 'TRAM1', 'CCPG1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'ACTN1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'RPL26', 'CDC42SE1', 'ASPH', 'LCE3E', 'CCNB1', 'KRT7', 'NUP37', 'NRP2', 'MT2A', 'PSME2', 'COL4A1', 'CA8', 'PKM', 'TKT', 'S100A16', 'AVPI1', 'CD24', 'IGFBP4', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'OSGIN1', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'UBE2S', 'CCT2', 'HMGA1', 'CXCL1', 'ATP1B1', 'FTL', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PRSS23', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'LCE3D', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'MRPS22', 'SNHG10', 'C1orf56', 'CES1', 'HACD3', 'BTG1', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'NUDT19', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'CYP24A1', 'MTHFD2', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'ENO3', 'DSE', 'CCNE1', 'EIF4A3', 'MEG3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'BICC1', 'PERP', 'DDX10', 'KCNG1', 'PGM2L1', 'ALDH3A1', 'STMN1', 'DLGAP5', 'ARHGAP29', 'FABP5', 'AREG', 'TXN', 'ANGPTL4', 'HMGB1', 'HSPA2', 'SMTN', 'ANXA1', 'UBE2C', 'ARL6IP1', 'TGM2', 'SLN', 'TSFM', 'AJUBA', 'ADAM19', 'VTN', 'SLC26A2', 'FSCN1', 'NTN4', 'FBXO2', 'CADM1', 'TUBA1A', 'APLP2', 'RBP4', 'EIF1', 'FLNB', 'RHOF', 'FGFR1', 'WDR43', 'MICAL2', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'SAMD11', 'CREM', 'SH3BGRL3', 'PDCD5', 'DHRS3', 'EMG1', 'AHNAK2', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'MYL6', 'FTH1', 'LGALS1', 'MALSU1', 'ZBED2', 'CYB5A', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'ORMDL2', 'PSMC4', 'LTBP3', 'DHRS7', 'TK1', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'ZFAS1', 'COPB1', 'CD9', 'SULT2B1', 'MYL12B', 'SLAMF9', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'KRR1', 'MAP2K3', 'ACP2', 'GSTO1', 'FOXD1', 'NME1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'PSMB1', 'COTL1', 'PBX1', 'PHF19', 'SAP30BP', 'PSMD2', 'BDNF', 'ARPC3', 'PMP22', 'SFPQ', 'PUS1', 'TPM2', 'MGST3', 'NPTX1', 'UBXN4', 'SAT1', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'HOXB8', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'EBNA1BP2', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'MALAT1', 'S100A6', 'ANTXR1', 'SLC35F6', 'TUBB', 'CNN3', 'TUBA4A', 'CDK1', 'MGST1', 'MT-ND6', 'SNAPC1', 'GALNT1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'RSU1', 'PRC1', 'MOB3B', 'UBC', 'HMGB3', 'NEMF', 'HMGB2', 'CCDC85B', 'DKC1', 'PSMA4', 'ETS2', 'SNRPA1', 'CBR1', 'TAGLN2', 'MT1X', 'PHKG1', 'AP1M2', 'TUBA1C', 'KRT19', 'NSMCE2', 'RGS3', 'CAPG', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'VCAN', 'NPC2', 'ITGA2', 'FN1', 'AMIGO2', 'RDX', 'JUNB', 'TP53I3', 'IGFBP6', 'RPL22L1', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'IL11', 'PSMA5', 'DUSP4', 'PSMD1', 'CCT3', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SPTSSA', 'SFN', 'TNFRSF12A', 'THRA', 'AGR2', 'NSMCE4A', 'DDX39A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'FXYD5', 'KRT81', 'REXO2', 'HEXA', 'HSP90AA1', 'GSN', 'CXCL8', 'TUBB2A', 'PPP1CB', 'MKI67', 'STC1', 'RAB3B', 'LIMD2', 'COL4A2', 'ARL4A', 'UPP1', 'BCL3', 'CDKN3', 'MLXIP', 'BLVRA', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'PHLDA3', 'AURKB', 'CA12', 'PACSIN3', 'KPNA2', 'SLC2A3', 'CENPA', 'ID1', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'AP2M1', 'FDXR', 'CKS1B', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'BLVRA', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'NNMT', 'FSTL3', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'SMTN', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'BICC1', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GSTP1', 'ASPH', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'LRRC75A', 'ID3', 'NSMCE2', 'NAP1L1', 'SLC2A3', 'PSMD2', 'CKS1B', 'BTG1', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'IL11', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'ARL4A', 'FOXM1', 'NT5E', 'CDCA4', 'ATP5G1', 'CA8', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'SLN', 'HNRNPD', 'HOXB8', 'CDC20', 'CPLX2', 'LAMC2', 'SRGAP1', 'ANTXR1', 'UBB', 'NPM1', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'TCEAL1', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'COPB1', 'TUBB2A', 'TXNDC9', 'PPP1R14A', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'NCOA7', 'TAGLN', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MGLL', 'PHLDA3', 'PLAUR', 'G6PD', 'RGS2', 'HELLS', 'ANXA1', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'PDLIM5', 'ENO3', 'WDR43', 'COL4A2', 'SRSF7', 'RPL22L1', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'SAT1', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ITGA3', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'TCEAL8', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'TMEM92', 'BIRC5', 'TSPAN15', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'SPOCK1', 'LBH', 'THRA', 'ARHGAP29', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'CCDC59', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'ALDH1A1', 'AURKB', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'PTPRJ', 'FGFR1', 'JUN', 'ITGA2', 'TOP2A', 'S100A3', 'SNAPC1', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'PVR', 'HMGB2', 'MT2A', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'EIF2S3', 'INO80C', 'MORC4', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'TP53I3', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'TRIML2', 'IL32', 'SGK1', 'CTPS1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'NUP93', 'KRR1', 'NME1', 'UBC', 'RSU1', 'CYB5A', 'RAET1G', 'PGM2L1', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'FAM89B', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'ISS', 'IBA'], ['IBA', 'ND'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['ND'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'HEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'HEP', 'IBA', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'ND'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'TAS'], ['ND', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEP', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['NAS', 'ND'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'TAS', 'ND', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['HEP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP'], ['IEA'], ['IMP', 'IBA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IBA', 'ND'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'ND', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEP', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IGI', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['EXP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GO:0050896</t>
+          <t>GO:0043229</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>response to stimulus</t>
+          <t>intracellular organelle</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01607679701341985</v>
+        <v>0.001334126045598259</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>"Any process that results in a change in state or activity of a cell or an organism (in terms of movement, secretion, enzyme production, gene expression, etc.) as a result of a stimulus. The process begins with detection of the stimulus and ends with a change in state or activity or the cell or organism." [GOC:ai, GOC:bf]</t>
+          <t>"Organized structure of distinctive morphology and function, occurring within the cell. Includes the nucleus, mitochondria, plastids, vacuoles, vesicles, ribosomes and the cytoskeleton. Excludes the plasma membrane." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1455</v>
+        <v>2008</v>
       </c>
       <c r="H17" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I17" t="n">
-        <v>306</v>
+        <v>401</v>
       </c>
       <c r="J17" t="n">
         <v>2717</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6388308977035491</v>
+        <v>0.8354166666666667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2103092783505155</v>
+        <v>0.1997011952191235</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>['GO:0008150']</t>
+          <t>['GO:0005622', 'GO:0043226']</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['OLFM2', 'CD44', 'EZH2', 'TM7SF3', 'SRSF7', 'CD63', 'ANXA3', 'NQO1', 'DYNLL1', 'ITGA11', 'EDN1', 'OCIAD2', 'ISG20', 'ACTG1', 'UBB', 'BIRC5', 'GCLC', 'BOP1', 'NNMT', 'IER3', 'SDC4', 'CLU', 'CAV1', 'PLAUR', 'HSPA1A', 'CCL2', 'JUN', 'IL32', 'CCDC80', 'TOP2A', 'TUBA1B', 'DERL1', 'RSPO3', 'MAP1B', 'AATF', 'ACTB', 'RAN', 'MAP1LC3A', 'RND1', 'HSPA5', 'EREG', 'F12', 'SCG5', 'CHCHD10', 'KCNMA1', 'GNG11', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'CXCL5', 'TSPAN5', 'CTPS1', 'AKR1B1', 'NAMPT', 'NT5E', 'MYL12A', 'HLA-C', 'SEMA3C', 'ENO1', 'NUDC', 'TFPI2', 'ID3', 'HSP90AB1', 'PLOD2', 'CTTN', 'IGFBP3', 'TIMP2', 'TRIML2', 'TRAM1', 'AKR1B10', 'TNFAIP6', 'IGFBP7', 'B4GALT1', 'SGK1', 'HSP90B1', 'HPGD', 'MAF', 'HSPD1', 'GRAMD1A', 'RPL26', 'CDC42SE1', 'ASPH', 'CCNB1', 'NRP2', 'MT2A', 'COL4A1', 'CA8', 'PKM', 'S100A16', 'AVPI1', 'CD24', 'IGFBP4', 'SLC22A18', 'PTTG1', 'NUP93', 'PCSK1N', 'OSGIN1', 'RBP1', 'PGK1', 'OSBPL8', 'DDX56', 'HMGA1', 'CXCL1', 'ATP1B1', 'CPLX2', 'CMTM3', 'DNER', 'MGLL', 'S100A10', 'KRT8', 'PLK2', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'SDC1', 'C15orf48', 'TOB1', 'AKR1C3', 'CES1', 'HACD3', 'EIF2S1', 'RHOU', 'NRG1', 'GAL', 'CYBA', 'KRT18', 'DOCK5', 'CTNNAL1', 'NUAK1', 'CYP24A1', 'DHRS2', 'KYNU', 'YWHAE', 'PMEPA1', 'IFITM2', 'SERPINE2', 'ANXA4', 'ALDH1A1', 'CCNE1', 'EIF4A3', 'G6PD', 'MYO10', 'PRNP', 'MYOF', 'BICC1', 'PERP', 'ALDH3A1', 'STMN1', 'ARHGAP29', 'FABP5', 'AREG', 'TXN', 'ANGPTL4', 'HMGB1', 'HSPA2', 'ANXA1', 'TGM2', 'AJUBA', 'VTN', 'FBXO2', 'CADM1', 'TUBA1A', 'APLP2', 'RBP4', 'FLNB', 'RHOF', 'FGFR1', 'GPX1', 'MORF4L2', 'AXL', 'LMNA', 'CDC42', 'CDK6', 'FH', 'KCNN4', 'CREM', 'PDCD5', 'DHRS3', 'NMI', 'HELLS', 'RAET1G', 'RASSF10', 'FSTL3', 'S100A4', 'FTH1', 'LGALS1', 'SVIP', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'LTBP3', 'SMAD3', 'RGS2', 'RIN2', 'NPM1', 'CD9', 'PPP3CA', 'FOXM1', 'CDC20', 'LBH', 'ILK', 'JUP', 'ARHGAP11A', 'MAP2K3', 'GSTO1', 'FOXD1', 'TXNRD1', 'TXNRD2', 'FAM89B', 'COTL1', 'SAP30BP', 'BDNF', 'ARPC3', 'SFPQ', 'MGST3', 'NPTX1', 'UBXN4', 'ADH5', 'CHST11', 'TRIB3', 'BLOC1S2', 'CDH2', 'ANXA2', 'NR0B1', 'ATF4', 'NCOA7', 'HMGA2', 'ELF3', 'COL5A2', 'S100A6', 'SLC35F6', 'TUBB', 'CDK1', 'MGST1', 'MT-ND6', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'PVR', 'RSU1', 'MOB3B', 'HMGB3', 'HMGB2', 'CBR1', 'MT1X', 'KRT19', 'NSMCE2', 'RGS3', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'RNF26', 'PDGFC', 'SYT1', 'NPC2', 'ITGA2', 'FN1', 'RDX', 'JUNB', 'IGFBP6', 'TUBB4B', 'FLOT1', 'TMSB4X', 'TRIM7', 'IL11', 'DUSP4', 'PTPRJ', 'CTNNB1', 'COL1A1', 'HNRNPD', 'PYCARD', 'SFN', 'TNFRSF12A', 'THRA', 'AGR2', 'NSMCE4A', 'GPX2', 'BCL2A1', 'VIM', 'PRMT1', 'HSP90AA1', 'GSN', 'CXCL8', 'PPP1CB', 'STC1', 'COL4A2', 'UPP1', 'BCL3', 'SOX4', 'TPM1', 'NUPR1', 'GSTP1', 'PHLDA3', 'AURKB', 'ID1', 'HBEGF', 'INO80C', 'SQSTM1', 'PLEK2', 'C1QBP', 'PRDX1']</t>
+          <t>['NSMCE4A', 'HSPA2', 'PHF19', 'TXNRD2', 'SPTSSA', 'MTHFD1', 'EMG1', 'CTNNB1', 'RHOU', 'TK1', 'MYL6', 'FSTL3', 'HSPD1', 'CDA', 'SAMD11', 'CDK6', 'TUBA4A', 'SMTN', 'CMTM3', 'SLC22A18', 'TRIB3', 'FSCN1', 'REXO2', 'TNS3', 'HSPA5', 'ACP2', 'GSN', 'TUBB4B', 'DDX10', 'PYCARD', 'RPL28', 'CES1', 'TM4SF20', 'HMGB3', 'DLGAP5', 'ARPC3', 'GSTP1', 'ASPH', 'MYOF', 'NEAT1', 'GALNT1', 'PPP3CA', 'KYNU', 'RPL26', 'NMI', 'CYP24A1', 'HSP90AB1', 'TXN', 'MRPL13', 'PSMB1', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'FH', 'S100A6', 'MGST1', 'OCIAD2', 'ID3', 'NSMCE2', 'NAP1L1', 'SLC2A3', 'PSMD2', 'CKS1B', 'BTG1', 'GLRX', 'SFPQ', 'CEP170', 'UBE2C', 'RDX', 'FKBP3', 'MGST3', 'CENPA', 'RHOF', 'CCDC85B', 'TSPAN5', 'NR0B1', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'CD9', 'ADAM19', 'LDHA', 'DYNLL1', 'ADH5', 'CCNB1', 'CSRP1', 'IFITM2', 'ARL4A', 'FOXM1', 'NT5E', 'CDCA4', 'ATP5G1', 'TRIM7', 'RNF26', 'AKR1C3', 'GNL3', 'EREG', 'APLP2', 'PPP1CB', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'AJUBA', 'HMGA2', 'C15orf48', 'SLN', 'HNRNPD', 'HOXB8', 'CDC20', 'CPLX2', 'ANTXR1', 'UBB', 'NPM1', 'ISG20', 'NUP37', 'GPX2', 'FLNB', 'COL5A2', 'ULK1', 'PLEK2', 'PSMD8', 'NRG1', 'CHCHD10', 'AXL', 'LIMD2', 'TAGLN2', 'ANXA2', 'PMEPA1', 'EIF2S1', 'TNFRSF1A', 'FBXO2', 'PCSK1N', 'MT1X', 'GAPDH', 'MYL12B', 'TCEAL1', 'DERL1', 'PRSS23', 'F12', 'ELF3', 'REEP5', 'IGFBP7', 'TSFM', 'AREG', 'FDXR', 'S100A16', 'UPP1', 'HSP90AA1', 'NUPR1', 'COPB1', 'TUBB2A', 'TXNDC9', 'HSPB1', 'MLXIP', 'KRT18', 'ACTG1', 'RAN', 'ARL6IP1', 'EBNA1BP2', 'SERPINE2', 'CALM2', 'S100A11', 'RGS3', 'FABP5', 'NCOA7', 'BCL3', 'SLC3A2', 'CCT2', 'CAPG', 'SFN', 'MGLL', 'PLAUR', 'G6PD', 'RGS2', 'HELLS', 'ANXA1', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'CSTF3', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'FOXD1', 'CHST11', 'PDLIM5', 'WDR43', 'COL4A2', 'SRSF7', 'RPL22L1', 'DKC1', 'TXNRD1', 'PRDX1', 'BAX', 'MAP2K3', 'AKR1B1', 'SNRPA1', 'ARHGAP11A', 'PBX1', 'TGFBI', 'DUSP4', 'ORMDL2', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'CCNB2', 'SYT1', 'JUNB', 'FN1', 'HSPA1A', 'POLR2L', 'AGR2', 'HBEGF', 'BDNF', 'MALSU1', 'IGFBP3', 'DSE', 'HPGD', 'ACTB', 'KRT81', 'GCLC', 'SMAD3', 'NUDT19', 'SH3BGRL3', 'TUBA1C', 'ATF4', 'NUAK1', 'CDKN3', 'TOB1', 'RAB3B', 'ANXA4', 'GPX1', 'SNHG10', 'PACSIN3', 'PDGFC', 'SLC35F6', 'MOB3B', 'NAMPT', 'CLU', 'PKM', 'SAP30BP', 'HEXA', 'UBXN4', 'AP1M2', 'TCEAL8', 'PSMA5', 'ACTN1', 'FTL', 'SDC4', 'BLOC1S2', 'AKR1B10', 'CTNNAL1', 'PLK2', 'CDK1', 'MYO10', 'AATF', 'DDX39A', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'TMEM92', 'BIRC5', 'TSPAN15', 'HMGA1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'LBH', 'THRA', 'CAV1', 'PGD', 'VTN', 'MYL12A', 'NQO1', 'PSME2', 'KRT19', 'SERPINE1', 'CCDC59', 'P4HA3', 'VIM', 'FTH1', 'DNER', 'PGK1', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'TKT', 'AURKB', 'KRT8', 'AHNAK2', 'EIF1', 'TGM2', 'OLFM2', 'KRT7', 'S100A4', 'SDC1', 'CTSL', 'CCNE1', 'TMSB10', 'PTPRJ', 'FGFR1', 'JUN', 'TOP2A', 'S100A3', 'SNAPC1', 'MRPS22', 'SCG5', 'CCT5', 'RBP1', 'MORF4L2', 'HMGB2', 'MT2A', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'ID1', 'CCT3', 'VCAN', 'PDCD5', 'TUBA1A', 'CDC25B', 'ZFAS1', 'TRAM1', 'TUBB', 'INO80C', 'MORC4', 'PRNP', 'AP2M1', 'ANPEP', 'NPTX1', 'PSMD1', 'NOL7', 'MAP1LC3A', 'CXCL1', 'DOCK5', 'HSP90B1', 'MAF', 'ANXA3', 'DHRS3', 'MTHFD2', 'CDC42SE1', 'NUDC', 'SGK1', 'NPC2', 'STC1', 'MT-ND6', 'PSMA4', 'CD24', 'DHRS7', 'PRMT1', 'CD63', 'TPM2', 'COTL1', 'C1QBP', 'LMNA', 'NUP93', 'KRR1', 'NME1', 'UBC', 'CYB5A', 'RAET1G', 'LDHB', 'TIMP2', 'IGFBP4', 'NEMF', 'ALDH3A1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'PLOD2', 'MAP1B', 'HNRNPH1', 'COL4A1', 'HACD3', 'PRC1', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IMP'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEP', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'HMP', 'IEA'], ['IDA'], ['NAS', 'IEA'], ['IDA', 'IEA'], ['IMP'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IEA'], ['IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'NAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'NAS'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['IDA', 'IMP'], ['IBA', 'TAS', 'IEA'], ['HMP'], ['IMP'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IMP'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['HMP'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'IEP'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEP'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['NAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IMP'], ['ISS', 'IEA'], ['IEP', 'IBA'], ['IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IEP', 'ISS', 'NAS', 'IC'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA'], ['ISS', 'IEA'], ['IDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS', 'TAS'], ['NAS'], ['IEA'], ['HMP', 'ISS', 'TAS', 'IEA'], ['IEP'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IEP'], ['IMP', 'TAS'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['TAS', 'IEA'], ['IMP'], ['IEA'], ['IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IGI', 'ISS', 'IEA'], ['ISS'], ['IDA'], ['IMP', 'IEA'], ['TAS'], ['IMP', 'IEP', 'TAS', 'NAS'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IC'], ['NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IEA'], ['ISS', 'TAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['NAS'], ['IDA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS'], ['IDA', 'HMP', 'IEA'], ['IMP', 'IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IMP', 'NAS'], ['IDA', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['NAS'], ['IMP', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IC', 'IEA'], ['ISS', 'IEA'], ['NAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IEP'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEP', 'ISS'], ['IEP', 'IEA'], ['IEA'], ['TAS'], ['IMP'], ['NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC'], ['IGI', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IBA', 'TAS'], ['IMP', 'IBA'], ['IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['IDA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IEP', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEP'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['NAS'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IEP', 'ISS'], ['IMP', 'ISS', 'IEA'], ['IDA', 'ISS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'TAS', 'NAS'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISO', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IC', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IC', 'IEA'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'HTP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'IMP', 'IBA', 'TAS'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['HDA', 'IBA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['ISA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['HDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IBA'], ['EXP', 'IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISA', 'IC', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['ISA', 'IC', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'IMP', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IGI', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'ISS', 'ISO', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['EXP', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['EXP', 'IDA', 'ISA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IBA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'IPI', 'IMP', 'ISA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'TAS'], ['IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IPI', 'ISS', 'ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'TAS'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2728,42 +2728,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GO:0044419</t>
+          <t>GO:0008637</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>biological process involved in interspecies interaction between organisms</t>
+          <t>apoptotic mitochondrial changes</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02761063960713716</v>
+        <v>0.009072875784810806</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>"Any process evolved to enable an interaction with an organism of a different species." [GOC:cc]</t>
+          <t>"The morphological and physiological alterations undergone by mitochondria during apoptosis." [GOC:mah, GOC:mtg_apoptosis]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>312</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I18" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
         <v>2717</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1837160751565762</v>
+        <v>0.03541666666666667</v>
       </c>
       <c r="L18" t="n">
-        <v>0.282051282051282</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2772,64 +2772,64 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>['GO:0008150']</t>
+          <t>['GO:0006915', 'GO:0007005']</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['ANXA3', 'NQO1', 'EDN1', 'OCIAD2', 'ISG20', 'ACTG1', 'IER3', 'CLU', 'CAV1', 'HSPA1A', 'CCL2', 'JUN', 'CCDC80', 'EREG', 'F12', 'SLC3A2', 'CXCL5', 'ANPEP', 'HLA-C', 'ENO1', 'HSP90AB1', 'TRIML2', 'HPGD', 'HSPD1', 'CD24', 'DDX56', 'CXCL1', 'ATP1B1', 'KRT8', 'CCT5', 'EPHB2', 'HSPB1', 'BAX', 'C15orf48', 'CYBA', 'KYNU', 'YWHAE', 'IFITM2', 'STMN1', 'HMGB1', 'ANXA1', 'CADM1', 'FLNB', 'GPX1', 'AXL', 'CDC42', 'CDK6', 'NMI', 'RAET1G', 'LGALS1', 'CTSL', 'GAPDH', 'SMAD3', 'MAP2K3', 'COTL1', 'SAP30BP', 'SFPQ', 'ADH5', 'HMGA2', 'TUBB', 'CDK1', 'SERPINE1', 'AKAP12', 'PVR', 'HMGB3', 'HMGB2', 'TNFRSF1A', 'PRSS3', 'RNF26', 'NPC2', 'ITGA2', 'FN1', 'TUBB4B', 'FLOT1', 'TRIM7', 'PYCARD', 'SFN', 'VIM', 'HSP90AA1', 'GSN', 'CXCL8', 'BCL3', 'GSTP1', 'AURKB', 'KPNA2', 'SQSTM1', 'C1QBP', 'PRDX1']</t>
+          <t>['HSPD1', 'PYCARD', 'BCL2A1', 'CHCHD10', 'SFN', 'PLAUR', 'BAX', 'HSPA1A', 'GCLC', 'SMAD3', 'GPX1', 'SLC35F6', 'CLU', 'BLOC1S2', 'IER3', 'NPTX1', 'LMNA']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[['IDA'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IEP', 'IEA'], ['IDA', 'IMP', 'IGI'], ['IMP', 'IEA'], ['IEP', 'ISS', 'IBA', 'NAS'], ['IDA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['IMP'], ['IBA'], ['IEA'], ['IEA'], ['IEP'], ['IMP'], ['IBA'], ['IEA'], ['IDA', 'IMP'], ['ISS'], ['IDA', 'IMP'], ['IBA'], ['IEA'], ['IEA'], ['IEP'], ['IEA'], ['IEP'], ['IDA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IEP'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IMP', 'IEA'], ['IEP'], ['IMP', 'ISS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEP'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IEP'], ['NAS'], ['IEA'], ['IMP', 'IGI'], ['IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['IEA'], ['TAS'], ['IDA'], ['IEP'], ['IEA'], ['IDA'], ['NAS'], ['IMP'], ['IDA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA'], ['IMP', 'IEA'], ['IDA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IEA'], ['ISS'], ['IDA'], ['IMP'], ['IDA'], ['IDA', 'IMP', 'IEA'], ['IEA']]</t>
+          <t>[['IBA'], ['IDA'], ['IBA'], ['IMP'], ['IDA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IEA'], ['IMP'], ['IMP'], ['TAS', 'IC'], ['IDA'], ['IEA'], ['IEA'], ['IEA']]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GO:0030141</t>
+          <t>GO:0032879</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>secretory granule</t>
+          <t>regulation of localization</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03488599278220982</v>
+        <v>0.01533072953068872</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>"A small subcellular vesicle, surrounded by a membrane, that is formed from the Golgi apparatus and contains a highly concentrated protein destined for secretion. Secretory granules move towards the periphery of the cell and upon stimulation, their membranes fuse with the cell membrane, and their protein load is exteriorized. Processing of the contained protein may take place in secretory granules." [GOC:mah, ISBN:0198506732]</t>
+          <t>"Any process that modulates the frequency, rate or extent of any process in which a cell, a substance, or a cellular entity is transported to, or maintained in, a specific location." [GOC:mah]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>202</v>
+        <v>363</v>
       </c>
       <c r="H19" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I19" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
         <v>2717</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1315240083507307</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3118811881188119</v>
+        <v>0.2754820936639119</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2838,64 +2838,64 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>['GO:0012505', 'GO:0099503']</t>
+          <t>['GO:0050789', 'GO:0051179']</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'DYNLL1', 'EDN1', 'CLU', 'CAV1', 'PLAUR', 'HSPA1A', 'SCG5', 'S100A11', 'ANPEP', 'HLA-C', 'HSP90AB1', 'TIMP2', 'TNFAIP6', 'B4GALT1', 'ACTN1', 'HSPD1', 'PKM', 'PCSK1N', 'CCT2', 'CXCL1', 'FTL', 'GAL', 'CYBA', 'SERPINE2', 'ANXA4', 'FABP5', 'HMGB1', 'APLP2', 'RHOF', 'CDC42', 'FTH1', 'SVIP', 'CTSL', 'COPB1', 'CD9', 'JUP', 'PSMB1', 'COTL1', 'PSMD2', 'ANXA2', 'TUBB', 'MGST1', 'SERPINE1', 'CDA', 'PRSS3', 'SYT1', 'NPC2', 'FN1', 'TUBB4B', 'TMSB4X', 'PSMA5', 'PSMD1', 'PTPRJ', 'COL1A1', 'PYCARD', 'HEXA', 'HSP90AA1', 'GSN', 'GSTP1', 'SLC2A3']</t>
+          <t>['CTNNB1', 'TRIB3', 'GSN', 'PYCARD', 'CES1', 'ARPC3', 'ASPH', 'MYOF', 'PPP3CA', 'HSP90AB1', 'TXN', 'YWHAE', 'SOX4', 'RDX', 'IL11', 'RBP4', 'ATP1B1', 'GNL3', 'KCNN4', 'FLOT1', 'EDN1', 'SLN', 'FXYD5', 'CPLX2', 'KCNG1', 'CCL2', 'NRG1', 'CHCHD10', 'AXL', 'ANXA2', 'TNFRSF1A', 'REEP5', 'HSP90AA1', 'ACTG1', 'RAN', 'ARL6IP1', 'SERPINE2', 'CALM2', 'FABP5', 'CCT2', 'SFN', 'G6PD', 'RGS2', 'ANXA1', 'SQSTM1', 'EPHB2', 'TNFAIP6', 'CYBA', 'HMGB1', 'DKC1', 'BAX', 'OSBPL8', 'SVIP', 'SYT1', 'HSPA1A', 'AGR2', 'BDNF', 'ACTB', 'GCLC', 'SMAD3', 'ATF4', 'RAB3B', 'ITGA3', 'PACSIN3', 'SLC35F6', 'CLU', 'SDC4', 'TM7SF3', 'CDK1', 'DDX39A', 'TMEM59', 'BIRC5', 'S100A10', 'CDC42', 'TMSB4X', 'CAV1', 'VTN', 'SERPINE1', 'IER3', 'GAL', 'AURKB', 'TGM2', 'GSTO1', 'SDC1', 'CCNE1', 'PTPRJ', 'FGFR1', 'ITGA2', 'SCG5', 'CCT5', 'CDH2', 'CCT3', 'PRNP', 'AP2M1', 'SGK1', 'STC1', 'CD63', 'LMNA', 'JUP', 'MAP1B']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'IMP'], ['IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['TAS'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS']]</t>
+          <t>[['IDA'], ['ISS', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['IDA', 'ISS', 'TAS'], ['IBA'], ['ISS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IDA'], ['ISS', 'IEA'], ['IGI', 'IBA'], ['IDA'], ['IMP'], ['IDA', 'IGI', 'ISS', 'IEA'], ['IMP'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'ISS'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS'], ['IDA', 'IMP'], ['IMP'], ['IMP'], ['IDA', 'IBA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['ISS'], ['ISS', 'IEA'], ['IMP', 'IEA'], ['IMP'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['IEA'], ['IMP', 'HMP'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['ISS', 'IEA'], ['IMP', 'IBA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IMP'], ['TAS'], ['IMP', 'IGI', 'ISS', 'TAS', 'IEA'], ['IEA'], ['NAS'], ['IEA'], ['IDA', 'IMP'], ['IDA'], ['ISS', 'IBA', 'IEA'], ['IMP'], ['IGI', 'ISS'], ['IMP'], ['IMP'], ['IDA', 'IMP', 'IEA'], ['IDA'], ['IDA'], ['NAS', 'IEA'], ['NAS'], ['ISS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'NAS'], ['IDA', 'IEA'], ['IDA', 'IC'], ['IMP'], ['IEA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['HMP'], ['IEA'], ['HMP'], ['ISS', 'IEA'], ['IMP', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IMP'], ['IEA'], ['IDA'], ['IEA']]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GO:0030055</t>
+          <t>GO:0044419</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cell-substrate junction</t>
+          <t>biological process involved in interspecies interaction between organisms</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.04141964385164288</v>
+        <v>0.01608775583946252</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>"A cell junction that forms a connection between a cell and the extracellular matrix." [GOC:aruk, GOC:bc, GOC:hb, GOC:mah, PMID:10419689, PMID:1643657, PMID:16805308, PMID:26923917, PMID:8314002]</t>
+          <t>"Any process evolved to enable an interaction with an organism of a different species." [GOC:cc]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>308</v>
       </c>
       <c r="H20" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I20" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="J20" t="n">
         <v>2717</v>
       </c>
       <c r="K20" t="n">
-        <v>0.09394572025052192</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3515625</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2904,83 +2904,347 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>['GO:0070161']</t>
+          <t>['GO:0008150']</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['CD44', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PLAUR', 'HSPA1A', 'ACTB', 'HSPA5', 'TSPAN4', 'CSRP1', 'TM4SF20', 'TNS3', 'CTTN', 'ACTN1', 'HSP90B1', 'HMGA1', 'HSPB1', 'HACD3', 'RHOU', 'YWHAE', 'ANXA1', 'TGM2', 'AJUBA', 'FLNB', 'CDC42', 'ITGA3', 'NPM1', 'CD9', 'ILK', 'JUP', 'ARPC3', 'CDH2', 'CNN3', 'AKAP12', 'PVR', 'RSU1', 'ITGA2', 'RDX', 'FLOT1', 'CTNNB1', 'VIM', 'REXO2', 'GSN', 'PPP1CB']</t>
+          <t>['HSPD1', 'CDK6', 'GSN', 'TUBB4B', 'PYCARD', 'CADM1', 'HMGB3', 'GSTP1', 'KYNU', 'NMI', 'HSP90AB1', 'ENO1', 'HLA-C', 'YWHAE', 'OCIAD2', 'SFPQ', 'AKAP12', 'ADH5', 'IFITM2', 'ATP1B1', 'TRIM7', 'RNF26', 'EREG', 'FLOT1', 'EDN1', 'PRSS3', 'HMGA2', 'C15orf48', 'CCL2', 'ISG20', 'FLNB', 'AXL', 'TNFRSF1A', 'GAPDH', 'F12', 'HSP90AA1', 'HSPB1', 'ACTG1', 'BCL3', 'SLC3A2', 'SFN', 'CXCL5', 'ANXA1', 'SQSTM1', 'EPHB2', 'DDX56', 'CYBA', 'STMN1', 'HMGB1', 'PRDX1', 'BAX', 'FN1', 'HSPA1A', 'HPGD', 'SMAD3', 'GPX1', 'CLU', 'SAP30BP', 'CDK1', 'DDX39A', 'CDC42', 'CAV1', 'NQO1', 'SERPINE1', 'VIM', 'IER3', 'LGALS1', 'AURKB', 'KRT8', 'CTSL', 'JUN', 'ITGA2', 'CCT5', 'PVR', 'HMGB2', 'TUBB', 'ANPEP', 'HSP90B1', 'ANXA3', 'TRIML2', 'CXCL8', 'NPC2', 'CD24', 'COTL1', 'C1QBP', 'RAET1G', 'CCDC80', 'KPNA2']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['ISS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA']]</t>
+          <t>[['IDA', 'IMP'], ['IEP'], ['IMP', 'IEA'], ['NAS'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA'], ['IEA'], ['ISS'], ['IDA'], ['IMP', 'ISS', 'IEA'], ['IMP'], ['IEP'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['TAS'], ['IDA', 'IEP'], ['IEA'], ['IEP', 'ISS', 'IBA', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA'], ['IEP'], ['IEA'], ['IDA', 'IEA'], ['IMP'], ['IDA'], ['IBA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEP'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEP', 'IEA'], ['IEP'], ['IEA'], ['IDA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IGI'], ['IEA'], ['IMP', 'IGI'], ['IMP', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IEP'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IEP', 'ISS', 'IEA'], ['NAS'], ['IEA'], ['IDA'], ['IDA'], ['IBA'], ['IDA', 'IMP', 'IBA'], ['IEP'], ['ISS'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IDA'], ['IEA'], ['IMP']]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>GO:BP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GO:0048522</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>positive regulation of cellular process</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.02004761179740784</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>"Any process that activates or increases the frequency, rate or extent of a cellular process, any of those that are carried out at the cellular level, but are not necessarily restricted to a single cell. For example, cell communication occurs among more than one cell, but occurs at the cellular level." [GOC:jid]</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1038</v>
+      </c>
+      <c r="H21" t="n">
+        <v>480</v>
+      </c>
+      <c r="I21" t="n">
+        <v>232</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2717</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2235067437379576</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>query_1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>['GO:0009987', 'GO:0048518', 'GO:0050794']</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>['HSPA2', 'CTNNB1', 'NNMT', 'FSTL3', 'HSPD1', 'CDK6', 'CMTM3', 'TRIB3', 'FSCN1', 'TNS3', 'HSPA5', 'GSN', 'PYCARD', 'CADM1', 'CES1', 'DLGAP5', 'GSTP1', 'ASPH', 'TNFRSF12A', 'NEAT1', 'PPP3CA', 'RPL26', 'NMI', 'HSP90AB1', 'TXN', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'SOX4', 'RIN2', 'S100A6', 'OCIAD2', 'ID3', 'NSMCE2', 'NAP1L1', 'KCNMA1', 'BTG1', 'SFPQ', 'UBE2C', 'RDX', 'IL11', 'RBP4', 'TSPAN5', 'BCL2A1', 'RASSF10', 'PRMT5', 'AKAP12', 'ADAM19', 'CCNB1', 'FOXM1', 'ATP1B1', 'CDCA4', 'CA8', 'AKR1C3', 'GNL3', 'EREG', 'KCNN4', 'FLOT1', 'COL1A1', 'EDN1', 'RSPO3', 'AJUBA', 'HMGA2', 'SLN', 'HNRNPD', 'FXYD5', 'CDC20', 'LAMC2', 'UBB', 'NPM1', 'CCL2', 'ULK1', 'PLEK2', 'NRG1', 'CHCHD10', 'AXL', 'ANXA2', 'EIF2S1', 'TNFRSF1A', 'GAPDH', 'IGFBP6', 'DERL1', 'F12', 'ELF3', 'AREG', 'HSP90AA1', 'NUPR1', 'AVPI1', 'HSPB1', 'MLXIP', 'ACTG1', 'RAN', 'ARL6IP1', 'SERPINE2', 'CALM2', 'S100A11', 'FABP5', 'NCOA7', 'BCL3', 'CCT2', 'SFN', 'PHLDA3', 'PLAUR', 'CXCL5', 'G6PD', 'RGS2', 'ANXA1', 'UBE2S', 'SQSTM1', 'B4GALT1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'MICAL2', 'ZBED2', 'HMGB1', 'CD44', 'FOXD1', 'WDR43', 'DKC1', 'BAX', 'MAP2K3', 'PBX1', 'OSBPL8', 'EIF4A3', 'SULT2B1', 'SVIP', 'SYT1', 'JUNB', 'LTBP3', 'FN1', 'HSPA1A', 'AGR2', 'HBEGF', 'BDNF', 'IGFBP3', 'HPGD', 'ACTB', 'GCLC', 'SMAD3', 'ATF4', 'TOB1', 'ITGA3', 'GPX1', 'PACSIN3', 'PDGFC', 'SLC35F6', 'NAMPT', 'CLU', 'PKM', 'ACTN1', 'SDC4', 'BLOC1S2', 'TM7SF3', 'MALAT1', 'PLK2', 'CDK1', 'MYO10', 'ETS2', 'TMEM59', 'TPM1', 'AMIGO2', 'CTTN', 'BIRC5', 'HMGA1', 'S100A10', 'CDC42', 'TMSB4X', 'PSMC4', 'LBH', 'THRA', 'CAV1', 'VTN', 'SERPINE1', 'VIM', 'IER3', 'LGALS1', 'EZH2', 'GAL', 'AURKB', 'TGM2', 'GSTO1', 'OLFM2', 'CBR1', 'S100A4', 'SDC1', 'CCNE1', 'PTPRJ', 'FGFR1', 'JUN', 'ITGA2', 'TOP2A', 'CCT5', 'MORF4L2', 'PVR', 'HMGB2', 'CDH2', 'CCT3', 'NRP2', 'PDCD5', 'CDC25B', 'INO80C', 'PRNP', 'AP2M1', 'DOCK5', 'HSP90B1', 'CCPG1', 'MAF', 'ANXA3', 'CXCL8', 'IL32', 'CD24', 'PRMT1', 'CD63', 'C1QBP', 'LMNA', 'NUP93', 'NME1', 'RSU1', 'RAET1G', 'CCDC80', 'IGFBP4', 'CREM', 'JUP', 'MAP1B', 'PRC1', 'FAM89B', 'ILK', 'KPNA2', 'SEMA3C']</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[['IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['ISS', 'IBA'], ['IDA', 'IMP', 'IEA'], ['IBA'], ['IMP', 'TAS', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA'], ['IMP'], ['NAS'], ['ISS'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS'], ['IMP'], ['IDA', 'IMP', 'IGI'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP'], ['NAS'], ['ISS'], ['IEA'], ['IMP'], ['ISS', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'NAS'], ['IDA', 'IMP'], ['IDA', 'IMP', 'TAS'], ['IMP', 'IGI', 'ISS', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'ISS'], ['IMP'], ['IBA'], ['ISS', 'IEA'], ['IGI', 'NAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IGI', 'ISS'], ['IEA'], ['IEA'], ['IDA', 'IMP'], ['IMP'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IMP', 'IGI', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['ISS'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IBA'], ['IMP', 'ISS', 'IBA'], ['IDA', 'ISS', 'ISO', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'TAS'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IMP', 'IEP', 'ISS', 'IEA'], ['IDA'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP'], ['IMP'], ['IMP'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IMP'], ['IEA'], ['IDA'], ['IDA', 'IMP', 'IEA'], ['IMP'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IGI', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IMP'], ['IMP'], ['IDA', 'IMP', 'ISS'], ['IDA', 'IMP', 'IBA'], ['ISS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IMP'], ['IMP', 'IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP'], ['IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IDA', 'NAS'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['IDA', 'HMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IMP', 'IBA'], ['ISS'], ['IBA', 'IEA'], ['IMP', 'ISS'], ['TAS', 'NAS'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'IGI'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'HMP', 'IEA'], ['IDA', 'IMP'], ['IDA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IMP'], ['IDA'], ['IDA', 'IBA'], ['IMP'], ['IMP', 'IBA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IMP', 'IEA'], ['IDA', 'NAS'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['TAS'], ['IDA', 'IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISO'], ['IMP', 'IGI', 'ISS', 'IEA'], ['IEA'], ['IMP'], ['IDA'], ['IMP', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IDA', 'IMP'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'ISS'], ['IEA'], ['IDA', 'IEA'], ['IMP'], ['IMP'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IGI', 'IBA', 'IC'], ['IEA'], ['IMP'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'IEA'], ['IDA'], ['ISS', 'IBA', 'IEA']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GO:BP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GO:0007155</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cell adhesion</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.03050883646956874</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>"The attachment of a cell, either to another cell or to an underlying substrate such as the extracellular matrix, via cell adhesion molecules." [GOC:hb, GOC:pf]</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>312</v>
+      </c>
+      <c r="H22" t="n">
+        <v>480</v>
+      </c>
+      <c r="I22" t="n">
+        <v>88</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2717</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>query_1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>['GO:0009987']</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>['CTNNB1', 'FSTL3', 'HSPD1', 'CDK6', 'PYCARD', 'CADM1', 'TNFRSF12A', 'PPP3CA', 'PERP', 'SOX4', 'RIN2', 'CNN3', 'RDX', 'CD9', 'ADAM19', 'CSRP1', 'NT5E', 'ATP1B1', 'PPP1CB', 'FLOT1', 'COL1A1', 'AJUBA', 'FXYD5', 'LAMC2', 'ANTXR1', 'CCL2', 'NRG1', 'AXL', 'ANXA2', 'IGFBP7', 'HSPB1', 'KRT18', 'ACTG1', 'SERPINE2', 'S100A11', 'SFN', 'PLAUR', 'ANXA1', 'B4GALT1', 'EPHB2', 'TNFAIP6', 'HMGB1', 'RND1', 'CD44', 'PDLIM5', 'TGFBI', 'FN1', 'AGR2', 'ACTB', 'SMAD3', 'NUAK1', 'ITGA3', 'ITGA11', 'ACTN1', 'SDC4', 'CTNNAL1', 'MYO10', 'AATF', 'TPM1', 'AMIGO2', 'CTTN', 'S100A10', 'CDC42', 'SPOCK1', 'CAV1', 'VTN', 'MYL12A', 'SERPINE1', 'LGALS1', 'TGM2', 'PTPRJ', 'ITGA2', 'PVR', 'CDH2', 'NRP2', 'VCAN', 'PRNP', 'DOCK5', 'CXCL8', 'IL32', 'CD24', 'CD63', 'C1QBP', 'NTN4', 'RSU1', 'CCDC80', 'JUP', 'ILK']</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>[['IMP', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IMP', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IEA'], ['IBA', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['IMP'], ['IDA', 'IEA'], ['IDA'], ['HMP'], ['IDA'], ['IEA'], ['IDA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['NAS'], ['IEA'], ['IDA'], ['ISS', 'TAS'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['HMP'], ['IEA'], ['IMP', 'HMP'], ['ISS', 'IEA'], ['IEA'], ['IMP'], ['IDA', 'IMP'], ['IDA', 'IEA'], ['IEA'], ['IMP'], ['IEA'], ['IDA', 'IMP'], ['IDA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP'], ['HMP', 'NAS'], ['IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IMP'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS'], ['ISS', 'IBA', 'IEA'], ['ISS'], ['IMP'], ['IDA'], ['IDA', 'NAS'], ['IDA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['NAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP'], ['IMP'], ['IBA'], ['IMP'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'HMP', 'IBA', 'TAS']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GO:BP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GO:0009605</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>response to external stimulus</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.03225265444694426</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>"Any process that results in a change in state or activity of a cell or an organism (in terms of movement, secretion, enzyme production, gene expression, etc.) as a result of an external stimulus." [GOC:hb]</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>425</v>
+      </c>
+      <c r="H23" t="n">
+        <v>480</v>
+      </c>
+      <c r="I23" t="n">
+        <v>112</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2717</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2635294117647059</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>query_1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>['GO:0050896']</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>['CTNNB1', 'HSPD1', 'CDA', 'CDK6', 'CMTM3', 'GSN', 'TUBB4B', 'PYCARD', 'CADM1', 'HMGB3', 'GSTP1', 'NEAT1', 'KYNU', 'NMI', 'ENO1', 'PERP', 'HLA-C', 'YWHAE', 'OCIAD2', 'SFPQ', 'AKAP12', 'CD9', 'ADH5', 'IFITM2', 'NT5E', 'ATP1B1', 'TRIM7', 'RNF26', 'EREG', 'PPP1CB', 'FLOT1', 'COL1A1', 'EDN1', 'PRSS3', 'HMGA2', 'C15orf48', 'CCL2', 'ISG20', 'FLNB', 'NRG1', 'AXL', 'ANXA2', 'TNFRSF1A', 'GAPDH', 'F12', 'HSP90AA1', 'NUPR1', 'HSPB1', 'ACTG1', 'SERPINE2', 'BCL3', 'SFN', 'MGLL', 'PLAUR', 'CXCL5', 'ANXA1', 'SQSTM1', 'EPHB2', 'DDX56', 'TNFAIP6', 'CYBA', 'STMN1', 'HMGB1', 'PRDX1', 'BAX', 'HSPA1A', 'HBEGF', 'HPGD', 'GCLC', 'SMAD3', 'GPX1', 'CLU', 'SAP30BP', 'PLK2', 'DDX39A', 'CDC42', 'TMSB4X', 'CAV1', 'VTN', 'NQO1', 'SERPINE1', 'VIM', 'IER3', 'LGALS1', 'AURKB', 'KRT8', 'S100A4', 'PTPRJ', 'FGFR1', 'ITGA2', 'CCT5', 'PVR', 'HMGB2', 'CDH2', 'NRP2', 'TUBA1A', 'TUBB', 'CXCL1', 'HSP90B1', 'ANXA3', 'TRIML2', 'CXCL8', 'NPC2', 'CD24', 'CD63', 'COTL1', 'C1QBP', 'RAET1G', 'CCDC80', 'JUP', 'MAP1B', 'SEMA3C']</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>[['TAS'], ['IDA'], ['IEA'], ['IEP'], ['IEA'], ['IMP', 'ISS', 'IEA'], ['NAS'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA'], ['IEA'], ['ISS', 'NAS'], ['IMP'], ['IDA'], ['IMP', 'ISS', 'IEA'], ['IEP'], ['IMP'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['IEP'], ['IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IEA'], ['IMP', 'IEP', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['IMP', 'IEP'], ['IEA'], ['IDA', 'ISS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['ISS'], ['TAS', 'NAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA'], ['IMP', 'IEA'], ['IDA'], ['IDA', 'IBA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEP'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IDA'], ['IMP'], ['IMP'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEP', 'IEA'], ['IEP'], ['TAS'], ['IDA'], ['IEA'], ['IDA', 'IMP'], ['IDA', 'IMP'], ['NAS', 'IC'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC'], ['IMP', 'IEA'], ['IEA'], ['IDA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['IEA'], ['IEP'], ['IDA', 'IMP'], ['IDA', 'IEP', 'ISS', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['NAS'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['IBA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IEP'], ['ISS'], ['IMP'], ['IEA'], ['IDA', 'IMP', 'IEA'], ['IDA'], ['IEA'], ['IDA'], ['IEA'], ['IBA']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>GO:CC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>GO:0005925</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>focal adhesion</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0.04141964385164288</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0.04407518735654439</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>"A cell-substrate junction that anchors the cell to the extracellular matrix and that forms a point of termination of actin filaments. In insects focal adhesion has also been referred to as hemi-adherens junction (HAJ)." [GOC:aruk, GOC:bc, ISBN:0124325653, ISBN:0815316208, PMID:10419689, PMID:12191915, PMID:15246682, PMID:1643657, PMID:16805308, PMID:19197329, PMID:23033047, PMID:26923917, PMID:28796323, PMID:8314002]</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G24" t="n">
         <v>128</v>
       </c>
-      <c r="H21" t="n">
-        <v>479</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H24" t="n">
+        <v>480</v>
+      </c>
+      <c r="I24" t="n">
         <v>45</v>
       </c>
-      <c r="J21" t="n">
-        <v>2717</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.09394572025052192</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J24" t="n">
+        <v>2717</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.3515625</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>query_1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>query_1</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>['GO:0030055']</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>['CD44', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PLAUR', 'HSPA1A', 'ACTB', 'HSPA5', 'TSPAN4', 'CSRP1', 'TM4SF20', 'TNS3', 'CTTN', 'ACTN1', 'HSP90B1', 'HMGA1', 'HSPB1', 'HACD3', 'RHOU', 'YWHAE', 'ANXA1', 'TGM2', 'AJUBA', 'FLNB', 'CDC42', 'ITGA3', 'NPM1', 'CD9', 'ILK', 'JUP', 'ARPC3', 'CDH2', 'CNN3', 'AKAP12', 'PVR', 'RSU1', 'ITGA2', 'RDX', 'FLOT1', 'CTNNB1', 'VIM', 'REXO2', 'GSN', 'PPP1CB']</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['ISS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA']]</t>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['CTNNB1', 'RHOU', 'REXO2', 'TNS3', 'HSPA5', 'GSN', 'TM4SF20', 'ARPC3', 'YWHAE', 'CNN3', 'TSPAN4', 'RDX', 'AKAP12', 'CD9', 'CSRP1', 'PPP1CB', 'FLOT1', 'AJUBA', 'NPM1', 'FLNB', 'HSPB1', 'ACTG1', 'PLAUR', 'ANXA1', 'CD44', 'HSPA1A', 'ACTB', 'ITGA3', 'ITGA11', 'ACTN1', 'SDC4', 'CTTN', 'HMGA1', 'CDC42', 'CAV1', 'VIM', 'TGM2', 'ITGA2', 'PVR', 'CDH2', 'HSP90B1', 'RSU1', 'JUP', 'HACD3', 'ILK']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>[['HDA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['ISS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IMP', 'HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA']]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GO:CC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GO:0030055</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cell-substrate junction</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.04407518735654439</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>"A cell junction that forms a connection between a cell and the extracellular matrix." [GOC:aruk, GOC:bc, GOC:hb, GOC:mah, PMID:10419689, PMID:1643657, PMID:16805308, PMID:26923917, PMID:8314002]</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>128</v>
+      </c>
+      <c r="H25" t="n">
+        <v>480</v>
+      </c>
+      <c r="I25" t="n">
+        <v>45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2717</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3515625</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>query_1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>['GO:0070161']</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['CTNNB1', 'RHOU', 'REXO2', 'TNS3', 'HSPA5', 'GSN', 'TM4SF20', 'ARPC3', 'YWHAE', 'CNN3', 'TSPAN4', 'RDX', 'AKAP12', 'CD9', 'CSRP1', 'PPP1CB', 'FLOT1', 'AJUBA', 'NPM1', 'FLNB', 'HSPB1', 'ACTG1', 'PLAUR', 'ANXA1', 'CD44', 'HSPA1A', 'ACTB', 'ITGA3', 'ITGA11', 'ACTN1', 'SDC4', 'CTTN', 'HMGA1', 'CDC42', 'CAV1', 'VIM', 'TGM2', 'ITGA2', 'PVR', 'CDH2', 'HSP90B1', 'RSU1', 'JUP', 'HACD3', 'ILK']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>[['HDA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['ISS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IMP', 'HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3088,42 +3352,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GO:0031982</t>
+          <t>GO:0005615</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vesicle</t>
+          <t>extracellular space</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.441883781795618e-05</v>
+        <v>5.736043351388936e-06</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>"Any small, fluid-filled, spherical organelle enclosed by membrane." [GOC:mah, GOC:pz, GOC:vesicles]</t>
+          <t>"That part of a multicellular organism outside the cells proper, usually taken to be outside the plasma membranes, and occupied by fluid." [ISBN:0198547684]</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>732</v>
+        <v>694</v>
       </c>
       <c r="H2" t="n">
         <v>464</v>
       </c>
       <c r="I2" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J2" t="n">
         <v>2717</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3900862068965517</v>
+        <v>0.3771551724137931</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2472677595628415</v>
+        <v>0.2521613832853026</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -3132,64 +3396,64 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>['GO:0043227']</t>
+          <t>['GO:0005576', 'GO:0110165']</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'PTGR1', 'FURIN', 'OCIAD2', 'ACTG1', 'UBB', 'GNPNAT1', 'SDC4', 'CAV1', 'CLU', 'PLAUR', 'GLRX', 'NAP1L1', 'GLIPR1', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'TSPAN4', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'COPZ2', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'HSP90AB1', 'BMP1', 'PSMB3', 'TIMP2', 'CTTN', 'IGFBP7', 'B4GALT1', 'GRAMD1A', 'KRT7', 'PSME2', 'HSPA8', 'PSMD14', 'PKM', 'TKT', 'S100A16', 'GIP', 'PDIA6', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'CMTM3', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'JAK1', 'GAL', 'SCCPDH', 'CYBA', 'GABARAPL1', 'F2RL1', 'YWHAE', 'PMEPA1', 'SERPINE2', 'ALDH1A1', 'DSE', 'G6PD', 'MYOF', 'STMN1', 'ADGRG1', 'HMGB1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'TGM2', 'RUVBL2', 'GPRC5A', 'TGFBR1', 'FSCN1', 'APLP2', 'DKK1', 'FLNB', 'RHOF', 'FGFR1', 'EIF6', 'RHOD', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MT3', 'ILF2', 'MYL6', 'CALM2', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SYT13', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'LTBP3', 'RIN2', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'TXNRD1', 'TGFBI', 'COTL1', 'MFSD12', 'EZR', 'PSMD2', 'ARPC3', 'SH3KBP1', 'NPTX1', 'GOLIM4', 'PODXL', 'ANXA2', 'ANTXR1', 'TUBB', 'S100A6', 'TUBA4A', 'CDK1', 'MGST1', 'SERPINE1', 'CDA', 'ECH1', 'UBC', 'SKIL', 'RAP2B', 'PSMA4', 'TUBA1C', 'TSPAN15', 'PRSS3', 'SYT1', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'TMSB4X', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'RAB3B', 'COL4A2', 'ITGA5', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1', 'PDIA4']</t>
+          <t>['HSPA2', 'HAPLN3', 'CTNNB1', 'PPIB', 'MYL6', 'FSTL3', 'ANGPTL4', 'TUBA4A', 'METRN', 'EIF6', 'CMTM3', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'LTBP4', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'TIMP4', 'YWHAE', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'IL11', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'DMKN', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'CNTN1', 'RSPO3', 'PRSS3', 'DKK1', 'GPRC5A', 'LAMC2', 'UBB', 'CCL2', 'FLNB', 'COL5A2', 'AXL', 'S100A13', 'ANXA2', 'RUVBL2', 'TNFRSF1A', 'PCSK1N', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'GIP', 'HSPB1', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'CXCL5', 'G6PD', 'MMP15', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'HMGB1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'TFPI2', 'PRDX1', 'TXNRD1', 'AKR1B1', 'CXCL2', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'SRGN', 'IGFBP3', 'ACTB', 'KRT81', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'COL22A1', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'NMB', 'COL5A1', 'CDK1', 'PTHLH', 'GLIPR1', 'S100A10', 'CDC42', 'SPOCK1', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'CCT5', 'PVR', 'HMGB2', 'PDCD5', 'VCAN', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'CXCL1', 'ANXA3', 'BMP1', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'RAET1G', 'MT3', 'LDHB', 'TIMP2', 'ADGRG1', 'IGFBP4', 'ALDH3A1', 'ECH1', 'JUP', 'COL4A1', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA'], ['IEA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['TAS'], ['IBA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['HDA', 'IEA'], ['IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IEA'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['HDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'IEA'], ['TAS'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'IBA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['HDA'], ['ISS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IBA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IEA']]</t>
+          <t>[['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['IDA', 'IBA'], ['IDA', 'IBA'], ['HDA', 'IBA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IBA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'ISS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['IBA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['ISS'], ['IBA'], ['HDA'], ['TAS'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['TAS'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['TAS', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['IEA'], ['HDA'], ['IBA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GO:0005615</t>
+          <t>GO:0007155</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>extracellular space</t>
+          <t>cell adhesion</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.530226396665426e-05</v>
+        <v>6.900794287382929e-06</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>"That part of a multicellular organism outside the cells proper, usually taken to be outside the plasma membranes, and occupied by fluid." [ISBN:0198547684]</t>
+          <t>"The attachment of a cell, either to another cell or to an underlying substrate such as the extracellular matrix, via cell adhesion molecules." [GOC:hb, GOC:pf]</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>696</v>
+        <v>312</v>
       </c>
       <c r="H3" t="n">
         <v>464</v>
       </c>
       <c r="I3" t="n">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="J3" t="n">
         <v>2717</v>
       </c>
       <c r="K3" t="n">
-        <v>0.375</v>
+        <v>0.2068965517241379</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -3198,64 +3462,64 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>['GO:0005576', 'GO:0110165']</t>
+          <t>['GO:0009987']</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'SPOCK1', 'LAMC2', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'COL5A1', 'SDC4', 'CLU', 'CCL2', 'IL32', 'GLRX', 'GLIPR1', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'CXCL5', 'DMKN', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'TFPI2', 'HSP90AB1', 'BMP1', 'PSMB3', 'IGFBP3', 'TIMP2', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'HAPLN3', 'COL4A1', 'LTBP4', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'GIP', 'PDIA6', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'MFGE8', 'FTL', 'PTHLH', 'CMTM3', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'GAL', 'CXCL2', 'MMP15', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'TIMP4', 'G6PD', 'MYOF', 'ALDH3A1', 'STMN1', 'ADGRG1', 'HMGB1', 'FABP5', 'TXN', 'ANGPTL4', 'PPIB', 'HSPA2', 'NMB', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'APLP2', 'DKK1', 'FLNB', 'RHOF', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MT3', 'RAET1G', 'FSTL3', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'COL22A1', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'COL5A2', 'TUBA4A', 'CDK1', 'SERPINE1', 'PVR', 'ECH1', 'UBC', 'METRN', 'HMGB2', 'RAP2B', 'PSMA4', 'TNFRSF1A', 'PRSS3', 'VCAN', 'NPC2', 'FN1', 'S100A13', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'SRGN', 'VIM', 'KRT81', 'HSP90AA1', 'CXCL8', 'PPP1CB', 'SPP1', 'STC1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1', 'PDIA4']</t>
+          <t>['HAPLN3', 'CTNNB1', 'FSTL3', 'RHOD', 'MFGE8', 'PYCARD', 'CADM1', 'SPINT2', 'TNFRSF12A', 'PPP3CA', 'SOX4', 'RIN2', 'CLDN4', 'CNN3', 'GTPBP4', 'RDX', 'ESAM', 'PODXL', 'ADAM19', 'CD9', 'CSRP1', 'NT5E', 'PPP1CB', 'COL1A1', 'FLOT1', 'CNTN1', 'FXYD5', 'LAMC2', 'ANTXR1', 'CCL2', 'AXL', 'ANXA2', 'ZFP36L1', 'IGFBP7', 'EZR', 'HSPB1', 'ACTG1', 'ITGA5', 'SERPINE2', 'S100A11', 'PLAUR', 'B4GALT1', 'HMGB1', 'RND1', 'CD44', 'SPP1', 'PDLIM5', 'LGALS3', 'JAK1', 'RND3', 'TGFBI', 'FN1', 'PCDH9', 'TESC', 'ACTB', 'RAP2B', 'NUAK1', 'ITGA3', 'ITGA11', 'SDC4', 'COL5A1', 'CTNNAL1', 'MYO10', 'TPM1', 'AMIGO2', 'CEBPB', 'CTTN', 'S100A10', 'CDC42', 'SPOCK1', 'CAV1', 'MYL12A', 'SERPINE1', 'LGALS1', 'TGM2', 'ITGB5', 'PTPRJ', 'ITGA2', 'SGCE', 'PVR', 'CDH2', 'VCAN', 'PTPRS', 'HES1', 'DOCK5', 'CXCL8', 'IL32', 'CD24', 'CD63', 'C1QBP', 'NTN4', 'SLC7A11', 'CCDC80', 'ADGRG1', 'JUP', 'ILK']</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IBA', 'IEA'], ['HDA', 'IBA', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IBA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['TAS'], ['IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'ISS'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['ISS'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['IBA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA'], ['IDA', 'IBA'], ['HDA', 'IBA'], ['IMP', 'HDA'], ['IDA', 'IPI', 'HDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'IEA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA']]</t>
+          <t>[['IEA'], ['IMP', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['IMP', 'ISS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA'], ['IEA'], ['IMP', 'ISS', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['ISS', 'IBA'], ['IEA'], ['IDA'], ['IMP'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['HMP'], ['IDA'], ['IDA'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['NAS'], ['IEA'], ['IDA'], ['ISS', 'TAS'], ['IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IEP'], ['HMP'], ['IMP', 'HMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IMP'], ['IDA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'ISS'], ['IMP', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA'], ['HMP', 'NAS'], ['IDA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA'], ['IEA'], ['IEA'], ['ISS'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['ISS'], ['IMP'], ['IDA'], ['IDA', 'NAS'], ['IDA'], ['HMP'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IMP'], ['IDA'], ['TAS'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP'], ['IMP'], ['IBA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'HMP', 'IBA', 'TAS']]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GO:0007155</t>
+          <t>GO:0031982</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cell adhesion</t>
+          <t>vesicle</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.881922493442715e-05</v>
+        <v>4.222562440350185e-05</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>"The attachment of a cell, either to another cell or to an underlying substrate such as the extracellular matrix, via cell adhesion molecules." [GOC:hb, GOC:pf]</t>
+          <t>"Any small, fluid-filled, spherical organelle enclosed by membrane." [GOC:mah, GOC:pz, GOC:vesicles]</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>317</v>
+        <v>735</v>
       </c>
       <c r="H4" t="n">
         <v>464</v>
       </c>
       <c r="I4" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="J4" t="n">
         <v>2717</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.3879310344827586</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3028391167192429</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -3264,17 +3528,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>['GO:0009987']</t>
+          <t>['GO:0043227']</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'SPOCK1', 'LAMC2', 'CLDN4', 'ITGA11', 'ACTG1', 'COL5A1', 'SDC4', 'CAV1', 'PDLIM5', 'PLAUR', 'CCL2', 'IL32', 'CCDC80', 'ACTB', 'RND1', 'CNTN1', 'CSRP1', 'S100A11', 'NT5E', 'MYL12A', 'CTTN', 'IGFBP7', 'B4GALT1', 'HAPLN3', 'CD24', 'MFGE8', 'ITGB5', 'S100A10', 'HSPB1', 'LGALS3', 'JAK1', 'SPINT2', 'DOCK5', 'CTNNAL1', 'NUAK1', 'RND3', 'SERPINE2', 'MYO10', 'SLC7A11', 'ADGRG1', 'HMGB1', 'TGM2', 'ADAM19', 'NTN4', 'CADM1', 'CEBPB', 'RHOD', 'AXL', 'CDC42', 'ZFP36L1', 'FSTL3', 'LGALS1', 'PTPRS', 'ITGA3', 'TESC', 'RIN2', 'CD9', 'PPP3CA', 'ILK', 'JUP', 'TGFBI', 'EZR', 'PODXL', 'CDH2', 'ANXA2', 'ANTXR1', 'CNN3', 'SERPINE1', 'PVR', 'HES1', 'RAP2B', 'SGCE', 'VCAN', 'FN1', 'ITGA2', 'GTPBP4', 'AMIGO2', 'RDX', 'FLOT1', 'PTPRJ', 'CTNNB1', 'COL1A1', 'PYCARD', 'TNFRSF12A', 'ESAM', 'FXYD5', 'PCDH9', 'CXCL8', 'PPP1CB', 'SPP1', 'ITGA5', 'TPM1', 'SOX4', 'C1QBP']</t>
+          <t>['HSPA2', 'CTNNB1', 'PPIB', 'MYL6', 'RHOD', 'CDA', 'TUBA4A', 'EIF6', 'CMTM3', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'RPL28', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'YWHAE', 'RIN2', 'S100A6', 'MGST1', 'OCIAD2', 'NAP1L1', 'SKIL', 'PSMD14', 'SLC2A3', 'PSMD2', 'TSPAN4', 'GLRX', 'RDX', 'RHOF', 'PODXL', 'MFSD12', 'QPCT', 'CD9', 'CSRP1', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'CNTN1', 'PRSS3', 'DKK1', 'GPRC5A', 'ANTXR1', 'UBB', 'F2RL1', 'FLNB', 'SYT13', 'ULK1', 'AXL', 'ANXA2', 'PMEPA1', 'RUVBL2', 'PCSK1N', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'GIP', 'HSPB1', 'ACTG1', 'RAN', 'ITGA5', 'SERPINE2', 'CALM2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'PLAUR', 'G6PD', 'GNG4', 'B4GALT1', 'CYBA', 'PDIA6', 'STMN1', 'HMGB1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'JAK1', 'NTS', 'PRDX1', 'TXNRD1', 'AKR1B1', 'TGFBI', 'SYT1', 'SULT2B1', 'LTBP3', 'FN1', 'SCCPDH', 'GABARAPL1', 'SRGN', 'DSE', 'ACTB', 'SH3BGRL3', 'RAP2B', 'TUBA1C', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'GNPNAT1', 'CDK1', 'CTTN', 'GLIPR1', 'GOLIM4', 'TSPAN15', 'S100A10', 'CDC42', 'TMSB4X', 'CAV1', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TGFBR1', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'FGFR1', 'ILF2', 'CCT5', 'GRAMD1A', 'PDCD5', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'NPTX1', 'CXCL1', 'ANXA3', 'BMP1', 'COPZ2', 'NPC2', 'PSMA4', 'SH3KBP1', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'MT3', 'LDHB', 'TIMP2', 'ADGRG1', 'ECH1', 'JUP', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP'], ['IDA', 'NAS'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'HMP'], ['IMP', 'IBA'], ['IMP', 'IEA'], ['IDA'], ['IEA'], ['IDA', 'IMP'], ['ISS', 'TAS'], ['TAS'], ['IBA', 'IEA'], ['HMP', 'NAS'], ['IDA'], ['IBA', 'NAS', 'IEA'], ['HMP'], ['IEA'], ['IDA'], ['HMP'], ['ISS'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IMP'], ['HMP'], ['IDA', 'ISS'], ['IMP', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['IDA', 'IEA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['ISS', 'IEA'], ['IDA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IMP'], ['IEA'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA'], ['IMP'], ['IDA', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IMP', 'IGI', 'HMP', 'IBA', 'TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEP'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA'], ['IBA', 'IEA'], ['IEA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['IMP'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['NAS'], ['IBA', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS'], ['ISS', 'IEA'], ['IMP']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['TAS'], ['HDA'], ['HDA'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IBA'], ['HDA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['IDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['TAS'], ['TAS'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IDA'], ['HDA', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['TAS'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HDA'], ['HDA', 'ISS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['TAS'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['TAS'], ['IEA'], ['IBA', 'TAS'], ['IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IBA'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'TAS'], ['HDA', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IEA'], ['TAS'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'ISS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['ISS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['ISS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3286,42 +3550,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GO:0070062</t>
+          <t>GO:0005576</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>extracellular exosome</t>
+          <t>extracellular region</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0002935541640231257</v>
+        <v>0.0002562078211521733</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>"A vesicle that is released into the extracellular region by fusion of the limiting endosomal membrane of a multivesicular body with the plasma membrane. Extracellular exosomes, also simply called exosomes, have a diameter of about 40-100 nm." [GOC:BHF, GOC:mah, GOC:vesicles, PMID:15908444, PMID:17641064, PMID:19442504, PMID:19498381, PMID:22418571, PMID:24009894]</t>
+          <t>"The space external to the outermost structure of a cell. For cells without external protective or external encapsulating structures this refers to space outside of the plasma membrane. This term covers the host cell environment outside an intracellular parasite." [GOC:go_curators]</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>465</v>
+        <v>808</v>
       </c>
       <c r="H5" t="n">
         <v>464</v>
       </c>
       <c r="I5" t="n">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="J5" t="n">
         <v>2717</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2672413793103448</v>
+        <v>0.4116379310344828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2363861386138614</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -3330,17 +3594,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>['GO:0005615', 'GO:1903561']</t>
+          <t>['GO:0110165']</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'GLRX', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'HSP90AB1', 'PSMB3', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'PKM', 'TKT', 'S100A16', 'PDIA6', 'PGK1', 'CCT2', 'MFGE8', 'FTL', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'YWHAE', 'ALDH1A1', 'G6PD', 'MYOF', 'STMN1', 'ADGRG1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'APLP2', 'FLNB', 'RHOF', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'UBC', 'RAP2B', 'PSMA4', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'PTPRJ', 'CTNNB1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1']</t>
+          <t>['HSPA2', 'HAPLN3', 'CTNNB1', 'PPIB', 'MYL6', 'FSTL3', 'ANGPTL4', 'CDA', 'TUBA4A', 'METRN', 'EIF6', 'CMTM3', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'RPL28', 'LTBP4', 'ARPC3', 'SPINT2', 'MYOF', 'C1orf56', 'HSP90AB1', 'TXN', 'ENO1', 'TIMP4', 'YWHAE', 'S100A6', 'PSMD14', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'IL11', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'DMKN', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'CNTN1', 'RSPO3', 'PRSS3', 'DKK1', 'GPRC5A', 'LAMC2', 'UBB', 'CCL2', 'FLNB', 'COL5A2', 'AXL', 'S100A13', 'ANXA2', 'RUVBL2', 'TNFRSF1A', 'PCSK1N', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'GIP', 'HSPB1', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'PLAUR', 'CXCL5', 'G6PD', 'MMP15', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'HMGB1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'TFPI2', 'NTS', 'PRDX1', 'TXNRD1', 'AKR1B1', 'CXCL2', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'SCCPDH', 'SRGN', 'IGFBP3', 'ACTB', 'KRT81', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'COL22A1', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'AKR1B10', 'TM7SF3', 'NMB', 'COL5A1', 'CDK1', 'PTHLH', 'GLIPR1', 'S100A10', 'CDC42', 'TMSB4X', 'SPOCK1', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'FGFR1', 'ILF2', 'CCT5', 'PVR', 'HMGB2', 'PDCD5', 'VCAN', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'NPTX1', 'CXCL1', 'ANXA3', 'BMP1', 'CXCL8', 'IL32', 'NPC2', 'STC1', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'C1QBP', 'PTGR1', 'NTN4', 'UBC', 'RAET1G', 'MT3', 'CCDC80', 'LDHB', 'TIMP2', 'ADGRG1', 'IGFBP4', 'ALDH3A1', 'ECH1', 'JUP', 'COL4A1', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['IBA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['TAS'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA'], ['TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IBA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['ISS', 'TAS', 'IEA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IDA'], ['IDA', 'HDA'], ['HDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IEA'], ['NAS'], ['HDA', 'TAS'], ['HDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['TAS', 'IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'TAS'], ['IEA'], ['HDA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3352,42 +3616,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GO:0005576</t>
+          <t>GO:0070062</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>extracellular region</t>
+          <t>extracellular exosome</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0003639216747408877</v>
+        <v>0.0002935541640231257</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>"The space external to the outermost structure of a cell. For cells without external protective or external encapsulating structures this refers to space outside of the plasma membrane. This term covers the host cell environment outside an intracellular parasite." [GOC:go_curators]</t>
+          <t>"A vesicle that is released into the extracellular region by fusion of the limiting endosomal membrane of a multivesicular body with the plasma membrane. Extracellular exosomes, also simply called exosomes, have a diameter of about 40-100 nm." [GOC:BHF, GOC:mah, GOC:vesicles, PMID:15908444, PMID:17641064, PMID:19442504, PMID:19498381, PMID:22418571, PMID:24009894]</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>811</v>
+        <v>465</v>
       </c>
       <c r="H6" t="n">
         <v>464</v>
       </c>
       <c r="I6" t="n">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="J6" t="n">
         <v>2717</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4116379310344828</v>
+        <v>0.2672413793103448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2355117139334155</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3396,64 +3660,64 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0005615', 'GO:1903561']</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'SPOCK1', 'LAMC2', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'COL5A1', 'SDC4', 'CLU', 'PLAUR', 'CCL2', 'IL32', 'CCDC80', 'GLRX', 'GLIPR1', 'RSPO3', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'CXCL5', 'DMKN', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'TFPI2', 'HSP90AB1', 'BMP1', 'PSMB3', 'IGFBP3', 'TIMP2', 'AKR1B10', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'HAPLN3', 'COL4A1', 'LTBP4', 'PSMD14', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'GIP', 'PDIA6', 'PCSK1N', 'PGK1', 'CCT2', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'PTHLH', 'CMTM3', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'C1orf56', 'GAL', 'SPINT2', 'SCCPDH', 'CXCL2', 'MMP15', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'TIMP4', 'G6PD', 'MYOF', 'ALDH3A1', 'STMN1', 'ADGRG1', 'HMGB1', 'FABP5', 'TXN', 'ANGPTL4', 'PPIB', 'HSPA2', 'NMB', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'NTN4', 'APLP2', 'DKK1', 'FLNB', 'RHOF', 'FGFR1', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MT3', 'RAET1G', 'ILF2', 'FSTL3', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'COL22A1', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'NPTX1', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'COL5A2', 'TUBA4A', 'CDK1', 'SERPINE1', 'CDA', 'PVR', 'ECH1', 'UBC', 'METRN', 'HMGB2', 'RAP2B', 'PSMA4', 'TNFRSF1A', 'PRSS3', 'VCAN', 'NPC2', 'FN1', 'S100A13', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'TMSB4X', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'SRGN', 'PYCARD', 'VIM', 'KRT81', 'HSP90AA1', 'CXCL8', 'PPP1CB', 'SPP1', 'STC1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'C1QBP', 'QPCT', 'PRDX1', 'PDIA4']</t>
+          <t>['HSPA2', 'CTNNB1', 'PPIB', 'MYL6', 'TUBA4A', 'EIF6', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'YWHAE', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'FLOT1', 'CNTN1', 'GPRC5A', 'UBB', 'FLNB', 'AXL', 'ANXA2', 'RUVBL2', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'HSPB1', 'ACTG1', 'RAN', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'G6PD', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'PRDX1', 'TXNRD1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'ACTB', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'CDK1', 'S100A10', 'CDC42', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'CCT5', 'PDCD5', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'ADGRG1', 'ECH1', 'JUP', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['HDA'], ['IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HDA', 'IBA', 'TAS', 'IC', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'NAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['TAS', 'IEA'], ['IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['ISS', 'TAS', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['NAS'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['HDA'], ['HDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IEA'], ['IDA', 'HDA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IBA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'HDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['HDA'], ['IDA', 'TAS', 'IEA'], ['HDA', 'TAS'], ['HDA', 'TAS'], ['HDA', 'IEA'], ['HDA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['HDA'], ['HDA', 'IBA', 'TAS', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA', 'TAS', 'IEA'], ['HDA'], ['IDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GO:1903561</t>
+          <t>GO:0008150</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>extracellular vesicle</t>
+          <t>biological_process</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0004006504636273837</v>
+        <v>0.0003566456701374491</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
+          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>472</v>
+        <v>2453</v>
       </c>
       <c r="H7" t="n">
         <v>464</v>
       </c>
       <c r="I7" t="n">
-        <v>125</v>
+        <v>449</v>
       </c>
       <c r="J7" t="n">
         <v>2717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.269396551724138</v>
+        <v>0.9676724137931034</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2648305084745763</v>
+        <v>0.1830411740725642</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -3462,17 +3726,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>['GO:0031982', 'GO:0065010']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'GLRX', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'HSP90AB1', 'PSMB3', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'PKM', 'TKT', 'S100A16', 'PDIA6', 'PGK1', 'CCT2', 'MFGE8', 'FTL', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'G6PD', 'MYOF', 'STMN1', 'ADGRG1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'APLP2', 'FLNB', 'RHOF', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'UBC', 'RAP2B', 'PSMA4', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'PTPRJ', 'CTNNB1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1']</t>
+          <t>['HSPA2', 'EMG1', 'HAPLN3', 'TXNRD2', 'UTP18', 'CXXC5', 'CTNNB1', 'PPIB', 'TK1', 'MYL6', 'FSTL3', 'RAP1GAP', 'RHOD', 'ANGPTL4', 'CDA', 'TUBA4A', 'METRN', 'EIF6', 'CMTM3', 'SLC22A18', 'MFGE8', 'EVA1A', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'CADM1', 'ST3GAL5', 'RPL28', 'CES1', 'LTBP4', 'ARPC3', 'GINS2', 'SPINT2', 'TNFRSF12A', 'NEAT1', 'MYOF', 'PAQR5', 'PPP3CA', 'C1orf56', 'KYNU', 'CYP24A1', 'HSP90AB1', 'TXN', 'GLS', 'ENO1', 'TIMP4', 'YWHAE', 'BBX', 'SOX4', 'RIN2', 'CLDN4', 'CNN3', 'S100A6', 'MGST1', 'FAM64A', 'OCIAD2', 'LRRC75A', 'ID3', 'NAP1L1', 'SKIL', 'SCD', 'KCNMA1', 'PSMD14', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'GTPBP4', 'BTG1', 'GLRX', 'UBA6', 'RDX', 'CENPA', 'ESAM', 'ELK3', 'IL11', 'LACTB', 'FBXO22', 'CLPTM1L', 'SSB', 'TSPAN5', 'CCDC85B', 'RHOF', 'NR0B1', 'BCL2A1', 'RASSF10', 'PODXL', 'MFSD12', 'QPCT', 'ADAM19', 'CD9', 'APOBEC3C', 'AKAP12', 'PRMT5', 'SLC25A37', 'CDC42EP3', 'SMC4', 'CCNB1', 'CSRP1', 'MLLT11', 'EPAS1', 'LMO4', 'DMKN', 'NT5E', 'ATP5G1', 'KMT5A', 'KLF6', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'CNTN1', 'RSPO3', 'PRSS3', 'TPX2', 'HMGA2', 'DKK1', 'SLN', 'C15orf48', 'CDC20', 'FXYD5', 'CPLX2', 'GPRC5A', 'LAMC2', 'SRGAP1', 'PDLIM7', 'HJURP', 'BCAT2', 'ANTXR1', 'KCNG1', 'PLGRKT', 'UBB', 'NPM1', 'SLU7', 'F2RL1', 'CCL2', 'ISG20', 'PIR', 'TRIM47', 'GPX2', 'FLNB', 'COL5A2', 'SYT13', 'PLEK2', 'ULK1', 'PSMD8', 'AXL', 'S100A13', 'ANXA2', 'PMEPA1', 'RUVBL2', 'TNFRSF1A', 'ZFP36L1', 'PCSK1N', 'SSR3', 'AKR1C2', 'MT1X', 'GAPDH', 'MYL12B', 'MCL1', 'PRSS23', 'ELF3', 'IGFBP7', 'PSMD4', 'NUSAP1', 'FDXR', 'UPP1', 'HSP90AA1', 'S100A16', 'AVPI1', 'NUPR1', 'EZR', 'TXNDC9', 'GIP', 'HSPB1', 'PPP1R14A', 'MLXIP', 'TMEM41B', 'ACTG1', 'CDK2AP2', 'RAN', 'TMBIM6', 'ARL6IP1', 'ETFB', 'ITGA5', 'SERPINE2', 'CALM2', 'AURKA', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'TAGLN', 'SLC3A2', 'MYC', 'MEG3', 'CCT2', 'MGLL', 'PHLDA3', 'CA12', 'PLAUR', 'TRAM1', 'CXCL5', 'G6PD', 'MMP15', 'GNG4', 'UBE2S', 'B4GALT1', 'CBX6', 'CYBA', 'PNPT1', 'PDIA6', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'SPP1', 'GADD45A', 'FOXD1', 'SNHG8', 'TMEM120B', 'NEK6', 'PDLIM5', 'WDR43', 'COL4A2', 'LGALS3', 'JAK1', 'TFPI2', 'RND3', 'RPL22L1', 'NTS', 'DKC1', 'PRDX1', 'TXNRD1', 'RASSF1', 'AKR1B1', 'CXCL2', 'TGFBI', 'OSBPL8', 'CCNB2', 'SYT1', 'SULT2B1', 'JUNB', 'LTBP3', 'FN1', 'PCDH9', 'SCCPDH', 'POLR2L', 'GABARAPL1', 'TESC', 'SRGN', 'MBOAT2', 'IGFBP3', 'DSE', 'CKS2', 'ACTB', 'KRT81', 'NUDT19', 'SH3BGRL3', 'DOLK', 'RAP2B', 'TUBA1C', 'NUAK1', 'CDKN3', 'RAB3B', 'ITGA3', 'GPX1', 'RPS27L', 'PACSIN3', 'HSPA8', 'PDLIM2', 'CLU', 'PKM', 'PSMA5', 'ITGA11', 'NUAK2', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'AKR1B10', 'ACOT9', 'TM7SF3', 'MALAT1', 'FBXO32', 'NMB', 'NAA38', 'COL5A1', 'CTNNAL1', 'GNPNAT1', 'PRR11', 'DDB2', 'CDCA3', 'CDK1', 'MYO10', 'ETS2', 'TPM1', 'AMIGO2', 'CENPW', 'CEBPB', 'DHRS2', 'CTTN', 'PTHLH', 'PLK1', 'GLIPR1', 'BIRC5', 'TSPAN15', 'ODC1', 'TRA2A', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'SPOCK1', 'CDKN1A', 'LBH', 'CAV1', 'MYL12A', 'NQO1', 'PSME2', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TGFBR1', 'TKT', 'ALDH1A1', 'SLAMF9', 'ZWINT', 'TGM2', 'AHNAK2', 'ITGB5', 'KRT7', 'RQCD1', 'S100A4', 'CTSL', 'TMSB10', 'PTPRJ', 'FGFR1', 'JUN', 'SUCLG1', 'ITGA2', 'TOP2A', 'ILF2', 'SGCE', 'MRPS22', 'LCE3E', 'CCT5', 'MORF4L2', 'RBP1', 'SNW1', 'PVR', 'HMGB2', 'MT2A', 'HPCAL1', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'GRB10', 'PDCD5', 'VCAN', 'CDC25B', 'SLC2A1', 'NKAIN4', 'TUBB', 'BAMBI', 'EIF2S3', 'FHL1', 'INO80C', 'PTPRS', 'HES1', 'AP2M1', 'NPTX1', 'CXCL1', 'DOCK5', 'SLC7A7', 'TP53I3', 'MAF', 'FOS', 'ANXA3', 'DHRS3', 'CDC42SE1', 'BMP1', 'ZFP36', 'SLC35F2', 'CXCL8', 'IL32', 'SGK1', 'DAAM1', 'COPZ2', 'CTPS1', 'NPC2', 'STC1', 'PSMA4', 'CD24', 'SH3KBP1', 'DHRS7', 'CD63', 'PRMT1', 'TPM2', 'TUBB6', 'COTL1', 'C1QBP', 'PTGR1', 'NTN4', 'LMNA', 'UBC', 'RAET1G', 'CYB5A', 'SLC7A11', 'MT3', 'CCDC80', 'LDHB', 'PGM2L1', 'TIMP2', 'ADGRG1', 'IGFBP4', 'ALDH3A1', 'PYCR1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'MDM4', 'MAP1B', 'COL4A1', 'MIS18BP1', 'HNRNPH1', 'EMP3', 'FRMD6', 'PRC1', 'FAM89B', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HMP'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IC', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'TAS'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'ISO', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['HMP', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['ISS', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IMP', 'IBA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA'], ['EXP', 'IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['HMP'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['NAS'], ['IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['ND', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3484,42 +3748,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GO:0005829</t>
+          <t>GO:1903561</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cytosol</t>
+          <t>extracellular vesicle</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0004508467053833433</v>
+        <v>0.0004006504636273837</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>"The part of the cytoplasm that does not contain organelles but which does contain other particulate matter, such as protein complexes." [GOC:hjd, GOC:jl]</t>
+          <t>"Any vesicle that is part of the extracellular region." [GO_REF:0000064, GOC:pm, GOC:TermGenie, PMID:24769233]</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>960</v>
+        <v>472</v>
       </c>
       <c r="H8" t="n">
         <v>464</v>
       </c>
       <c r="I8" t="n">
-        <v>218</v>
+        <v>125</v>
       </c>
       <c r="J8" t="n">
         <v>2717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4698275862068966</v>
+        <v>0.269396551724138</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2270833333333333</v>
+        <v>0.2648305084745763</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3528,17 +3792,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>['GO:0005737', 'GO:0110165']</t>
+          <t>['GO:0031982', 'GO:0065010']</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>['TXNDC9', 'CD44', 'LDHB', 'SSB', 'FOS', 'NQO1', 'RQCD1', 'ACTG1', 'UBB', 'BIRC5', 'HNRNPH1', 'GNPNAT1', 'KLF6', 'CLU', 'PDLIM5', 'IL32', 'GLRX', 'DAAM1', 'MAP1B', 'ACTB', 'RAN', 'PPP1R14A', 'RND1', 'HSPA5', 'COPZ2', 'CTPS1', 'AKR1B1', 'MLLT11', 'NT5E', 'CDC25B', 'MYL12A', 'TPX2', 'RPL28', 'PSMD8', 'ENO1', 'GRB10', 'POLR2L', 'HSP90AB1', 'PSMB3', 'CTTN', 'AKR1B10', 'SGK1', 'S100A3', 'GRAMD1A', 'CCNB1', 'KRT7', 'MT2A', 'PSME2', 'HSPA8', 'PSMD14', 'PKM', 'TKT', 'S100A16', 'PTTG1', 'PDIA6', 'OSBPL8', 'PGK1', 'CCT2', 'RBP1', 'UBE2S', 'KMT5A', 'HMGA1', 'FTL', 'PTHLH', 'CPLX2', 'CMTM3', 'FBXO22', 'MGLL', 'CCT5', 'HSPB1', 'LGALS3', 'LCE3D', 'AKR1C3', 'CES1', 'JAK1', 'UBA6', 'DOCK5', 'NUDT19', 'GABARAPL1', 'CTNNAL1', 'RND3', 'ZWINT', 'FBXO32', 'KYNU', 'YWHAE', 'PIR', 'CDCA3', 'GLS', 'SERPINE2', 'ALDH1A1', 'PNPT1', 'G6PD', 'MYO10', 'PGM2L1', 'ALDH3A1', 'STMN1', 'CEP170', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'RPS27L', 'ARL6IP1', 'TGM2', 'RUVBL2', 'ODC1', 'FSCN1', 'AKR1C2', 'FLNB', 'RHOF', 'NEK6', 'FGFR1', 'GPX1', 'EIF6', 'RHOD', 'CDC42', 'LMNA', 'SLU7', 'SH3BGRL3', 'PDCD5', 'ZFP36L1', 'AHNAK2', 'CDKN1A', 'MT3', 'RASSF10', 'ILF2', 'CXXC5', 'MYL6', 'CALM2', 'S100A4', 'FTH1', 'LGALS1', 'PTPRS', 'CYB5A', 'GAPDH', 'ULK1', 'SMC4', 'TESC', 'TK1', 'TRIM47', 'RIN2', 'NPM1', 'CDC20', 'ETS2', 'MYL12B', 'PPP3CA', 'SULT2B1', 'ILK', 'JUP', 'FHL1', 'HJURP', 'TXNRD1', 'MPRIP', 'TXNRD2', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PSMD4', 'TPM2', 'SH3KBP1', 'ANXA2', 'ELF3', 'TUBB', 'S100A6', 'CNN3', 'TUBA4A', 'AURKA', 'CDK1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'ECH1', 'PRC1', 'UBC', 'SPATS2', 'RAP2B', 'PSMA4', 'PHKG1', 'PDLIM7', 'RGS3', 'SRGAP1', 'TSPAN15', 'SYT1', 'GTPBP4', 'S100A13', 'EPAS1', 'TP53I3', 'LACTB', 'EIF2S3', 'TUBB4B', 'TMSB4X', 'PSMA5', 'CTNNB1', 'RAP1GAP', 'PYCARD', 'GPX2', 'BCL2A1', 'VIM', 'KRT81', 'PRMT1', 'HSP90AA1', 'PPP1CB', 'MCL1', 'ZFP36', 'CDC42EP3', 'UPP1', 'CDKN3', 'TPM1', 'CENPA', 'KPNA2', 'PACSIN3', 'SLC2A1', 'AP2M1', 'C1QBP', 'PRDX1', 'PLK1']</t>
+          <t>['HSPA2', 'CTNNB1', 'PPIB', 'MYL6', 'TUBA4A', 'EIF6', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'YWHAE', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'FLOT1', 'CNTN1', 'GPRC5A', 'UBB', 'FLNB', 'AXL', 'ANXA2', 'RUVBL2', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'HSPB1', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'G6PD', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'PRDX1', 'TXNRD1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'ACTB', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'CDK1', 'S100A10', 'CDC42', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'CCT5', 'PDCD5', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'ADGRG1', 'ECH1', 'JUP', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[['IDA'], ['IDA'], ['IDA', 'TAS'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IEA'], ['IDA'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IBA', 'TAS'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IBA'], ['IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IBA'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IBA'], ['TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IDA'], ['IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['TAS'], ['IEA'], ['IDA'], ['TAS'], ['IDA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IDA'], ['IEA'], ['IDA'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS', 'NAS'], ['IDA'], ['IEA'], ['TAS'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['TAS']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3863,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'GLRX', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'HSP90AB1', 'PSMB3', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'PKM', 'TKT', 'S100A16', 'PDIA6', 'PGK1', 'CCT2', 'MFGE8', 'FTL', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'G6PD', 'MYOF', 'STMN1', 'ADGRG1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'APLP2', 'FLNB', 'RHOF', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'UBC', 'RAP2B', 'PSMA4', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'PTPRJ', 'CTNNB1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'PPIB', 'MYL6', 'TUBA4A', 'EIF6', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'YWHAE', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'FLOT1', 'CNTN1', 'GPRC5A', 'UBB', 'FLNB', 'AXL', 'ANXA2', 'RUVBL2', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'HSPB1', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'G6PD', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'PRDX1', 'TXNRD1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'ACTB', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'CDK1', 'S100A10', 'CDC42', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'CCT5', 'PDCD5', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'ADGRG1', 'ECH1', 'JUP', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3929,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['CD44', 'LDHB', 'TM7SF3', 'CD63', 'ANXA3', 'PTGR1', 'FURIN', 'ACTG1', 'UBB', 'SDC4', 'CLU', 'GLRX', 'ACTB', 'RAN', 'HSPA5', 'CNTN1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'AKR1B1', 'NT5E', 'MYL12A', 'RPL28', 'SEMA3C', 'ENO1', 'HSP90AB1', 'PSMB3', 'IGFBP7', 'B4GALT1', 'KRT7', 'PSME2', 'HSPA8', 'PKM', 'TKT', 'S100A16', 'PDIA6', 'PGK1', 'CCT2', 'MFGE8', 'FTL', 'ITGB5', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'AKR1C3', 'YWHAE', 'SERPINE2', 'ALDH1A1', 'G6PD', 'MYOF', 'STMN1', 'ADGRG1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'TGM2', 'RUVBL2', 'GPRC5A', 'FSCN1', 'APLP2', 'FLNB', 'RHOF', 'EIF6', 'AXL', 'CDC42', 'SH3BGRL3', 'PDCD5', 'MYL6', 'S100A4', 'FTH1', 'TUBB6', 'LGALS1', 'PTPRS', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'LTBP3', 'CD9', 'MYL12B', 'SULT2B1', 'JUP', 'ACP2', 'TXNRD1', 'TGFBI', 'COTL1', 'EZR', 'PSMD2', 'ARPC3', 'PODXL', 'ANXA2', 'TUBB', 'S100A6', 'TUBA4A', 'CDK1', 'SERPINE1', 'ECH1', 'UBC', 'RAP2B', 'PSMA4', 'NPC2', 'FN1', 'RDX', 'EIF2S3', 'TUBB4B', 'FLOT1', 'PSMA5', 'PTPRJ', 'CTNNB1', 'VIM', 'HSP90AA1', 'PPP1CB', 'SPP1', 'RAB3B', 'COL4A2', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1']</t>
+          <t>['HSPA2', 'CTNNB1', 'PPIB', 'MYL6', 'TUBA4A', 'EIF6', 'MFGE8', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'RPL28', 'ARPC3', 'MYOF', 'HSP90AB1', 'TXN', 'ENO1', 'YWHAE', 'S100A6', 'SLC2A3', 'PSMD2', 'GLRX', 'RDX', 'RHOF', 'PODXL', 'QPCT', 'CD9', 'CSRP1', 'NT5E', 'AKR1C3', 'PPP1CB', 'APLP2', 'FLOT1', 'CNTN1', 'GPRC5A', 'UBB', 'FLNB', 'AXL', 'ANXA2', 'RUVBL2', 'GAPDH', 'MYL12B', 'PRSS23', 'IGFBP7', 'HSP90AA1', 'S100A16', 'EZR', 'HSPB1', 'ACTG1', 'RAN', 'SERPINE2', 'S100A11', 'FABP5', 'SLC3A2', 'CCT2', 'G6PD', 'GNG4', 'B4GALT1', 'PDIA6', 'STMN1', 'CD44', 'SPP1', 'COL4A2', 'LGALS3', 'PRDX1', 'TXNRD1', 'AKR1B1', 'TGFBI', 'SULT2B1', 'LTBP3', 'FN1', 'ACTB', 'SH3BGRL3', 'RAP2B', 'RAB3B', 'ITGA3', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'TM7SF3', 'CDK1', 'S100A10', 'CDC42', 'MYL12A', 'PSME2', 'SERPINE1', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'TGM2', 'ITGB5', 'KRT7', 'S100A4', 'CTSL', 'PTPRJ', 'CCT5', 'PDCD5', 'SLC2A1', 'TUBB', 'EIF2S3', 'PTPRS', 'AP2M1', 'ANXA3', 'NPC2', 'PSMA4', 'CD63', 'TUBB6', 'COTL1', 'PTGR1', 'UBC', 'LDHB', 'ADGRG1', 'ECH1', 'JUP', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
+          <t>[['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA']]</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3955,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0006849146270164356</v>
+        <v>0.001314407581964363</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -3702,22 +3966,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1924</v>
+        <v>1937</v>
       </c>
       <c r="H11" t="n">
         <v>464</v>
       </c>
       <c r="I11" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J11" t="n">
         <v>2717</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8125</v>
+        <v>0.8146551724137931</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1959459459459459</v>
+        <v>0.1951471347444502</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3731,12 +3995,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['TXNDC9', 'CD44', 'LDHB', 'TAGLN', 'CD63', 'ANXA3', 'SPOCK1', 'LAMC2', 'SSB', 'FOS', 'NQO1', 'RQCD1', 'PTGR1', 'FURIN', 'ISG20', 'OCIAD2', 'ACTG1', 'UBB', 'BIRC5', 'HNRNPH1', 'GNPNAT1', 'KLF6', 'COL5A1', 'SDC4', 'CAV1', 'GADD45A', 'CLU', 'PDLIM5', 'PLAUR', 'TMSB10', 'IL32', 'GLRX', 'NAP1L1', 'ATP5G1', 'GLIPR1', 'TOP2A', 'RASSF1', 'TUBA1B', 'DAAM1', 'MAP1B', 'CDK2AP2', 'ACTB', 'RAN', 'PPP1R14A', 'RND1', 'HSPA5', 'GALNT14', 'CSRP1', 'SLC3A2', 'S100A11', 'COPZ2', 'CTPS1', 'TSPAN5', 'AKR1B1', 'MLLT11', 'NT5E', 'CDC25B', 'MYL12A', 'TPX2', 'RPL28', 'PSMD8', 'ENO1', 'TMBIM6', 'GRB10', 'ID3', 'POLR2L', 'HSP90AB1', 'BMP1', 'MBOAT2', 'PSMB3', 'IGFBP3', 'TRAM1', 'TIMP2', 'CTTN', 'AKR1B10', 'IGFBP7', 'B4GALT1', 'SGK1', 'MAF', 'BCAT2', 'S100A3', 'CDC42SE1', 'GRAMD1A', 'CCNB1', 'KRT7', 'FRMD6', 'ELK3', 'MT2A', 'PSME2', 'HSPA8', 'COL4A1', 'SCD', 'PSMD14', 'PKM', 'TKT', 'S100A16', 'IGFBP4', 'SLC22A18', 'PTTG1', 'GIP', 'PDIA6', 'PCSK1N', 'OSBPL8', 'PGK1', 'CCT2', 'RBP1', 'UBE2S', 'KMT5A', 'HMGA1', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'PTHLH', 'CPLX2', 'CMTM3', 'ITGB5', 'FBXO22', 'MGLL', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'LCE3D', 'BTG1', 'C15orf48', 'AKR1C3', 'MRPS22', 'CES1', 'JAK1', 'GAL', 'UBA6', 'SPINT2', 'SCCPDH', 'CYBA', 'DOCK5', 'NUDT19', 'GABARAPL1', 'CTNNAL1', 'NUAK1', 'SLC25A37', 'CYP24A1', 'ST3GAL5', 'F2RL1', 'BAMBI', 'RND3', 'ZNF185', 'ZWINT', 'FBXO32', 'DHRS2', 'KYNU', 'YWHAE', 'PIR', 'CDCA3', 'PMEPA1', 'GLS', 'SERPINE2', 'ALDH1A1', 'PNPT1', 'DSE', 'G6PD', 'MYO10', 'ETFB', 'MYOF', 'PYCR1', 'PGM2L1', 'ALDH3A1', 'STMN1', 'CEP170', 'NUSAP1', 'HMGB1', 'FABP5', 'TXN', 'PPIB', 'HSPA2', 'MYC', 'RPS27L', 'ARL6IP1', 'TGM2', 'SLN', 'EVA1A', 'RUVBL2', 'ODC1', 'GPRC5A', 'TGFBR1', 'FSCN1', 'PDLIM2', 'APLP2', 'AKR1C2', 'DKK1', 'FLNB', 'RHOF', 'NEK6', 'FGFR1', 'CEBPB', 'GPX1', 'EIF6', 'RHOD', 'CDC42', 'LMNA', 'SLU7', 'SH3BGRL3', 'CREM', 'PDCD5', 'PLGRKT', 'DHRS3', 'ZFP36L1', 'AHNAK2', 'EMG1', 'CDKN1A', 'MT3', 'RAET1G', 'RASSF10', 'ILF2', 'CXXC5', 'FSTL3', 'MYL6', 'CALM2', 'S100A4', 'FTH1', 'TUBB6', 'TMEM41B', 'LGALS1', 'PTPRS', 'PRR11', 'CYB5A', 'SYT13', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'SMC4', 'TESC', 'DHRS7', 'TK1', 'TRIM47', 'RIN2', 'NPM1', 'CD9', 'LRRC75A', 'CDC20', 'ETS2', 'MYL12B', 'PPP3CA', 'SULT2B1', 'LBH', 'ILK', 'JUP', 'FHL1', 'HJURP', 'ACP2', 'COL22A1', 'TXNRD1', 'MPRIP', 'TGFBI', 'TXNRD2', 'FAM89B', 'COTL1', 'MFSD12', 'EZR', 'PSMD2', 'ARPC3', 'PSMD4', 'PUS1', 'APOBEC3C', 'TPM2', 'SH3KBP1', 'NPTX1', 'GOLIM4', 'PODXL', 'CDH2', 'ANXA2', 'ELF3', 'ACOT9', 'ANTXR1', 'TUBB', 'S100A6', 'COL5A2', 'CNN3', 'TUBA4A', 'AURKA', 'CDK1', 'MGST1', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'PRC1', 'UBC', 'SKIL', 'HES1', 'SPATS2', 'HMGB2', 'DKC1', 'NAA38', 'RAP2B', 'CCDC85B', 'PSMA4', 'MT1X', 'SGCE', 'PHKG1', 'TUBA1C', 'PDLIM7', 'RGS3', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'SYT1', 'VCAN', 'NPC2', 'P4HA3', 'FN1', 'ITGA2', 'GTPBP4', 'S100A13', 'RDX', 'EPAS1', 'TP53I3', 'LACTB', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'TMSB4X', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'GPX2', 'SSR3', 'BCL2A1', 'VIM', 'KRT81', 'PRMT1', 'HSP90AA1', 'PPP1CB', 'SPP1', 'MCL1', 'STC1', 'ZFP36', 'RAB3B', 'COL4A2', 'CDC42EP3', 'ITGA5', 'UPP1', 'CDKN3', 'MLXIP', 'NR0B1', 'TPM1', 'SOX4', 'NUPR1', 'PHLDA3', 'CENPA', 'KPNA2', 'SUCLG1', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'DOLK', 'CLPTM1L', 'PLEK2', 'AP2M1', 'C1QBP', 'FDXR', 'QPCT', 'PRDX1', 'PDIA4', 'PLK1']</t>
+          <t>['HSPA2', 'EMG1', 'TXNRD2', 'CXXC5', 'CTNNB1', 'PPIB', 'TK1', 'MYL6', 'ZNF185', 'FSTL3', 'RAP1GAP', 'RHOD', 'CDA', 'TUBA4A', 'EIF6', 'CMTM3', 'SLC22A18', 'SPATS2', 'MFGE8', 'EVA1A', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'ST3GAL5', 'RPL28', 'CES1', 'ARPC3', 'SPINT2', 'MYOF', 'PPP3CA', 'KYNU', 'CYP24A1', 'HSP90AB1', 'TXN', 'GLS', 'ENO1', 'YWHAE', 'SOX4', 'RIN2', 'CNN3', 'S100A6', 'MGST1', 'OCIAD2', 'LRRC75A', 'ID3', 'NAP1L1', 'SKIL', 'SCD', 'PSMD14', 'SLC2A3', 'PSMD2', 'GTPBP4', 'BTG1', 'GLRX', 'MPRIP', 'UBA6', 'CEP170', 'RDX', 'CENPA', 'ELK3', 'IL11', 'LACTB', 'FBXO22', 'CLPTM1L', 'SSB', 'TSPAN5', 'CCDC85B', 'RHOF', 'NR0B1', 'BCL2A1', 'RASSF10', 'PODXL', 'MFSD12', 'QPCT', 'CD9', 'APOBEC3C', 'AKAP12', 'PRMT5', 'SLC25A37', 'CDC42EP3', 'SMC4', 'CCNB1', 'CSRP1', 'MLLT11', 'EPAS1', 'NT5E', 'ATP5G1', 'KMT5A', 'KLF6', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'PRSS3', 'TPX2', 'DKK1', 'SLN', 'C15orf48', 'CDC20', 'CPLX2', 'GPRC5A', 'LAMC2', 'SRGAP1', 'PDLIM7', 'HJURP', 'BCAT2', 'ANTXR1', 'PLGRKT', 'UBB', 'NPM1', 'SLU7', 'F2RL1', 'ISG20', 'PIR', 'TRIM47', 'GPX2', 'FLNB', 'COL5A2', 'SYT13', 'PLEK2', 'ULK1', 'PSMD8', 'S100A13', 'ANXA2', 'PMEPA1', 'RUVBL2', 'TNFRSF1A', 'ZFP36L1', 'PCSK1N', 'SSR3', 'AKR1C2', 'MT1X', 'GAPDH', 'MYL12B', 'MCL1', 'PRSS23', 'ELF3', 'IGFBP7', 'PSMD4', 'NUSAP1', 'FDXR', 'UPP1', 'HSP90AA1', 'S100A16', 'NUPR1', 'EZR', 'TXNDC9', 'GIP', 'HSPB1', 'PPP1R14A', 'MLXIP', 'TMEM41B', 'ACTG1', 'CDK2AP2', 'RAN', 'TMBIM6', 'ARL6IP1', 'ETFB', 'ITGA5', 'SERPINE2', 'CALM2', 'AURKA', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'TAGLN', 'SLC3A2', 'MYC', 'CCT2', 'MGLL', 'PHLDA3', 'PLAUR', 'TRAM1', 'G6PD', 'UBE2S', 'B4GALT1', 'CYBA', 'PNPT1', 'PDIA6', 'TUBA1B', 'STMN1', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'SPP1', 'GADD45A', 'NEK6', 'PDLIM5', 'COL4A2', 'LGALS3', 'JAK1', 'RND3', 'NTS', 'DKC1', 'PRDX1', 'TXNRD1', 'RASSF1', 'AKR1B1', 'TGFBI', 'OSBPL8', 'CCNB2', 'SYT1', 'SULT2B1', 'FN1', 'SCCPDH', 'POLR2L', 'GABARAPL1', 'TESC', 'SRGN', 'MBOAT2', 'IGFBP3', 'DSE', 'ACTB', 'KRT81', 'NUDT19', 'SH3BGRL3', 'DOLK', 'RAP2B', 'TUBA1C', 'NUAK1', 'CDKN3', 'RAB3B', 'ITGA3', 'GPX1', 'RPS27L', 'PACSIN3', 'HSPA8', 'PDLIM2', 'CLU', 'PKM', 'COL22A1', 'PSMA5', 'SLPI', 'FTL', 'SDC4', 'PSMB3', 'AKR1B10', 'ACOT9', 'FBXO32', 'NAA38', 'COL5A1', 'CTNNAL1', 'GNPNAT1', 'PRR11', 'CDCA3', 'CDK1', 'MYO10', 'ETS2', 'TPM1', 'CEBPB', 'DHRS2', 'CTTN', 'PTHLH', 'PLK1', 'GLIPR1', 'GOLIM4', 'BIRC5', 'TSPAN15', 'ODC1', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'SPOCK1', 'CDKN1A', 'LBH', 'CAV1', 'MYL12A', 'NQO1', 'PSME2', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TGFBR1', 'TKT', 'ALDH1A1', 'ZWINT', 'TGM2', 'AHNAK2', 'ITGB5', 'KRT7', 'RQCD1', 'S100A4', 'CTSL', 'TMSB10', 'PTPRJ', 'FGFR1', 'SUCLG1', 'ITGA2', 'TOP2A', 'S100A3', 'ILF2', 'SGCE', 'MRPS22', 'CCT5', 'RBP1', 'PVR', 'HMGB2', 'MT2A', 'PTTG1', 'CDH2', 'GRAMD1A', 'GRB10', 'PDCD5', 'VCAN', 'CDC25B', 'SLC2A1', 'TUBB', 'BAMBI', 'EIF2S3', 'FHL1', 'INO80C', 'PTPRS', 'HES1', 'AP2M1', 'NPTX1', 'CXCL1', 'DOCK5', 'TP53I3', 'MAF', 'FOS', 'ANXA3', 'DHRS3', 'CDC42SE1', 'BMP1', 'ZFP36', 'IL32', 'SGK1', 'DAAM1', 'COPZ2', 'CTPS1', 'NPC2', 'STC1', 'PSMA4', 'SH3KBP1', 'DHRS7', 'CD63', 'PRMT1', 'TPM2', 'TUBB6', 'COTL1', 'C1QBP', 'PTGR1', 'LMNA', 'UBC', 'RAET1G', 'CYB5A', 'MT3', 'LDHB', 'PGM2L1', 'TIMP2', 'IGFBP4', 'ALDH3A1', 'PYCR1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'MAP1B', 'COL4A1', 'HNRNPH1', 'FRMD6', 'PRC1', 'FAM89B', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[['IDA', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['ISS'], ['IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'ISS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['ISS', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IBA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['HTP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['HTP', 'HDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['HTP', 'ISS', 'IBA', 'IEA'], ['HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['IDA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['HDA', 'IBA'], ['HTP'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS'], ['ISS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'IEA'], ['ISS'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IEA'], ['IBA'], ['IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA', 'IMP', 'IBA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['TAS'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'HTP', 'HDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'HTP', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'ISS', 'IEA'], ['HTP'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['TAS'], ['HTP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC'], ['IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['HTP', 'HDA', 'TAS'], ['TAS'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['HTP', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['HTP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'HTP', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['IEA'], ['IPI', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HDA', 'IBA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IBA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'ISS', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['HTP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'HTP', 'TAS', 'IEA'], ['IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3748,42 +4012,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GO:0070161</t>
+          <t>GO:0005829</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>anchoring junction</t>
+          <t>cytosol</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.005042232589773696</v>
+        <v>0.001996146017181339</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>"A cell junction that mechanically attaches a cell (and its cytoskeleton) to neighboring cells or to the extracellular matrix." [ISBN:0815332181]</t>
+          <t>"The part of the cytoplasm that does not contain organelles but which does contain other particulate matter, such as protein complexes." [GOC:hjd, GOC:jl]</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>974</v>
       </c>
       <c r="H12" t="n">
         <v>464</v>
       </c>
       <c r="I12" t="n">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="J12" t="n">
         <v>2717</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1443965517241379</v>
+        <v>0.4698275862068966</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3101851851851852</v>
+        <v>0.2238193018480493</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3792,64 +4056,64 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>['GO:0030054']</t>
+          <t>['GO:0005737', 'GO:0110165']</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['CD44', 'CLDN4', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PDLIM5', 'PLAUR', 'ACTB', 'RND1', 'HSPA5', 'TSPAN4', 'CSRP1', 'SLC3A2', 'S100A11', 'CTTN', 'B4GALT1', 'FRMD6', 'HSPA8', 'HMGA1', 'ITGB5', 'HSPB1', 'JAK1', 'DOCK5', 'RND3', 'ZNF185', 'YWHAE', 'CDCA3', 'PPIB', 'TGM2', 'TGFBR1', 'FSCN1', 'CADM1', 'PDLIM2', 'FLNB', 'CDC42', 'ITGA3', 'NPM1', 'CD9', 'PPP3CA', 'ILK', 'JUP', 'FHL1', 'MPRIP', 'EZR', 'ARPC3', 'SH3KBP1', 'PODXL', 'CDH2', 'ANXA2', 'CNN3', 'AKAP12', 'PVR', 'RAP2B', 'CCDC85B', 'PDLIM7', 'ITGA2', 'RDX', 'FLOT1', 'PTPRJ', 'CTNNB1', 'VIM', 'ESAM', 'PCDH9', 'PPP1CB', 'ITGA5', 'SLC2A1']</t>
+          <t>['HSPA2', 'TXNRD2', 'CXXC5', 'CTNNB1', 'PPIB', 'TK1', 'MYL6', 'RAP1GAP', 'RHOD', 'CDA', 'TUBA4A', 'EIF6', 'CMTM3', 'SPATS2', 'FSCN1', 'HSPA5', 'TUBB4B', 'PYCARD', 'RPL28', 'CES1', 'ARPC3', 'PPP3CA', 'KYNU', 'HSP90AB1', 'TXN', 'GLS', 'ENO1', 'YWHAE', 'RIN2', 'CNN3', 'S100A6', 'PSMD14', 'PSMD2', 'GTPBP4', 'GLRX', 'MPRIP', 'UBA6', 'CEP170', 'CENPA', 'LACTB', 'FBXO22', 'SSB', 'RHOF', 'BCL2A1', 'RASSF10', 'AKAP12', 'PRMT5', 'CDC42EP3', 'SMC4', 'CCNB1', 'MLLT11', 'EPAS1', 'NT5E', 'KMT5A', 'KLF6', 'AKR1C3', 'PPP1CB', 'TPX2', 'CDC20', 'CPLX2', 'SRGAP1', 'PDLIM7', 'HJURP', 'UBB', 'NPM1', 'SLU7', 'PIR', 'TRIM47', 'GPX2', 'FLNB', 'ULK1', 'PSMD8', 'S100A13', 'ANXA2', 'RUVBL2', 'ZFP36L1', 'AKR1C2', 'GAPDH', 'MYL12B', 'MCL1', 'ELF3', 'PSMD4', 'UPP1', 'HSP90AA1', 'S100A16', 'EZR', 'TXNDC9', 'HSPB1', 'PPP1R14A', 'ACTG1', 'RAN', 'ARL6IP1', 'SERPINE2', 'CALM2', 'AURKA', 'RGS3', 'FABP5', 'LCE3D', 'CCT2', 'MGLL', 'G6PD', 'UBE2S', 'PNPT1', 'STMN1', 'RND1', 'CD44', 'NEK6', 'PDLIM5', 'LGALS3', 'JAK1', 'RND3', 'PRDX1', 'TXNRD1', 'AKR1B1', 'OSBPL8', 'CCNB2', 'SYT1', 'SULT2B1', 'POLR2L', 'GABARAPL1', 'TESC', 'ACTB', 'KRT81', 'NUDT19', 'SH3BGRL3', 'RAP2B', 'CDKN3', 'GPX1', 'RPS27L', 'PACSIN3', 'HSPA8', 'CLU', 'PKM', 'PSMA5', 'FTL', 'PSMB3', 'AKR1B10', 'FBXO32', 'CTNNAL1', 'GNPNAT1', 'CDCA3', 'CDK1', 'MYO10', 'ETS2', 'TPM1', 'CTTN', 'PTHLH', 'PLK1', 'BIRC5', 'TSPAN15', 'ODC1', 'HMGA1', 'PHKG1', 'CDC42', 'TMSB4X', 'CDKN1A', 'MYL12A', 'NQO1', 'PSME2', 'VIM', 'FTH1', 'PGK1', 'LGALS1', 'TKT', 'ALDH1A1', 'ZWINT', 'TGM2', 'AHNAK2', 'KRT7', 'RQCD1', 'S100A4', 'FGFR1', 'S100A3', 'ILF2', 'CCT5', 'RBP1', 'MT2A', 'PTTG1', 'GRAMD1A', 'GRB10', 'PDCD5', 'CDC25B', 'SLC2A1', 'TUBB', 'EIF2S3', 'FHL1', 'INO80C', 'PTPRS', 'AP2M1', 'DOCK5', 'TP53I3', 'FOS', 'ZFP36', 'IL32', 'SGK1', 'DAAM1', 'COPZ2', 'CTPS1', 'PSMA4', 'SH3KBP1', 'PRMT1', 'TPM2', 'COTL1', 'C1QBP', 'LMNA', 'UBC', 'CYB5A', 'MT3', 'LDHB', 'PGM2L1', 'ALDH3A1', 'ECH1', 'JUP', 'MAP1B', 'HNRNPH1', 'PRC1', 'ILK', 'KPNA2']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'ISS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA', 'IBA'], ['HDA', 'IEA'], ['IDA', 'IMP', 'HDA', 'ISS'], ['IDA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IEA'], ['HDA'], ['IDA'], ['HDA'], ['HDA'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['ISS'], ['IBA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IEA'], ['ISS'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['IDA', 'HDA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IEA'], ['IEA']]</t>
+          <t>[['IDA', 'IBA'], ['IDA', 'IBA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IBA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IPI', 'HDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'TAS'], ['IDA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IBA'], ['IBA'], ['TAS'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['IDA', 'IBA'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IEA'], ['TAS'], ['TAS'], ['IDA'], ['TAS'], ['TAS'], ['IDA'], ['IDA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['ISS', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['ISS', 'IEA'], ['IDA'], ['IBA', 'TAS'], ['IBA'], ['IBA', 'TAS'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['IBA', 'TAS'], ['IBA', 'TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEA'], ['IDA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['IDA'], ['IEA'], ['IDA'], ['IDA', 'TAS'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'TAS'], ['IDA'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['IDA'], ['TAS'], ['IDA'], ['TAS'], ['IEA'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['TAS'], ['TAS', 'IEA'], ['TAS'], ['IDA'], ['IDA', 'TAS'], ['TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS'], ['IDA', 'TAS'], ['TAS', 'IEA'], ['IDA', 'ISS', 'TAS'], ['TAS'], ['ISS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['TAS'], ['IDA', 'TAS'], ['IDA', 'TAS', 'NAS']]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GO:0099080</t>
+          <t>GO:0009987</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>supramolecular complex</t>
+          <t>cellular process</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.007775571530290674</v>
+        <v>0.003881946687949618</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>"A cellular component that consists of an indeterminate number of proteins or macromolecular complexes, organized into a regular, higher-order structure such as a polymer, sheet, network or a fiber." [GOC:dos]</t>
+          <t>"Any process that is carried out at the cellular level, but not necessarily restricted to a single cell. For example, cell communication occurs among more than one cell, but occurs at the cellular level." [GOC:go_curators, GOC:isa_complete]</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>263</v>
+        <v>2402</v>
       </c>
       <c r="H13" t="n">
         <v>464</v>
       </c>
       <c r="I13" t="n">
-        <v>77</v>
+        <v>441</v>
       </c>
       <c r="J13" t="n">
         <v>2717</v>
       </c>
       <c r="K13" t="n">
-        <v>0.165948275862069</v>
+        <v>0.9504310344827587</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2927756653992395</v>
+        <v>0.1835970024979184</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3858,64 +4122,64 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>['GO:0110165']</t>
+          <t>['GO:0008150']</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>['CENPW', 'SSB', 'RQCD1', 'ISG20', 'ACTG1', 'BIRC5', 'COL5A1', 'SDC4', 'PDLIM5', 'RASSF1', 'TUBA1B', 'MAP1B', 'CDK2AP2', 'ACTB', 'CSRP1', 'CTPS1', 'TPX2', 'RPL28', 'ENO1', 'CTTN', 'CCNB1', 'KRT7', 'HSPA8', 'COL4A1', 'LTBP4', 'CCT2', 'FBXO22', 'CCT5', 'HSPB1', 'GABARAPL1', 'ZWINT', 'FBXO32', 'STMN1', 'CEP170', 'NUSAP1', 'PDLIM2', 'FLNB', 'NEK6', 'EIF6', 'CDC42', 'LMNA', 'ZFP36L1', 'AHNAK2', 'MT3', 'CALM2', 'TUBB6', 'CDC20', 'MYL12B', 'PPP3CA', 'ILK', 'JUP', 'HJURP', 'COTL1', 'EZR', 'ARPC3', 'APOBEC3C', 'TPM2', 'TUBB', 'COL5A2', 'TUBA4A', 'AURKA', 'CDK1', 'PRC1', 'PSMA4', 'TUBA1C', 'PDLIM7', 'TUBB4B', 'CTNNB1', 'COL1A1', 'PYCARD', 'VIM', 'KRT81', 'ZFP36', 'COL4A2', 'TPM1', 'SLC2A1', 'PLK1']</t>
+          <t>['HSPA2', 'EMG1', 'HAPLN3', 'TXNRD2', 'UTP18', 'CXXC5', 'CTNNB1', 'PPIB', 'TK1', 'MYL6', 'FSTL3', 'RAP1GAP', 'RHOD', 'ANGPTL4', 'CDA', 'TUBA4A', 'METRN', 'EIF6', 'CMTM3', 'SLC22A18', 'MFGE8', 'EVA1A', 'FSCN1', 'FURIN', 'HSPA5', 'ACP2', 'TUBB4B', 'PYCARD', 'CADM1', 'ST3GAL5', 'RPL28', 'CES1', 'LTBP4', 'ARPC3', 'GINS2', 'SPINT2', 'TNFRSF12A', 'NEAT1', 'MYOF', 'PAQR5', 'PPP3CA', 'C1orf56', 'KYNU', 'CYP24A1', 'HSP90AB1', 'TXN', 'GLS', 'ENO1', 'TIMP4', 'YWHAE', 'BBX', 'SOX4', 'RIN2', 'CLDN4', 'CNN3', 'S100A6', 'MGST1', 'FAM64A', 'OCIAD2', 'LRRC75A', 'ID3', 'NAP1L1', 'SKIL', 'SCD', 'KCNMA1', 'PSMD14', 'SLC2A3', 'PSMD2', 'TSPAN4', 'CKS1B', 'GTPBP4', 'BTG1', 'GLRX', 'UBA6', 'RDX', 'CENPA', 'ESAM', 'ELK3', 'IL11', 'LACTB', 'FBXO22', 'CLPTM1L', 'SSB', 'TSPAN5', 'CCDC85B', 'RHOF', 'NR0B1', 'BCL2A1', 'RASSF10', 'PODXL', 'MFSD12', 'QPCT', 'ADAM19', 'CD9', 'APOBEC3C', 'AKAP12', 'PRMT5', 'SLC25A37', 'CDC42EP3', 'SMC4', 'CCNB1', 'CSRP1', 'MLLT11', 'EPAS1', 'LMO4', 'DMKN', 'NT5E', 'ATP5G1', 'KMT5A', 'KLF6', 'AKR1C3', 'PPP1CB', 'APLP2', 'COL1A1', 'FLOT1', 'CNTN1', 'RSPO3', 'PRSS3', 'TPX2', 'HMGA2', 'DKK1', 'SLN', 'CDC20', 'FXYD5', 'CPLX2', 'GPRC5A', 'LAMC2', 'SRGAP1', 'PDLIM7', 'HJURP', 'BCAT2', 'ANTXR1', 'KCNG1', 'PLGRKT', 'UBB', 'NPM1', 'SLU7', 'F2RL1', 'CCL2', 'ISG20', 'PIR', 'TRIM47', 'GPX2', 'FLNB', 'COL5A2', 'SYT13', 'PLEK2', 'ULK1', 'PSMD8', 'AXL', 'S100A13', 'ANXA2', 'PMEPA1', 'RUVBL2', 'TNFRSF1A', 'ZFP36L1', 'PCSK1N', 'SSR3', 'AKR1C2', 'MT1X', 'GAPDH', 'MCL1', 'PRSS23', 'ELF3', 'IGFBP7', 'PSMD4', 'NUSAP1', 'FDXR', 'UPP1', 'HSP90AA1', 'AVPI1', 'NUPR1', 'EZR', 'TXNDC9', 'GIP', 'HSPB1', 'PPP1R14A', 'MLXIP', 'TMEM41B', 'ACTG1', 'CDK2AP2', 'RAN', 'TMBIM6', 'ARL6IP1', 'ETFB', 'ITGA5', 'SERPINE2', 'CALM2', 'AURKA', 'S100A11', 'RGS3', 'FABP5', 'LCE3D', 'TAGLN', 'SLC3A2', 'MYC', 'MEG3', 'CCT2', 'MGLL', 'PHLDA3', 'PLAUR', 'TRAM1', 'CXCL5', 'G6PD', 'MMP15', 'GNG4', 'UBE2S', 'B4GALT1', 'CBX6', 'CYBA', 'PNPT1', 'PDIA6', 'TUBA1B', 'STMN1', 'ZBED2', 'HMGB1', 'RND1', 'CD44', 'GALNT14', 'SPP1', 'GADD45A', 'FOXD1', 'SNHG8', 'TMEM120B', 'NEK6', 'PDLIM5', 'WDR43', 'COL4A2', 'LGALS3', 'JAK1', 'TFPI2', 'RND3', 'RPL22L1', 'NTS', 'DKC1', 'PRDX1', 'TXNRD1', 'RASSF1', 'AKR1B1', 'CXCL2', 'TGFBI', 'OSBPL8', 'CCNB2', 'SYT1', 'SULT2B1', 'JUNB', 'LTBP3', 'FN1', 'PCDH9', 'SCCPDH', 'POLR2L', 'GABARAPL1', 'TESC', 'SRGN', 'MBOAT2', 'IGFBP3', 'DSE', 'CKS2', 'ACTB', 'KRT81', 'NUDT19', 'SH3BGRL3', 'DOLK', 'RAP2B', 'TUBA1C', 'NUAK1', 'CDKN3', 'RAB3B', 'ITGA3', 'GPX1', 'RPS27L', 'PACSIN3', 'HSPA8', 'PDLIM2', 'CLU', 'PKM', 'PSMA5', 'ITGA11', 'NUAK2', 'SDC4', 'PSMB3', 'AKR1B10', 'ACOT9', 'TM7SF3', 'MALAT1', 'FBXO32', 'NMB', 'NAA38', 'COL5A1', 'CTNNAL1', 'GNPNAT1', 'PRR11', 'DDB2', 'CDCA3', 'CDK1', 'MYO10', 'ETS2', 'TPM1', 'AMIGO2', 'CENPW', 'CEBPB', 'DHRS2', 'CTTN', 'PTHLH', 'PLK1', 'BIRC5', 'TSPAN15', 'ODC1', 'TRA2A', 'HMGA1', 'PHKG1', 'S100A10', 'CDC42', 'TMSB4X', 'SPOCK1', 'CDKN1A', 'LBH', 'CAV1', 'MYL12A', 'NQO1', 'PSME2', 'SERPINE1', 'P4HA3', 'VIM', 'FTH1', 'PDIA4', 'PGK1', 'LGALS1', 'GAL', 'TGFBR1', 'TKT', 'ALDH1A1', 'SLAMF9', 'ZWINT', 'TGM2', 'AHNAK2', 'ITGB5', 'KRT7', 'RQCD1', 'S100A4', 'CTSL', 'TMSB10', 'PTPRJ', 'FGFR1', 'JUN', 'SUCLG1', 'ITGA2', 'TOP2A', 'ILF2', 'SGCE', 'MRPS22', 'LCE3E', 'CCT5', 'MORF4L2', 'RBP1', 'SNW1', 'PVR', 'HMGB2', 'MT2A', 'HPCAL1', 'PTTG1', 'BOP1', 'CDH2', 'GRAMD1A', 'MKI67', 'GRB10', 'PDCD5', 'VCAN', 'CDC25B', 'SLC2A1', 'TUBB', 'BAMBI', 'EIF2S3', 'FHL1', 'INO80C', 'PTPRS', 'HES1', 'AP2M1', 'NPTX1', 'CXCL1', 'DOCK5', 'SLC7A7', 'TP53I3', 'MAF', 'FOS', 'ANXA3', 'DHRS3', 'CDC42SE1', 'BMP1', 'ZFP36', 'SLC35F2', 'CXCL8', 'IL32', 'SGK1', 'DAAM1', 'COPZ2', 'CTPS1', 'NPC2', 'STC1', 'PSMA4', 'CD24', 'SH3KBP1', 'DHRS7', 'CD63', 'PRMT1', 'TPM2', 'TUBB6', 'COTL1', 'C1QBP', 'PTGR1', 'NTN4', 'LMNA', 'UBC', 'RAET1G', 'CYB5A', 'SLC7A11', 'MT3', 'CCDC80', 'LDHB', 'PGM2L1', 'TIMP2', 'ADGRG1', 'IGFBP4', 'ALDH3A1', 'PYCR1', 'ECH1', 'PUS1', 'CREM', 'JUP', 'MDM4', 'MAP1B', 'COL4A1', 'MIS18BP1', 'HNRNPH1', 'EMP3', 'FRMD6', 'PRC1', 'FAM89B', 'ILK', 'KPNA2', 'SEMA3C']</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[['IDA', 'IPI', 'IBA', 'IEA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS'], ['IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IDA'], ['IEA'], ['IDA'], ['IDA'], ['IBA', 'NAS', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IEA'], ['IDA'], ['IEA'], ['IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IBA'], ['IEA'], ['IEA'], ['IEA'], ['IDA'], ['TAS', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA'], ['IEA'], ['IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['NAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA']]</t>
+          <t>[['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['IDA', 'HMP'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['IMP', 'TAS', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['TAS', 'IC', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['ISS', 'IBA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['ISS'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IGI', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['TAS'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'TAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS'], ['IDA', 'ISS', 'ISO', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['HMP', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS'], ['IDA', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IEP', 'IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'IEA'], ['IBA'], ['IDA', 'TAS', 'IEA'], ['IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'HMP', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['IDA'], ['IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'HDA', 'HMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA'], ['ISS', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['ISS', 'IBA'], ['IMP', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA'], ['EXP', 'IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['HMP'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS'], ['IBA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IEP', 'ISS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['NAS'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'IBA'], ['IBA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IBA'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GO:BP</t>
+          <t>GO:CC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GO:0009987</t>
+          <t>GO:0070161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cellular process</t>
+          <t>anchoring junction</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01089090300064682</v>
+        <v>0.01313870156083368</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"Any process that is carried out at the cellular level, but not necessarily restricted to a single cell. For example, cell communication occurs among more than one cell, but occurs at the cellular level." [GOC:go_curators, GOC:isa_complete]</t>
+          <t>"A cell junction that mechanically attaches a cell (and its cytoskeleton) to neighboring cells or to the extracellular matrix." [ISBN:0815332181]</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2402</v>
+        <v>212</v>
       </c>
       <c r="H14" t="n">
         <v>464</v>
       </c>
       <c r="I14" t="n">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="J14" t="n">
         <v>2717</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9482758620689655</v>
+        <v>0.1400862068965517</v>
       </c>
       <c r="L14" t="n">
-        <v>0.183180682764363</v>
+        <v>0.3066037735849056</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3924,17 +4188,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>['GO:0008150']</t>
+          <t>['GO:0030054']</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>['TXNDC9', 'CD44', 'LDHB', 'TM7SF3', 'TAGLN', 'CENPW', 'CD63', 'ANXA3', 'SPOCK1', 'UTP18', 'LAMC2', 'SSB', 'CLDN4', 'FOS', 'NQO1', 'RQCD1', 'PTGR1', 'FURIN', 'ITGA11', 'ISG20', 'OCIAD2', 'ACTG1', 'UBB', 'BIRC5', 'BOP1', 'HNRNPH1', 'GNPNAT1', 'KLF6', 'COL5A1', 'SDC4', 'CAV1', 'GADD45A', 'CLU', 'PDLIM5', 'LMO4', 'PLAUR', 'CCL2', 'MIS18BP1', 'JUN', 'TMSB10', 'IL32', 'CCDC80', 'GLRX', 'NAP1L1', 'ATP5G1', 'TOP2A', 'RASSF1', 'TUBA1B', 'DAAM1', 'BBX', 'RSPO3', 'MAP1B', 'CDK2AP2', 'ACTB', 'RAN', 'PPP1R14A', 'RND1', 'HSPA5', 'CNTN1', 'TSPAN4', 'GALNT14', 'KCNMA1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'CXCL5', 'DMKN', 'COPZ2', 'CTPS1', 'TSPAN5', 'AKR1B1', 'MLLT11', 'NT5E', 'CDC25B', 'MYL12A', 'TPX2', 'RPL28', 'PSMD8', 'SEMA3C', 'ENO1', 'EMP3', 'TMBIM6', 'GRB10', 'TFPI2', 'ID3', 'POLR2L', 'HSP90AB1', 'BMP1', 'MBOAT2', 'PSMB3', 'CKS2', 'IGFBP3', 'TRAM1', 'TIMP2', 'CTTN', 'AKR1B10', 'TMEM120B', 'IGFBP7', 'B4GALT1', 'SGK1', 'MAF', 'BCAT2', 'CDC42SE1', 'GRAMD1A', 'PAQR5', 'LCE3E', 'CCNB1', 'KRT7', 'FRMD6', 'ELK3', 'MT2A', 'PSME2', 'HSPA8', 'HAPLN3', 'COL4A1', 'LTBP4', 'SCD', 'PSMD14', 'PKM', 'TKT', 'AVPI1', 'CD24', 'IGFBP4', 'SLC22A18', 'PTTG1', 'GIP', 'PDIA6', 'PCSK1N', 'OSBPL8', 'PGK1', 'CCT2', 'RBP1', 'UBE2S', 'KMT5A', 'HMGA1', 'CXCL1', 'NTS', 'MFGE8', 'PTHLH', 'CPLX2', 'CMTM3', 'ITGB5', 'FBXO22', 'MGLL', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'LCE3D', 'BTG1', 'AKR1C3', 'MRPS22', 'C1orf56', 'CES1', 'JAK1', 'GAL', 'UBA6', 'SPINT2', 'SCCPDH', 'CYBA', 'DOCK5', 'NUDT19', 'GABARAPL1', 'CTNNAL1', 'NUAK1', 'CXCL2', 'SLC25A37', 'CYP24A1', 'ST3GAL5', 'F2RL1', 'BAMBI', 'RND3', 'ZWINT', 'FBXO32', 'MMP15', 'DHRS2', 'KYNU', 'YWHAE', 'PIR', 'CDCA3', 'PMEPA1', 'CBX6', 'GLS', 'TRA2A', 'SERPINE2', 'ALDH1A1', 'PNPT1', 'DSE', 'MEG3', 'TIMP4', 'G6PD', 'MYO10', 'ETFB', 'MYOF', 'PYCR1', 'SLC7A11', 'KCNG1', 'PGM2L1', 'ALDH3A1', 'STMN1', 'ADGRG1', 'MDM4', 'NUSAP1', 'HMGB1', 'FABP5', 'TXN', 'ANGPTL4', 'PPIB', 'HSPA2', 'NMB', 'MYC', 'RPS27L', 'ARL6IP1', 'TGM2', 'SLN', 'ADAM19', 'EVA1A', 'RUVBL2', 'ODC1', 'GPRC5A', 'TGFBR1', 'FSCN1', 'NTN4', 'CADM1', 'PDLIM2', 'APLP2', 'AKR1C2', 'DKK1', 'FLNB', 'RHOF', 'NEK6', 'FGFR1', 'WDR43', 'CEBPB', 'GPX1', 'EIF6', 'MORF4L2', 'RHOD', 'AXL', 'CDC42', 'LMNA', 'SLU7', 'SH3BGRL3', 'CREM', 'PDCD5', 'PLGRKT', 'DHRS3', 'ZFP36L1', 'AHNAK2', 'EMG1', 'CDKN1A', 'MT3', 'RAET1G', 'RASSF10', 'ILF2', 'CXXC5', 'FSTL3', 'MYL6', 'CALM2', 'S100A4', 'FTH1', 'TUBB6', 'TMEM41B', 'LGALS1', 'PTPRS', 'PRR11', 'ZBED2', 'CYB5A', 'SYT13', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'SMC4', 'TESC', 'LTBP3', 'DHRS7', 'TK1', 'TRIM47', 'RIN2', 'NPM1', 'CD9', 'CDC20', 'ETS2', 'PPP3CA', 'SLAMF9', 'SULT2B1', 'LBH', 'ILK', 'JUP', 'FHL1', 'HJURP', 'ACP2', 'FOXD1', 'COL22A1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'COTL1', 'SNHG8', 'MFSD12', 'SLC35F2', 'EZR', 'PSMD2', 'ARPC3', 'PSMD4', 'PUS1', 'APOBEC3C', 'TPM2', 'SH3KBP1', 'NPTX1', 'PODXL', 'CDH2', 'ANXA2', 'HMGA2', 'ELF3', 'ACOT9', 'ANTXR1', 'TUBB', 'S100A6', 'FAM64A', 'MALAT1', 'COL5A2', 'CNN3', 'TUBA4A', 'AURKA', 'CDK1', 'MGST1', 'NUAK2', 'DDB2', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'PRC1', 'UBC', 'METRN', 'SKIL', 'HES1', 'HMGB2', 'DKC1', 'NAA38', 'RAP2B', 'CCDC85B', 'PSMA4', 'MT1X', 'SGCE', 'PHKG1', 'TUBA1C', 'PDLIM7', 'RGS3', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'SYT1', 'VCAN', 'NPC2', 'FN1', 'ITGA2', 'GTPBP4', 'S100A13', 'AMIGO2', 'RDX', 'JUNB', 'EPAS1', 'TP53I3', 'RPL22L1', 'LACTB', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'TMSB4X', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'TNFRSF12A', 'GPX2', 'HAGHL', 'SSR3', 'BCL2A1', 'VIM', 'ESAM', 'GINS2', 'FXYD5', 'KRT81', 'PRMT1', 'HSP90AA1', 'PCDH9', 'CXCL8', 'PPP1CB', 'SLC7A7', 'SPP1', 'MKI67', 'MCL1', 'STC1', 'ZFP36', 'RAB3B', 'COL4A2', 'CDC42EP3', 'ITGA5', 'UPP1', 'SNW1', 'CDKN3', 'MLXIP', 'NR0B1', 'TPM1', 'SOX4', 'NUPR1', 'PHLDA3', 'CENPA', 'CA12', 'KPNA2', 'SUCLG1', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'DOLK', 'CLPTM1L', 'INO80C', 'PLEK2', 'AP2M1', 'C1QBP', 'FDXR', 'QPCT', 'CKS1B', 'PRDX1', 'PDIA4', 'PLK1']</t>
+          <t>['CTNNB1', 'PPIB', 'ZNF185', 'FSCN1', 'HSPA5', 'CADM1', 'ARPC3', 'YWHAE', 'CLDN4', 'CNN3', 'TSPAN4', 'MPRIP', 'RDX', 'ESAM', 'CCDC85B', 'PODXL', 'CD9', 'AKAP12', 'CSRP1', 'PPP1CB', 'FLOT1', 'PDLIM7', 'NPM1', 'FLNB', 'ANXA2', 'EZR', 'HSPB1', 'ACTG1', 'ITGA5', 'S100A11', 'SLC3A2', 'PLAUR', 'B4GALT1', 'RND1', 'CD44', 'PDLIM5', 'JAK1', 'RND3', 'ACTB', 'RAP2B', 'ITGA3', 'HSPA8', 'PDLIM2', 'ITGA11', 'SDC4', 'CDCA3', 'CTTN', 'HMGA1', 'CDC42', 'CAV1', 'VIM', 'TGFBR1', 'TGM2', 'ITGB5', 'PTPRJ', 'ITGA2', 'PVR', 'CDH2', 'SLC2A1', 'FHL1', 'DOCK5', 'SH3KBP1', 'JUP', 'FRMD6', 'ILK']</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[['IBA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IDA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IEA'], ['IMP', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS'], ['IMP', 'HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['HMP', 'IBA', 'IEA'], ['IGI', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEP', 'IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'IEA'], ['IMP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['NAS'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IMP', 'IGI', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HMP'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS'], ['IDA', 'IMP', 'ISS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'ISO', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['IBA'], ['NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['EXP', 'IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['TAS'], ['NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['NAS'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA']]</t>
+          <t>[['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IEA'], ['IDA', 'IEA'], ['HDA'], ['ISS'], ['HDA'], ['HDA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['ISS'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IDA', 'IBA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['IDA', 'HDA', 'IBA'], ['HDA'], ['IDA', 'ISS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['IEA'], ['HDA', 'IEA'], ['IDA'], ['IDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['IDA', 'IMP', 'HDA', 'ISS'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['IBA'], ['IDA', 'HDA'], ['IEA'], ['IDA'], ['HDA', 'IEA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['IDA', 'IEA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'IEA'], ['IDA', 'HDA', 'IEA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['HDA'], ['IEA'], ['IEA'], ['IDA', 'HDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4259,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>['CD44', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PLAUR', 'ACTB', 'HSPA5', 'TSPAN4', 'CSRP1', 'CTTN', 'HSPA8', 'HMGA1', 'ITGB5', 'HSPB1', 'JAK1', 'RND3', 'ZNF185', 'YWHAE', 'PPIB', 'TGM2', 'FLNB', 'CDC42', 'ITGA3', 'NPM1', 'CD9', 'ILK', 'JUP', 'FHL1', 'MPRIP', 'EZR', 'ARPC3', 'SH3KBP1', 'CDH2', 'CNN3', 'AKAP12', 'PVR', 'PDLIM7', 'ITGA2', 'RDX', 'FLOT1', 'CTNNB1', 'VIM', 'PPP1CB', 'ITGA5']</t>
+          <t>['CTNNB1', 'PPIB', 'ZNF185', 'HSPA5', 'ARPC3', 'YWHAE', 'CNN3', 'TSPAN4', 'MPRIP', 'RDX', 'CD9', 'AKAP12', 'CSRP1', 'PPP1CB', 'FLOT1', 'PDLIM7', 'NPM1', 'FLNB', 'EZR', 'HSPB1', 'ACTG1', 'ITGA5', 'PLAUR', 'CD44', 'JAK1', 'RND3', 'ACTB', 'ITGA3', 'HSPA8', 'ITGA11', 'SDC4', 'CTTN', 'HMGA1', 'CDC42', 'CAV1', 'VIM', 'TGM2', 'ITGB5', 'ITGA2', 'PVR', 'CDH2', 'FHL1', 'SH3KBP1', 'JUP', 'ILK']</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['ISS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA']]</t>
+          <t>[['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['ISS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
@@ -4061,59 +4325,59 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>['CD44', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PLAUR', 'ACTB', 'HSPA5', 'TSPAN4', 'CSRP1', 'CTTN', 'HSPA8', 'HMGA1', 'ITGB5', 'HSPB1', 'JAK1', 'RND3', 'ZNF185', 'YWHAE', 'PPIB', 'TGM2', 'FLNB', 'CDC42', 'ITGA3', 'NPM1', 'CD9', 'ILK', 'JUP', 'FHL1', 'MPRIP', 'EZR', 'ARPC3', 'SH3KBP1', 'CDH2', 'CNN3', 'AKAP12', 'PVR', 'PDLIM7', 'ITGA2', 'RDX', 'FLOT1', 'CTNNB1', 'VIM', 'PPP1CB', 'ITGA5']</t>
+          <t>['CTNNB1', 'PPIB', 'ZNF185', 'HSPA5', 'ARPC3', 'YWHAE', 'CNN3', 'TSPAN4', 'MPRIP', 'RDX', 'CD9', 'AKAP12', 'CSRP1', 'PPP1CB', 'FLOT1', 'PDLIM7', 'NPM1', 'FLNB', 'EZR', 'HSPB1', 'ACTG1', 'ITGA5', 'PLAUR', 'CD44', 'JAK1', 'RND3', 'ACTB', 'ITGA3', 'HSPA8', 'ITGA11', 'SDC4', 'CTTN', 'HMGA1', 'CDC42', 'CAV1', 'VIM', 'TGM2', 'ITGB5', 'ITGA2', 'PVR', 'CDH2', 'FHL1', 'SH3KBP1', 'JUP', 'ILK']</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[['HDA'], ['IDA', 'HDA'], ['ISS'], ['IEA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['IDA', 'HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IEA']]</t>
+          <t>[['HDA'], ['HDA'], ['IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['IDA'], ['HDA'], ['HDA', 'IEA'], ['IDA', 'HDA'], ['HDA'], ['ISS'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['HDA'], ['HDA', 'ISS'], ['HDA'], ['HDA'], ['IDA', 'HDA'], ['IEA'], ['HDA', 'IEA'], ['HDA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA'], ['HDA'], ['HDA'], ['HDA', 'IBA'], ['IDA', 'HDA', 'IEA'], ['HDA'], ['HDA'], ['HDA'], ['IEA'], ['HDA'], ['IDA', 'HDA', 'IBA', 'IEA']]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GO:0031410</t>
+          <t>GO:0098609</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cytoplasmic vesicle</t>
+          <t>cell-cell adhesion</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02018528119468635</v>
+        <v>0.02383294544661132</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>"A vesicle found in the cytoplasm of a cell." [GOC:ai, GOC:mah, GOC:vesicles]</t>
+          <t>"The attachment of one cell to another cell via adhesion molecules." [GOC:dos]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>436</v>
+        <v>180</v>
       </c>
       <c r="H17" t="n">
         <v>464</v>
       </c>
       <c r="I17" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="J17" t="n">
         <v>2717</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.1228448275862069</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2568807339449541</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4122,64 +4386,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>['GO:0005737', 'GO:0097708']</t>
+          <t>['GO:0007155']</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'FURIN', 'OCIAD2', 'ACTG1', 'UBB', 'GNPNAT1', 'CAV1', 'CLU', 'PLAUR', 'NAP1L1', 'GLIPR1', 'RAN', 'HSPA5', 'SLC3A2', 'S100A11', 'COPZ2', 'HSP90AB1', 'TIMP2', 'CTTN', 'B4GALT1', 'GRAMD1A', 'HSPA8', 'PSMD14', 'PKM', 'GIP', 'PDIA6', 'PCSK1N', 'CCT2', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'CMTM3', 'ITGB5', 'LGALS3', 'JAK1', 'GAL', 'SCCPDH', 'CYBA', 'GABARAPL1', 'F2RL1', 'YWHAE', 'PMEPA1', 'SERPINE2', 'DSE', 'MYOF', 'HMGB1', 'FABP5', 'PPIB', 'GPRC5A', 'TGFBR1', 'APLP2', 'DKK1', 'FLNB', 'RHOF', 'FGFR1', 'RHOD', 'CDC42', 'MT3', 'ILF2', 'FTH1', 'PTPRS', 'SYT13', 'SLPI', 'CTSL', 'ULK1', 'RIN2', 'CD9', 'JUP', 'COTL1', 'MFSD12', 'EZR', 'PSMD2', 'SH3KBP1', 'NPTX1', 'GOLIM4', 'ANXA2', 'ANTXR1', 'TUBB', 'MGST1', 'SERPINE1', 'CDA', 'UBC', 'SKIL', 'RAP2B', 'TSPAN15', 'PRSS3', 'SYT1', 'NPC2', 'FN1', 'TUBB4B', 'FLOT1', 'TMSB4X', 'PSMA5', 'PTPRJ', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'VIM', 'HSP90AA1', 'RAB3B', 'ITGA5', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1', 'PDIA4']</t>
+          <t>['CTNNB1', 'FSTL3', 'PYCARD', 'CADM1', 'SPINT2', 'PPP3CA', 'SOX4', 'CLDN4', 'CNN3', 'GTPBP4', 'RDX', 'ESAM', 'PODXL', 'ADAM19', 'CD9', 'CSRP1', 'NT5E', 'FLOT1', 'CNTN1', 'FXYD5', 'CCL2', 'ANXA2', 'ZFP36L1', 'EZR', 'HSPB1', 'ACTG1', 'ITGA5', 'SERPINE2', 'S100A11', 'PLAUR', 'HMGB1', 'CD44', 'PDLIM5', 'LGALS3', 'JAK1', 'PCDH9', 'ACTB', 'RAP2B', 'ITGA3', 'ITGA11', 'SDC4', 'MYO10', 'AMIGO2', 'CEBPB', 'CAV1', 'MYL12A', 'LGALS1', 'ITGB5', 'ITGA2', 'PVR', 'CDH2', 'PTPRS', 'HES1', 'CD24', 'SLC7A11', 'JUP', 'ILK']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IEA']]</t>
+          <t>[['IMP', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IMP', 'ISS', 'IEA'], ['ISS', 'IBA'], ['IDA'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['ISS'], ['IEA'], ['IDA'], ['IMP'], ['IDA', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['HMP'], ['IDA'], ['IMP', 'IBA', 'IEA'], ['IBA'], ['NAS'], ['ISS'], ['IEA'], ['IEA'], ['IEP'], ['HMP'], ['HMP'], ['IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IMP'], ['IDA', 'IMP'], ['IMP', 'NAS'], ['IEA'], ['IDA', 'ISS'], ['IMP'], ['IEA'], ['HMP', 'NAS'], ['IDA'], ['IBA', 'IEA'], ['IBA'], ['IMP'], ['IEA'], ['ISS', 'IBA'], ['ISS', 'IEA'], ['IDA'], ['HMP'], ['IDA', 'IEA'], ['IMP', 'IBA'], ['IBA'], ['IBA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IDA', 'IBA', 'NAS'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['HMP']]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GO:CC</t>
+          <t>GO:BP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GO:0099081</t>
+          <t>GO:0065008</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supramolecular polymer</t>
+          <t>regulation of biological quality</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02286555199333306</v>
+        <v>0.02877661413571817</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>"A polymeric supramolecular structure." [GOC:dos]</t>
+          <t>"Any process that modulates a qualitative or quantitative trait of a biological quality. A biological quality is a measurable attribute of an organism or part of an organism, such as size, mass, shape, color, etc." [GOC:dph, GOC:isa_complete, GOC:mah, GOC:pr, GOC:vw]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="H18" t="n">
         <v>464</v>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="J18" t="n">
         <v>2717</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1357758620689655</v>
+        <v>0.2737068965517241</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3058252427184466</v>
+        <v>0.2470817120622568</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4188,215 +4452,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>['GO:0099080']</t>
+          <t>['GO:0065007']</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['ACTG1', 'BIRC5', 'COL5A1', 'SDC4', 'PDLIM5', 'RASSF1', 'TUBA1B', 'MAP1B', 'CDK2AP2', 'ACTB', 'CSRP1', 'CTPS1', 'TPX2', 'ENO1', 'CTTN', 'KRT7', 'HSPA8', 'COL4A1', 'LTBP4', 'CCT2', 'FBXO22', 'CCT5', 'HSPB1', 'GABARAPL1', 'FBXO32', 'STMN1', 'CEP170', 'NUSAP1', 'PDLIM2', 'FLNB', 'NEK6', 'EIF6', 'LMNA', 'AHNAK2', 'MT3', 'CALM2', 'TUBB6', 'MYL12B', 'PPP3CA', 'ILK', 'JUP', 'COTL1', 'EZR', 'ARPC3', 'TPM2', 'TUBB', 'COL5A2', 'TUBA4A', 'AURKA', 'CDK1', 'PRC1', 'TUBA1C', 'PDLIM7', 'TUBB4B', 'CTNNB1', 'COL1A1', 'PYCARD', 'VIM', 'KRT81', 'COL4A2', 'TPM1', 'SLC2A1', 'PLK1']</t>
+          <t>['CTNNB1', 'PPIB', 'ANGPTL4', 'FURIN', 'PYCARD', 'LTBP4', 'ARPC3', 'PPP3CA', 'HSP90AB1', 'YWHAE', 'SOX4', 'KCNMA1', 'GTPBP4', 'GLRX', 'RDX', 'ESAM', 'IL11', 'CLPTM1L', 'CD9', 'AKAP12', 'CDC42EP3', 'CSRP1', 'MLLT11', 'EPAS1', 'AKR1C3', 'FLOT1', 'DKK1', 'CDC20', 'CPLX2', 'BCAT2', 'KCNG1', 'UBB', 'NPM1', 'F2RL1', 'CCL2', 'TRIM47', 'ULK1', 'AXL', 'ANXA2', 'RUVBL2', 'ZFP36L1', 'PCSK1N', 'AKR1C2', 'GAPDH', 'MYL12B', 'HSP90AA1', 'EZR', 'GIP', 'HSPB1', 'TMEM41B', 'ACTG1', 'TMBIM6', 'SERPINE2', 'CALM2', 'AURKA', 'SLC3A2', 'CCT2', 'PLAUR', 'B4GALT1', 'CYBA', 'PNPT1', 'HMGB1', 'SPP1', 'FOXD1', 'PDLIM5', 'TFPI2', 'NTS', 'DKC1', 'RASSF1', 'AKR1B1', 'FN1', 'TESC', 'ACTB', 'RAP2B', 'RAB3B', 'GPX1', 'HSPA8', 'CLU', 'AKR1B10', 'TM7SF3', 'NMB', 'MYO10', 'TPM1', 'AMIGO2', 'DHRS2', 'CTTN', 'PLK1', 'BIRC5', 'CDC42', 'TMSB4X', 'CAV1', 'MYL12A', 'SERPINE1', 'VIM', 'GAL', 'ALDH1A1', 'RQCD1', 'CTSL', 'PTPRJ', 'FGFR1', 'ITGA2', 'CCT5', 'RBP1', 'CDH2', 'TUBB', 'BAMBI', 'FHL1', 'PTPRS', 'AP2M1', 'NPTX1', 'DOCK5', 'DHRS3', 'CDC42SE1', 'ZFP36', 'SGK1', 'CD24', 'SH3KBP1', 'DHRS7', 'COTL1', 'LMNA', 'SLC7A11', 'MT3', 'PYCR1', 'JUP', 'MDM4', 'MAP1B', 'ILK']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[['IDA', 'IBA', 'IEA'], ['IEA'], ['IMP', 'IBA', 'TAS', 'NAS'], ['IEA'], ['IBA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IBA'], ['IEA'], ['IEA'], ['IDA'], ['IBA', 'NAS', 'IEA'], ['IEA'], ['IMP', 'IEA'], ['ISS', 'IEA'], ['IDA'], ['IEA'], ['IDA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IEA'], ['IBA'], ['IEA'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IBA'], ['IEA'], ['IDA'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IBA', 'IEA'], ['IDA'], ['IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'NAS'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA'], ['TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA'], ['IDA', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IMP', 'IBA', 'IEA'], ['NAS'], ['IDA', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GO:CC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GO:0097708</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>intracellular vesicle</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.02303883088567201</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>"Any vesicle that is part of the intracellular region." [GOC:vesicles]</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>437</v>
-      </c>
-      <c r="H19" t="n">
-        <v>464</v>
-      </c>
-      <c r="I19" t="n">
-        <v>112</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2717</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2413793103448276</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.2562929061784897</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>query_1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>['GO:0031982', 'GO:0043231']</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>['CD44', 'CD63', 'ANXA3', 'FURIN', 'OCIAD2', 'ACTG1', 'UBB', 'GNPNAT1', 'CAV1', 'CLU', 'PLAUR', 'NAP1L1', 'GLIPR1', 'RAN', 'HSPA5', 'SLC3A2', 'S100A11', 'COPZ2', 'HSP90AB1', 'TIMP2', 'CTTN', 'B4GALT1', 'GRAMD1A', 'HSPA8', 'PSMD14', 'PKM', 'GIP', 'PDIA6', 'PCSK1N', 'CCT2', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'CMTM3', 'ITGB5', 'LGALS3', 'JAK1', 'GAL', 'SCCPDH', 'CYBA', 'GABARAPL1', 'F2RL1', 'YWHAE', 'PMEPA1', 'SERPINE2', 'DSE', 'MYOF', 'HMGB1', 'FABP5', 'PPIB', 'GPRC5A', 'TGFBR1', 'APLP2', 'DKK1', 'FLNB', 'RHOF', 'FGFR1', 'RHOD', 'CDC42', 'MT3', 'ILF2', 'FTH1', 'PTPRS', 'SYT13', 'SLPI', 'CTSL', 'ULK1', 'RIN2', 'CD9', 'JUP', 'COTL1', 'MFSD12', 'EZR', 'PSMD2', 'SH3KBP1', 'NPTX1', 'GOLIM4', 'ANXA2', 'ANTXR1', 'TUBB', 'MGST1', 'SERPINE1', 'CDA', 'UBC', 'SKIL', 'RAP2B', 'TSPAN15', 'PRSS3', 'SYT1', 'NPC2', 'FN1', 'TUBB4B', 'FLOT1', 'TMSB4X', 'PSMA5', 'PTPRJ', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'VIM', 'HSP90AA1', 'RAB3B', 'ITGA5', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'AP2M1', 'QPCT', 'PRDX1', 'PDIA4']</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>[['TAS'], ['IDA', 'HDA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['TAS'], ['IDA', 'IEA'], ['IEA'], ['IEA'], ['TAS'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IBA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA'], ['TAS'], ['TAS'], ['TAS'], ['IBA', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['TAS', 'IEA'], ['TAS'], ['IEA'], ['IEA'], ['IDA', 'IEA'], ['TAS'], ['TAS'], ['IEA'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IEA'], ['ISS', 'IEA'], ['TAS'], ['TAS', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA'], ['TAS'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS'], ['IBA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IEA'], ['IDA'], ['TAS'], ['ISS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['ISS', 'TAS', 'IEA'], ['IEA'], ['TAS'], ['IBA', 'TAS', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['TAS'], ['TAS'], ['IEA'], ['IEA'], ['IBA', 'TAS'], ['TAS'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IEA'], ['IBA'], ['TAS'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS'], ['IEA'], ['IEA']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GO:BP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>GO:0008150</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>biological_process</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0294772890734313</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>"A biological process is the execution of a genetically-encoded biological module or program. It consists of all the steps required to achieve the specific biological objective of the module. A biological process is accomplished by a particular set of molecular functions carried out by specific gene products (or macromolecular complexes), often in a highly regulated manner and in a particular temporal sequence." [GOC:pdt]</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>2459</v>
-      </c>
-      <c r="H20" t="n">
-        <v>464</v>
-      </c>
-      <c r="I20" t="n">
-        <v>446</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2717</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9612068965517241</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.18137454249695</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>query_1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>['TXNDC9', 'CD44', 'NKAIN4', 'LDHB', 'TM7SF3', 'TAGLN', 'CENPW', 'CD63', 'ANXA3', 'SPOCK1', 'UTP18', 'LAMC2', 'SSB', 'CLDN4', 'FOS', 'NQO1', 'RQCD1', 'PTGR1', 'FURIN', 'ITGA11', 'ISG20', 'OCIAD2', 'ACTG1', 'UBB', 'BIRC5', 'BOP1', 'HNRNPH1', 'GNPNAT1', 'KLF6', 'COL5A1', 'SDC4', 'CAV1', 'GADD45A', 'CLU', 'PDLIM5', 'LMO4', 'PLAUR', 'CCL2', 'MIS18BP1', 'JUN', 'TMSB10', 'IL32', 'CCDC80', 'GLRX', 'NAP1L1', 'ATP5G1', 'TOP2A', 'RASSF1', 'TUBA1B', 'DAAM1', 'BBX', 'RSPO3', 'MAP1B', 'CDK2AP2', 'ACTB', 'RAN', 'PPP1R14A', 'RND1', 'HSPA5', 'CNTN1', 'TSPAN4', 'GALNT14', 'KCNMA1', 'CSRP1', 'SLC3A2', 'GNG4', 'S100A11', 'CXCL5', 'DMKN', 'COPZ2', 'CTPS1', 'TSPAN5', 'AKR1B1', 'MLLT11', 'NT5E', 'CDC25B', 'MYL12A', 'TPX2', 'RPL28', 'PSMD8', 'SEMA3C', 'ENO1', 'EMP3', 'TMBIM6', 'GRB10', 'TFPI2', 'ID3', 'POLR2L', 'HSP90AB1', 'BMP1', 'MBOAT2', 'PSMB3', 'CKS2', 'IGFBP3', 'TRAM1', 'TIMP2', 'CTTN', 'AKR1B10', 'TMEM120B', 'IGFBP7', 'B4GALT1', 'SGK1', 'MAF', 'BCAT2', 'CDC42SE1', 'GRAMD1A', 'PAQR5', 'LCE3E', 'CCNB1', 'KRT7', 'FRMD6', 'ELK3', 'MT2A', 'PSME2', 'HSPA8', 'HAPLN3', 'COL4A1', 'LTBP4', 'SCD', 'PSMD14', 'PKM', 'TKT', 'AVPI1', 'S100A16', 'CD24', 'IGFBP4', 'SLC22A18', 'PTTG1', 'GIP', 'PDIA6', 'PCSK1N', 'OSBPL8', 'PGK1', 'CCT2', 'RBP1', 'UBE2S', 'KMT5A', 'HMGA1', 'CXCL1', 'NTS', 'MFGE8', 'FTL', 'PTHLH', 'CPLX2', 'CMTM3', 'ITGB5', 'FBXO22', 'MGLL', 'S100A10', 'PRSS23', 'CCT5', 'HSPB1', 'LGALS3', 'LCE3D', 'BTG1', 'C15orf48', 'AKR1C3', 'MRPS22', 'C1orf56', 'CES1', 'JAK1', 'GAL', 'UBA6', 'SPINT2', 'SCCPDH', 'CYBA', 'DOCK5', 'NUDT19', 'GABARAPL1', 'CTNNAL1', 'NUAK1', 'CXCL2', 'SLC25A37', 'CYP24A1', 'ST3GAL5', 'F2RL1', 'BAMBI', 'RND3', 'ZWINT', 'FBXO32', 'MMP15', 'DHRS2', 'KYNU', 'YWHAE', 'PIR', 'CDCA3', 'PMEPA1', 'CBX6', 'GLS', 'TRA2A', 'SERPINE2', 'ALDH1A1', 'PNPT1', 'DSE', 'MEG3', 'TIMP4', 'G6PD', 'MYO10', 'ETFB', 'MYOF', 'PYCR1', 'SLC7A11', 'KCNG1', 'PGM2L1', 'ALDH3A1', 'STMN1', 'ADGRG1', 'MDM4', 'NUSAP1', 'HMGB1', 'FABP5', 'TXN', 'ANGPTL4', 'PPIB', 'HSPA2', 'NMB', 'MYC', 'RPS27L', 'ARL6IP1', 'TGM2', 'SLN', 'ADAM19', 'EVA1A', 'RUVBL2', 'ODC1', 'GPRC5A', 'TGFBR1', 'FSCN1', 'NTN4', 'CADM1', 'PDLIM2', 'APLP2', 'AKR1C2', 'DKK1', 'FLNB', 'RHOF', 'NEK6', 'FGFR1', 'WDR43', 'CEBPB', 'GPX1', 'EIF6', 'MORF4L2', 'RHOD', 'AXL', 'CDC42', 'LMNA', 'SLU7', 'SH3BGRL3', 'CREM', 'PDCD5', 'PLGRKT', 'DHRS3', 'ZFP36L1', 'AHNAK2', 'EMG1', 'CDKN1A', 'MT3', 'RAET1G', 'RASSF10', 'ILF2', 'CXXC5', 'FSTL3', 'MYL6', 'CALM2', 'S100A4', 'FTH1', 'TUBB6', 'TMEM41B', 'LGALS1', 'PTPRS', 'PRR11', 'ZBED2', 'CYB5A', 'SYT13', 'SLPI', 'ITGA3', 'CTSL', 'GAPDH', 'ULK1', 'SMC4', 'TESC', 'LTBP3', 'DHRS7', 'TK1', 'TRIM47', 'RIN2', 'NPM1', 'CD9', 'CDC20', 'ETS2', 'MYL12B', 'PPP3CA', 'SLAMF9', 'SULT2B1', 'LBH', 'ILK', 'JUP', 'FHL1', 'HJURP', 'ACP2', 'FOXD1', 'COL22A1', 'TXNRD1', 'TGFBI', 'TXNRD2', 'FAM89B', 'COTL1', 'SNHG8', 'MFSD12', 'SLC35F2', 'EZR', 'PSMD2', 'ARPC3', 'PSMD4', 'PUS1', 'APOBEC3C', 'TPM2', 'SH3KBP1', 'NPTX1', 'PODXL', 'CDH2', 'ANXA2', 'HMGA2', 'ELF3', 'ACOT9', 'ANTXR1', 'TUBB', 'S100A6', 'FAM64A', 'MALAT1', 'COL5A2', 'CNN3', 'TUBA4A', 'AURKA', 'CDK1', 'MGST1', 'NUAK2', 'DDB2', 'SERPINE1', 'PRMT5', 'CDA', 'AKAP12', 'CCNB2', 'PVR', 'ECH1', 'PRC1', 'UBC', 'METRN', 'SKIL', 'HES1', 'HMGB2', 'DKC1', 'NAA38', 'RAP2B', 'CCDC85B', 'PSMA4', 'MT1X', 'SGCE', 'PHKG1', 'TUBA1C', 'PDLIM7', 'RGS3', 'SRGAP1', 'TSPAN15', 'TNFRSF1A', 'PRSS3', 'SYT1', 'VCAN', 'NPC2', 'FN1', 'ITGA2', 'GTPBP4', 'S100A13', 'AMIGO2', 'RDX', 'JUNB', 'EPAS1', 'TP53I3', 'RPL22L1', 'LACTB', 'EIF2S3', 'TUBB4B', 'FLOT1', 'IL11', 'TMSB4X', 'PSMA5', 'PTPRJ', 'CTNNB1', 'COL1A1', 'RAP1GAP', 'SRGN', 'PYCARD', 'TNFRSF12A', 'GPX2', 'HAGHL', 'SSR3', 'BCL2A1', 'VIM', 'ESAM', 'GINS2', 'FXYD5', 'KRT81', 'PRMT1', 'HSP90AA1', 'PCDH9', 'CXCL8', 'PPP1CB', 'SLC7A7', 'SPP1', 'MKI67', 'MCL1', 'STC1', 'ZFP36', 'RAB3B', 'COL4A2', 'CDC42EP3', 'ITGA5', 'UPP1', 'SNW1', 'CDKN3', 'MLXIP', 'NR0B1', 'TPM1', 'SOX4', 'NUPR1', 'PHLDA3', 'CENPA', 'CA12', 'KPNA2', 'SUCLG1', 'PACSIN3', 'SLC2A3', 'SLC2A1', 'DOLK', 'CLPTM1L', 'INO80C', 'PLEK2', 'AP2M1', 'C1QBP', 'FDXR', 'QPCT', 'CKS1B', 'PRDX1', 'PDIA4', 'PLK1']</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>[['IBA', 'ND'], ['IDA', 'IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IDA', 'TAS'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IC', 'IEA'], ['IMP', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'NAS'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['ISS', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'TAS'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HDA', 'HMP', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IC', 'IEA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['HMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IMP', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['HMP'], ['IDA', 'ISS', 'TAS', 'IEA'], ['TAS', 'NAS', 'IC', 'IEA'], ['IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IDA', 'IGI', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'TAS', 'IEA'], ['ISS', 'IBA', 'ND', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IGI', 'NAS', 'IEA'], ['IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IMP', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISO', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'HMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'HMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['NAS', 'ND'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['ISS', 'TAS', 'ND', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'NAS'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'NAS', 'IC', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ND', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IC', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IEA'], ['IBA', 'ND', 'IEA'], ['IDA', 'IMP', 'HEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IBA', 'NAS', 'IEA'], ['IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IC', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'ND', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IDA', 'ISS', 'NAS'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'HMP', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'IC', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IPI', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['EXP', 'IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IPI', 'IMP', 'IGI', 'HEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'IC', 'IEA'], ['IMP'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEA'], ['IBA', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IBA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'HMP'], ['IDA', 'IBA', 'IEA'], ['TAS'], ['IDA', 'IMP', 'HEP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'HMP', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA'], ['IMP'], ['IEA'], ['IBA', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'ISO', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'ISO', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEA'], ['IEA'], ['IDA', 'IPI', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'ND'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'HMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'IC', 'IEA'], ['IDA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA'], ['ISS', 'IBA', 'IEA'], ['IBA'], ['IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'TAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IBA', 'ND', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['ND', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISO', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IEP', 'ISS', 'IBA', 'IEA'], ['ISS', 'IBA'], ['IDA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['TAS', 'NAS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IEP', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IEA'], ['EXP', 'IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'NAS', 'IC'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP', 'IBA', 'TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IBA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'ISS', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'HMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IMP'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['TAS'], ['NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['TAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'HDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'HDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IGI', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA'], ['IBA', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IBA', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'TAS', 'NAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IDA', 'IPI', 'IMP', 'ISS', 'ISO', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IBA', 'IEA'], ['NAS', 'IEA'], ['IBA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IGI', 'IEP', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'ISS', 'IBA', 'TAS'], ['IDA', 'IMP', 'IGI', 'IBA', 'NAS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IEP', 'IBA', 'NAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IEP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'TAS', 'IC', 'IEA'], ['IDA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'NAS', 'IEA'], ['IMP', 'IEP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'NAS', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IDA', 'IGI', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IGI', 'ISS', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA'], ['IEA'], ['IDA', 'IMP', 'ISO', 'IBA', 'IEA'], ['IBA', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'NAS', 'IEA'], ['IDA', 'IMP', 'ISS', 'IBA', 'TAS', 'IEA'], ['IBA', 'TAS', 'IEA'], ['IDA', 'TAS'], ['IBA', 'IEA'], ['IDA', 'IBA', 'TAS', 'IEA'], ['ISS', 'IBA', 'TAS', 'IEA'], ['IDA', 'IMP', 'IBA', 'TAS', 'IEA']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GO:BP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GO:0098609</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>cell-cell adhesion</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.04426473377476416</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>"The attachment of one cell to another cell via adhesion molecules." [GOC:dos]</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>183</v>
-      </c>
-      <c r="H21" t="n">
-        <v>464</v>
-      </c>
-      <c r="I21" t="n">
-        <v>57</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2717</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.1228448275862069</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.3114754098360656</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>query_1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>['GO:0007155']</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>['CD44', 'CLDN4', 'ITGA11', 'ACTG1', 'SDC4', 'CAV1', 'PDLIM5', 'PLAUR', 'CCL2', 'ACTB', 'CNTN1', 'CSRP1', 'S100A11', 'NT5E', 'MYL12A', 'CD24', 'ITGB5', 'HSPB1', 'LGALS3', 'JAK1', 'SPINT2', 'SERPINE2', 'MYO10', 'SLC7A11', 'HMGB1', 'ADAM19', 'CADM1', 'CEBPB', 'ZFP36L1', 'FSTL3', 'LGALS1', 'PTPRS', 'ITGA3', 'CD9', 'PPP3CA', 'ILK', 'JUP', 'EZR', 'PODXL', 'CDH2', 'ANXA2', 'CNN3', 'PVR', 'HES1', 'RAP2B', 'ITGA2', 'GTPBP4', 'AMIGO2', 'RDX', 'FLOT1', 'CTNNB1', 'PYCARD', 'ESAM', 'FXYD5', 'PCDH9', 'ITGA5', 'SOX4']</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>[['IMP', 'NAS'], ['ISS'], ['IBA'], ['HMP'], ['IMP'], ['IDA'], ['IEA'], ['IMP'], ['ISS'], ['HMP', 'NAS'], ['IBA'], ['HMP'], ['IEA'], ['IDA'], ['HMP'], ['IDA', 'IBA', 'NAS'], ['IMP', 'IBA'], ['HMP'], ['IDA', 'ISS'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['IDA', 'IMP'], ['IDA'], ['ISS', 'IBA'], ['ISS', 'IEA'], ['IEA'], ['IDA'], ['IDA', 'IEA'], ['IDA', 'IMP', 'IBA'], ['IBA', 'IEA'], ['IDA'], ['ISS', 'IEA'], ['HMP'], ['IDA', 'IMP', 'ISS', 'IBA', 'IEA'], ['IEP'], ['IDA', 'ISS', 'IBA', 'IEA'], ['IMP', 'ISS', 'IBA', 'IEA'], ['IEA'], ['IEA'], ['IBA'], ['IEA'], ['IDA'], ['IBA'], ['IDA'], ['ISS'], ['IMP'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IBA', 'IEA'], ['NAS'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['ISS', 'IEA']]</t>
+          <t>[['IEA'], ['IMP'], ['IEA'], ['IDA', 'IBA'], ['ISS', 'IEA'], ['IEA'], ['IEA'], ['ISS', 'IEA'], ['IBA'], ['IDA', 'NAS', 'IC'], ['IMP', 'ISS', 'IEA'], ['IDA', 'IBA'], ['IDA'], ['IDA'], ['IMP', 'IGI', 'IBA', 'IEA'], ['IDA'], ['IDA'], ['IEA'], ['IDA', 'NAS'], ['IEA'], ['IBA', 'IEA'], ['HMP'], ['IDA', 'IBA'], ['IEA'], ['IDA', 'IBA', 'IEA'], ['IMP'], ['IEA'], ['ISS', 'IEA'], ['ISS', 'IEA'], ['IEA'], ['IBA'], ['IDA'], ['IMP'], ['IDA', 'ISS', 'TAS', 'IEA'], ['IDA'], ['IEA'], ['IBA'], ['IBA', 'IEA'], ['IEA'], ['NAS'], ['IDA', 'IMP', 'ISS', 'IEA'], ['IEA'], ['IDA', 'IBA'], ['ISS'], ['IEA'], ['IMP', 'IBA', 'IEA'], ['IMP', 'IBA', 'IEA'], ['TAS', 'IEA'], ['HMP'], ['IEA'], ['HMP'], ['IDA'], ['IDA', 'ISS', 'IC', 'IEA'], ['IMP', 'TAS'], ['IMP'], ['IDA'], ['IMP'], ['TAS', 'NAS'], ['IMP'], ['IEA'], ['IDA'], ['IDA'], ['IDA', 'IEA'], ['IEA'], ['ISS'], ['IEA'], ['IEA'], ['IMP'], ['IDA'], ['TAS', 'IEA'], ['IEA'], ['IDA'], ['HMP'], ['IDA'], ['IDA'], ['IEA'], ['IMP', 'ISS'], ['IDA'], ['IEA'], ['IMP'], ['ISS', 'IBA', 'IEA'], ['IMP', 'IBA'], ['IMP', 'ISS'], ['IBA', 'IEA'], ['NAS'], ['IMP', 'ISS'], ['IDA'], ['IEA'], ['IEA'], ['IDA'], ['IMP', 'ISS', 'IC', 'IEA'], ['HMP'], ['IDA', 'IMP', 'TAS', 'NAS', 'IC'], ['IMP'], ['IDA', 'NAS', 'IEA'], ['IEA'], ['NAS'], ['ISS'], ['IDA', 'IEA'], ['IEA'], ['TAS'], ['IMP', 'IEA'], ['IEA'], ['IEA'], ['IEA'], ['IMP'], ['IDA'], ['ISS', 'IEA'], ['IMP', 'NAS', 'IEA'], ['IEA'], ['IMP'], ['TAS'], ['IEA'], ['IDA', 'IMP', 'ISS'], ['TAS'], ['IDA'], ['IMP'], ['IEA'], ['IBA'], ['IEA'], ['IEA'], ['IDA'], ['IMP'], ['IMP'], ['IEP', 'IEA'], ['IEA'], ['HMP']]</t>
         </is>
       </c>
     </row>
